--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/aeu.00037_19470820/aeu.00037_19470820.7.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/aeu.00037_19470820/aeu.00037_19470820.7.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -979,7 +979,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/aeu.00037_19470820/aeu.00037_19470820.7.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/aeu.00037_19470820/aeu.00037_19470820.7.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y644"/>
+  <dimension ref="A1:Y648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -598,7 +598,7 @@
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>L1312: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 86Edouard (letter/digit mix) | localized OCR phrase divergence vs other OCR: "65 Edouard" vs "86Edouard" :: 86Edouard Garneau, Ã©cole Grandin ..........</t>
+          <t>L1312: punctuation artifact: repeated periods | suspicious token(s): 86Edouard (letter/digit mix) | localized OCR phrase divergence vs other OCR: "65 Edouard" vs "86Edouard" :: 86Edouard Garneau, école Grandin ..........</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
@@ -608,21 +608,25 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>L330: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): eThibeault (odd internal casing) :: Lorraine Tellier, Ã©col eThibeault .........</t>
+          <t>L330: punctuation artifact: repeated periods | suspicious token(s): eThibeault (odd internal casing) :: Lorraine Tellier, écol eThibeault .........</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Carmelle Latour, Ã© cole Grandin</t>
+          <t>L327: stray/suspicious non-ASCII glyph(s): U+53E3 CJK UNIFIED IDEOGRAPH-53E3 | isolated marker/symbol line :: 口</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L2: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Pierrette Soumis, Ã©cole Thibeault ......</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM](Suite de la page 6)</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM](Suite de la page 6)</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L3: isolated marker/symbol line :: 91</t>
@@ -635,12 +639,12 @@
       </c>
       <c r="P2" s="1" t="inlineStr">
         <is>
-          <t>L43: punctuation artifact: repeated periods :: FranÃ§cole Ouellette, Legal ...</t>
+          <t>L43: punctuation artifact: repeated periods :: Françcole Ouellette, Legal ...</t>
         </is>
       </c>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L2: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Pierrette Soumis, Ã©cole Thibeault ......</t>
+          <t>L2: punctuation artifact: repeated periods :: Pierrette Soumis, école Thibeault ......</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -677,7 +681,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -704,12 +708,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: H Ã© Ã©lÃ¨ne Dansereau, pensionnat de I'Assomption.</t>
+          <t>L372: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Lapointe, Bonnyville ...........</t>
+          <t>L621: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods | line starts with punctuation glued to text :: • Irène Lambert, Bonnyville .....................</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -726,18 +730,18 @@
       </c>
       <c r="P3" s="1" t="inlineStr">
         <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: C Ã© cile Roy, Fort Kent...</t>
+          <t>L142: punctuation artifact: repeated periods :: C é cile Roy, Fort Kent...</t>
         </is>
       </c>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Lapointe, Bonnyville ...........</t>
+          <t>L3: punctuation artifact: repeated periods :: Thérèse Lapointe, Bonnyville ...........</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L627: punctuation artifact: repeated periods | line starts with lowercase prefix glued to capitalized word | suspicious token(s): iJacques (odd internal casing) :: iJacques Gagnon, Bonnyville......................</t>
+          <t>L621: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods | line starts with punctuation glued to text :: • Irène Lambert, Bonnyville .....................</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -787,12 +791,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L34: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lorette Meunier, Ã© cole Thibeault</t>
+          <t>L1227: stray/suspicious non-ASCII glyph(s): U+54C1 CJK UNIFIED IDEOGRAPH-54C1 :: 8 品 8</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L4: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Bordeleau, Bonnyville ...........</t>
+          <t>L1877: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Victor Beaudry</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -809,16 +813,20 @@
       </c>
       <c r="P4" s="1" t="inlineStr">
         <is>
-          <t>L1307: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: double/multiple hyphen :: les noms sont inscrits dans le dÃ©velop--</t>
+          <t>L1307: punctuation artifact: double/multiple hyphen :: les noms sont inscrits dans le dévelop--</t>
         </is>
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L4: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Bordeleau, Bonnyville ...........</t>
+          <t>L4: punctuation artifact: repeated periods :: Cécile Bordeleau, Bonnyville ...........</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L627: punctuation artifact: repeated periods | line starts with lowercase prefix glued to capitalized word | suspicious token(s): iJacques (odd internal casing) :: iJacques Gagnon, Bonnyville......................</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -834,12 +842,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>682</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>802</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -862,14 +870,10 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L39: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Adrienne Thivierge, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L6: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Cannelle Latour, Ã©cole Grandin .........</t>
-        </is>
-      </c>
+          <t>L1238: stray/suspicious non-ASCII glyph(s): U+540D CJK UNIFIED IDEOGRAPH-540D, U+7537 CJK UNIFIED IDEOGRAPH-7537, U+5976 CJK UNIFIED IDEOGRAPH-5976, U+51FA CJK UNIFIED IDEOGRAPH-51FA :: 名 男 奶 出 出</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -884,7 +888,7 @@
       </c>
       <c r="P5" s="1" t="inlineStr">
         <is>
-          <t>L1325: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: double/multiple hyphen :: des San-Fran partitÃ©s par les dÃ©pour--</t>
+          <t>L1325: punctuation artifact: double/multiple hyphen :: des San-Fran partités par les dépour--</t>
         </is>
       </c>
       <c r="Q5" s="1" t="inlineStr">
@@ -893,7 +897,11 @@
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L1877: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Victor Beaudry</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr"/>
@@ -932,19 +940,15 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>L623: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 1C (letter/digit mix) :: 1CÃ©cile Lacombe, Bonnyville.................</t>
+          <t>L623: punctuation artifact: repeated periods | suspicious token(s): 1C (letter/digit mix) :: 1Cécile Lacombe, Bonnyville.................</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Denis Villecourt, La Corey â€¦.</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L8: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: IrÃ¨ne Beaudoin, Tangente ...............</t>
-        </is>
-      </c>
+          <t>L1282: stray/suspicious non-ASCII glyph(s): U+4E0A CJK UNIFIED IDEOGRAPH-4E0A | isolated marker/symbol line :: 上</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -959,12 +963,12 @@
       </c>
       <c r="P6" s="1" t="inlineStr">
         <is>
-          <t>L1327: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: double/multiple hyphen :: gnala en fondant une agence de goÃ©let--</t>
+          <t>L1327: punctuation artifact: double/multiple hyphen :: gnala en fondant une agence de goélet--</t>
         </is>
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L6: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Cannelle Latour, Ã©cole Grandin .........</t>
+          <t>L6: punctuation artifact: repeated periods :: Cannelle Latour, école Grandin .........</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -1012,14 +1016,10 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Germaine Roy, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: HÃ©lÃ¨ne Dansereau, pensionnat de l'Assomption</t>
-        </is>
-      </c>
+          <t>L1294: stray/suspicious non-ASCII glyph(s): U+548C CJK UNIFIED IDEOGRAPH-548C | isolated marker/symbol line :: 和</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -1082,19 +1082,15 @@
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>L1095: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 7C (letter/digit mix) :: 89 Monique Roy. Ã©cole consolidÃ©e, Donnelly ............7C</t>
+          <t>L1095: punctuation artifact: repeated periods | suspicious token(s): 7C (letter/digit mix) :: 89 Monique Roy. école consolidée, Donnelly ............7C</t>
         </is>
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ren Ã© Roy, ecole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L16: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Schayes, Ã©cole Thibeault ........</t>
-        </is>
-      </c>
+          <t>L1301: stray/suspicious non-ASCII glyph(s): U+771F CJK UNIFIED IDEOGRAPH-771F | isolated marker/symbol line :: 真</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -1109,12 +1105,12 @@
       </c>
       <c r="P8" s="1" t="inlineStr">
         <is>
-          <t>L1468: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: double/multiple hyphen :: ommÃ© plus tard a--</t>
+          <t>L1468: punctuation artifact: double/multiple hyphen :: ommé plus tard a--</t>
         </is>
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L8: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: IrÃ¨ne Beaudoin, Tangente ...............</t>
+          <t>L8: punctuation artifact: repeated periods :: Irène Beaudoin, Tangente ...............</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -1157,19 +1153,15 @@
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>L1312: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 86Edouard (letter/digit mix) | localized OCR phrase divergence vs other OCR: "65 Edouard" vs "86Edouard" :: 86Edouard Garneau, Ã©cole Grandin ..........</t>
+          <t>L1312: punctuation artifact: repeated periods | suspicious token(s): 86Edouard (letter/digit mix) | localized OCR phrase divergence vs other OCR: "65 Edouard" vs "86Edouard" :: 86Edouard Garneau, école Grandin ..........</t>
         </is>
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Raymond Cot Ã©, Couvent Notre-Dame</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lorette Meunier, Ã©cole Thibeault .......</t>
-        </is>
-      </c>
+          <t>L1405: stray/suspicious non-ASCII glyph(s): U+7C73 CJK UNIFIED IDEOGRAPH-7C73 | isolated marker/symbol line :: 米</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1205,12 +1197,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1227,16 +1219,8 @@
           <t>L1665: punctuation artifact: repeated periods | suspicious token(s): 82i (letter/digit mix) | localized OCR phrase divergence vs other OCR: "57 Leo" vs "82i 81 L o" :: ...82i</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L72: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Andr Ã© Doucet, Saint-Paul</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L19: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Adrienne Thivierge, Ã©cole Grandin ......</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
@@ -1277,7 +1261,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1291,19 +1275,11 @@
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>L1814: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): l'artiste1 (letter/digit mix) :: clave tomba et fut prÃ©sentÃ©e Ã l'artiste1</t>
-        </is>
-      </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L76: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Madeleine Cloutier, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Madeleine Meunier, Ã©cole Thibeault .....</t>
-        </is>
-      </c>
+          <t>L1814: suspicious token(s): l'artiste1 (letter/digit mix) :: clave tomba et fut présentée à l'artiste1</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr"/>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1339,7 +1315,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>647</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1361,16 +1337,8 @@
           <t>L1901: suspicious token(s): 1er (letter/digit mix) :: National avant le 1er septembre 1947.</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Leo Garand, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Germaine Roy, Ã©cole consolidÃ©e, Falher .</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
@@ -1386,7 +1354,7 @@
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>L12: punctuation artifact: repeated periods :: FranÃ§ois McMahon, Saint-Paul ...........</t>
+          <t>L12: punctuation artifact: repeated periods :: François McMahon, Saint-Paul ...........</t>
         </is>
       </c>
       <c r="R12" s="1" t="inlineStr"/>
@@ -1425,19 +1393,11 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>L2048: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN | suspicious token(s): sa1 (letter/digit mix) :: Ã l'Ã¢ge de 77 ans. Cinq ans avant sa1</t>
-        </is>
-      </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Cl Ã© ment B Ã© rub Ã©, Beaumont</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Roy, Ã©cole consolidÃ©e, Falher .....</t>
-        </is>
-      </c>
+          <t>L2048: suspicious token(s): sa1 (letter/digit mix) :: à l'âge de 77 ans. Cinq ans avant sa1</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr"/>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
@@ -1478,7 +1438,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1491,16 +1451,8 @@
       <c r="G14" s="1" t="inlineStr"/>
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Jeannine Gosselin, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT, U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Raymond CÃ´tÃ©, Couvent Notre-Dame .......</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
@@ -1554,16 +1506,8 @@
       <c r="G15" s="1" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: L Ã© on Hebert, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L35: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© Doucet, Saint-Paul ...............</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
@@ -1579,7 +1523,7 @@
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>L16: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Schayes, Ã©cole Thibeault ........</t>
+          <t>L16: punctuation artifact: repeated periods :: Cécile Schayes, école Thibeault ........</t>
         </is>
       </c>
       <c r="R15" s="1" t="inlineStr"/>
@@ -1617,16 +1561,8 @@
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Georges Lajoie, Th Ã© rien</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L37: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Madeleine Cloutier, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
@@ -1642,7 +1578,7 @@
       <c r="P16" s="1" t="inlineStr"/>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lorette Meunier, Ã©cole Thibeault .......</t>
+          <t>L17: punctuation artifact: repeated periods :: Lorette Meunier, école Thibeault .......</t>
         </is>
       </c>
       <c r="R16" s="1" t="inlineStr"/>
@@ -1680,16 +1616,8 @@
       <c r="G17" s="1" t="inlineStr"/>
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L122: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paul Labonte. Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L38: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©o Garand, Ã©cole consolidÃ©e, Falher ...</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
@@ -1731,16 +1659,8 @@
       <c r="G18" s="1" t="inlineStr"/>
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Guy Bachand, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeannette Morin, Ã©cole Grandin .........</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
@@ -1756,7 +1676,7 @@
       <c r="P18" s="1" t="inlineStr"/>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>L19: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Adrienne Thivierge, Ã©cole Grandin ......</t>
+          <t>L19: punctuation artifact: repeated periods :: Adrienne Thivierge, école Grandin ......</t>
         </is>
       </c>
       <c r="R18" s="1" t="inlineStr"/>
@@ -1782,16 +1702,8 @@
       <c r="G19" s="1" t="inlineStr"/>
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L133: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: Cecile Bussi Ã¨ re, pensionnat de l'Assomption</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ClÃ©ment BÃ©rubÃ©, Beaumont ...............</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
@@ -1833,16 +1745,8 @@
       <c r="G20" s="1" t="inlineStr"/>
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L139: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paul Roy, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeannine Gosselin, Ã©cole Thibeault .....</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
@@ -1858,7 +1762,7 @@
       <c r="P20" s="1" t="inlineStr"/>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>L21: punctuation artifact: repeated periods :: FranÃ§oise Ouellette, Legal .............</t>
+          <t>L21: punctuation artifact: repeated periods :: Françoise Ouellette, Legal .............</t>
         </is>
       </c>
       <c r="R20" s="1" t="inlineStr"/>
@@ -1884,16 +1788,8 @@
       <c r="G21" s="1" t="inlineStr"/>
       <c r="H21" s="1" t="inlineStr"/>
       <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: C Ã© cile Roy, Fort Kent...</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Armand Robert, Ã©cole Thibeault .........</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
@@ -1935,16 +1831,8 @@
       <c r="G22" s="1" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L146: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Joseph Girard, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©on HÃ©bert, Ã©cole consolidÃ©e, Falher ..</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
@@ -1960,7 +1848,7 @@
       <c r="P22" s="1" t="inlineStr"/>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Madeleine Meunier, Ã©cole Thibeault .....</t>
+          <t>L23: punctuation artifact: repeated periods :: Madeleine Meunier, école Thibeault .....</t>
         </is>
       </c>
       <c r="R22" s="1" t="inlineStr"/>
@@ -1982,16 +1870,8 @@
       <c r="G23" s="1" t="inlineStr"/>
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr"/>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L152: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Andr Ã© Fortier, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L52: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Adolphe Boissonneault, Ã©cole Thibeault .</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
@@ -2029,16 +1909,8 @@
       <c r="G24" s="1" t="inlineStr"/>
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr"/>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>L156: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Raymond Roy, Ã©cole consolidee, Falher . .</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jean-Louis Champagne, Ã©cole Thibeault ..</t>
-        </is>
-      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
@@ -2076,16 +1948,8 @@
       <c r="G25" s="1" t="inlineStr"/>
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr"/>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>L160: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Cecile Pariseau, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Georges Lajoie, ThÃ©rien ................</t>
-        </is>
-      </c>
+      <c r="J25" s="1" t="inlineStr"/>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
@@ -2123,16 +1987,8 @@
       <c r="G26" s="1" t="inlineStr"/>
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>L162: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Jeannine Cote, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeannine Chalifoux, Ã©cole Thibeault .....</t>
-        </is>
-      </c>
+      <c r="J26" s="1" t="inlineStr"/>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
@@ -2148,7 +2004,7 @@
       <c r="P26" s="1" t="inlineStr"/>
       <c r="Q26" s="1" t="inlineStr">
         <is>
-          <t>L27: punctuation artifact: repeated periods :: Marie-Rose-NoÃ«lla Croteau, Fort Kent ...</t>
+          <t>L27: punctuation artifact: repeated periods :: Marie-Rose-Noëlla Croteau, Fort Kent ...</t>
         </is>
       </c>
       <c r="R26" s="1" t="inlineStr"/>
@@ -2170,16 +2026,8 @@
       <c r="G27" s="1" t="inlineStr"/>
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>L164: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Claire Rondeau, Fort Kent .â€¦ .</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Paul LabontÃ©. Ã©cole Thibeault .......</t>
-        </is>
-      </c>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
@@ -2195,7 +2043,7 @@
       <c r="P27" s="1" t="inlineStr"/>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Roy, Ã©cole consolidÃ©e, Falher .....</t>
+          <t>L29: punctuation artifact: repeated periods :: René Roy, école consolidée, Falher .....</t>
         </is>
       </c>
       <c r="R27" s="1" t="inlineStr"/>
@@ -2217,16 +2065,8 @@
       <c r="G28" s="1" t="inlineStr"/>
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>L168: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Denise Maure, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Guy Bachand, Ã©cole Thibeault ........</t>
-        </is>
-      </c>
+      <c r="J28" s="1" t="inlineStr"/>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
@@ -2264,16 +2104,8 @@
       <c r="G29" s="1" t="inlineStr"/>
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>L186: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: G Ã© rard Levasseur, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: AdÃ¨le Legault, Bonnyville ...........</t>
-        </is>
-      </c>
+      <c r="J29" s="1" t="inlineStr"/>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
@@ -2289,7 +2121,7 @@
       <c r="P29" s="1" t="inlineStr"/>
       <c r="Q29" s="1" t="inlineStr">
         <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT, U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Raymond CÃ´tÃ©, Couvent Notre-Dame .......</t>
+          <t>L31: punctuation artifact: repeated periods :: Raymond Côté, Couvent Notre-Dame .......</t>
         </is>
       </c>
       <c r="R29" s="1" t="inlineStr"/>
@@ -2311,16 +2143,8 @@
       <c r="G30" s="1" t="inlineStr"/>
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
-      <c r="J30" s="1" t="inlineStr">
-        <is>
-          <t>L200: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: JosÃ©phine L L'Heureux, pensionnat de I'Assomption</t>
-        </is>
-      </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Gemma Girard, Ã©cole Grandin ...</t>
-        </is>
-      </c>
+      <c r="J30" s="1" t="inlineStr"/>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
@@ -2358,16 +2182,8 @@
       <c r="G31" s="1" t="inlineStr"/>
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>L204: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: L Ã© o Faucher, Saint-Paul</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© Picard, Ã©cole Grandin ...</t>
-        </is>
-      </c>
+      <c r="J31" s="1" t="inlineStr"/>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
@@ -2405,16 +2221,8 @@
       <c r="G32" s="1" t="inlineStr"/>
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
-      <c r="J32" s="1" t="inlineStr">
-        <is>
-          <t>L210: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©da Bonin, La Corey ........................</t>
-        </is>
-      </c>
+      <c r="J32" s="1" t="inlineStr"/>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
@@ -2452,16 +2260,8 @@
       <c r="G33" s="1" t="inlineStr"/>
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
-      <c r="J33" s="1" t="inlineStr">
-        <is>
-          <t>L211: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marie-Rose Garneau, Ã©cole Dunrobin ..........</t>
-        </is>
-      </c>
+      <c r="J33" s="1" t="inlineStr"/>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
@@ -2477,7 +2277,7 @@
       <c r="P33" s="1" t="inlineStr"/>
       <c r="Q33" s="1" t="inlineStr">
         <is>
-          <t>L35: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© Doucet, Saint-Paul ...............</t>
+          <t>L35: punctuation artifact: repeated periods :: André Doucet, Saint-Paul ...............</t>
         </is>
       </c>
       <c r="R33" s="1" t="inlineStr"/>
@@ -2499,16 +2299,8 @@
       <c r="G34" s="1" t="inlineStr"/>
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>L217: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Laurette Pr Ã© fentaine, Legal</t>
-        </is>
-      </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L76: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: HÃ©lÃ¨ne Richard, Bonnyville ..................</t>
-        </is>
-      </c>
+      <c r="J34" s="1" t="inlineStr"/>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
@@ -2546,16 +2338,8 @@
       <c r="G35" s="1" t="inlineStr"/>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
-      <c r="J35" s="1" t="inlineStr">
-        <is>
-          <t>L229: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Robert Despins, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoinette Casavant, Ã©cole Dunrobin .........</t>
-        </is>
-      </c>
+      <c r="J35" s="1" t="inlineStr"/>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
@@ -2571,7 +2355,7 @@
       <c r="P35" s="1" t="inlineStr"/>
       <c r="Q35" s="1" t="inlineStr">
         <is>
-          <t>L38: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©o Garand, Ã©cole consolidÃ©e, Falher ...</t>
+          <t>L38: punctuation artifact: repeated periods :: Léo Garand, école consolidée, Falher ...</t>
         </is>
       </c>
       <c r="R35" s="1" t="inlineStr"/>
@@ -2593,16 +2377,8 @@
       <c r="G36" s="1" t="inlineStr"/>
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
-      <c r="J36" s="1" t="inlineStr">
-        <is>
-          <t>L235: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Huguette H Ã© tu. Bonnyville</t>
-        </is>
-      </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Philippe Lemire, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="J36" s="1" t="inlineStr"/>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
@@ -2640,16 +2416,8 @@
       <c r="G37" s="1" t="inlineStr"/>
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
-      <c r="J37" s="1" t="inlineStr">
-        <is>
-          <t>L239: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Bernard Ouellette, Sainte-Lina .â€¦ . .â€¦</t>
-        </is>
-      </c>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GisÃ¨le Aubin, Ã©cole consolidÃ©e, Falher ......</t>
-        </is>
-      </c>
+      <c r="J37" s="1" t="inlineStr"/>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
@@ -2687,16 +2455,8 @@
       <c r="G38" s="1" t="inlineStr"/>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
-      <c r="J38" s="1" t="inlineStr">
-        <is>
-          <t>L250: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Carmela Ch Ã© nard, Tangente</t>
-        </is>
-      </c>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Hector Letourneau, Ã©cole Grandin ............</t>
-        </is>
-      </c>
+      <c r="J38" s="1" t="inlineStr"/>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
@@ -2734,16 +2494,8 @@
       <c r="G39" s="1" t="inlineStr"/>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
-      <c r="J39" s="1" t="inlineStr">
-        <is>
-          <t>L257: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: McElizabeth Meunier, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L87: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: EugÃ©nie Forcier, Ã©cole consolidÃ©e, Donnelly .</t>
-        </is>
-      </c>
+      <c r="J39" s="1" t="inlineStr"/>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
@@ -2781,16 +2533,8 @@
       <c r="G40" s="1" t="inlineStr"/>
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>L262: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: G Ã© rald Royer, Beaumont</t>
-        </is>
-      </c>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Raymond Sauvageau, Ã©cole consolidÃ©e, Falher .</t>
-        </is>
-      </c>
+      <c r="J40" s="1" t="inlineStr"/>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
@@ -2828,16 +2572,8 @@
       <c r="G41" s="1" t="inlineStr"/>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>L264: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Laurier Rousseau, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L89: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Mercier, Fort Kent ...................</t>
-        </is>
-      </c>
+      <c r="J41" s="1" t="inlineStr"/>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
@@ -2853,7 +2589,7 @@
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeannette Morin, Ã©cole Grandin .........</t>
+          <t>L44: punctuation artifact: repeated periods :: Jeannette Morin, école Grandin .........</t>
         </is>
       </c>
       <c r="R41" s="1" t="inlineStr"/>
@@ -2875,16 +2611,8 @@
       <c r="G42" s="1" t="inlineStr"/>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
-      <c r="J42" s="1" t="inlineStr">
-        <is>
-          <t>L268: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Claude Proulx, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roger Dusseault, Ã©cole consolidÃ©e, Falher ...</t>
-        </is>
-      </c>
+      <c r="J42" s="1" t="inlineStr"/>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
@@ -2900,7 +2628,7 @@
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr">
         <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ClÃ©ment BÃ©rubÃ©, Beaumont ...............</t>
+          <t>L45: punctuation artifact: repeated periods :: Clément Bérubé, Beaumont ...............</t>
         </is>
       </c>
       <c r="R42" s="1" t="inlineStr"/>
@@ -2922,16 +2650,8 @@
       <c r="G43" s="1" t="inlineStr"/>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
-      <c r="J43" s="1" t="inlineStr">
-        <is>
-          <t>L270: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Marcel Abont Ã©, ecole Thibeault</t>
-        </is>
-      </c>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoinette Brien, Ã©cole consolidÃ©e, Falher ..</t>
-        </is>
-      </c>
+      <c r="J43" s="1" t="inlineStr"/>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
@@ -2969,16 +2689,8 @@
       <c r="G44" s="1" t="inlineStr"/>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
-      <c r="J44" s="1" t="inlineStr">
-        <is>
-          <t>L277: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: G Ã© rard Casavant, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L95: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roger Loiseau, Ã©cole consolidÃ©e, Falher .....</t>
-        </is>
-      </c>
+      <c r="J44" s="1" t="inlineStr"/>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
@@ -2994,7 +2706,7 @@
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr">
         <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeannine Gosselin, Ã©cole Thibeault .....</t>
+          <t>L47: punctuation artifact: repeated periods :: Jeannine Gosselin, école Thibeault .....</t>
         </is>
       </c>
       <c r="R44" s="1" t="inlineStr"/>
@@ -3016,16 +2728,8 @@
       <c r="G45" s="1" t="inlineStr"/>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
-      <c r="J45" s="1" t="inlineStr">
-        <is>
-          <t>L280: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Maurice Chevalier, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Garneau, Ã©cole Dunrobin ..............</t>
-        </is>
-      </c>
+      <c r="J45" s="1" t="inlineStr"/>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
@@ -3041,7 +2745,7 @@
       <c r="P45" s="1" t="inlineStr"/>
       <c r="Q45" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Armand Robert, Ã©cole Thibeault .........</t>
+          <t>L48: punctuation artifact: repeated periods :: Armand Robert, école Thibeault .........</t>
         </is>
       </c>
       <c r="R45" s="1" t="inlineStr"/>
@@ -3063,16 +2767,8 @@
       <c r="G46" s="1" t="inlineStr"/>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
-      <c r="J46" s="1" t="inlineStr">
-        <is>
-          <t>L282: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: L Ã© a Ricard, couvent Notre-Dame</t>
-        </is>
-      </c>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rita Laplante, Ã©cole Dunrobin ...............</t>
-        </is>
-      </c>
+      <c r="J46" s="1" t="inlineStr"/>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
@@ -3110,16 +2806,8 @@
       <c r="G47" s="1" t="inlineStr"/>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
-      <c r="J47" s="1" t="inlineStr">
-        <is>
-          <t>L286: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Euclidean B Ã© rub Ã©, Beaumont</t>
-        </is>
-      </c>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©ona Verreault, Tangente ...................</t>
-        </is>
-      </c>
+      <c r="J47" s="1" t="inlineStr"/>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
@@ -3135,7 +2823,7 @@
       <c r="P47" s="1" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©on HÃ©bert, Ã©cole consolidÃ©e, Falher ..</t>
+          <t>L50: punctuation artifact: repeated periods :: Léon Hébert, école consolidée, Falher ..</t>
         </is>
       </c>
       <c r="R47" s="1" t="inlineStr"/>
@@ -3157,16 +2845,8 @@
       <c r="G48" s="1" t="inlineStr"/>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
-      <c r="J48" s="1" t="inlineStr">
-        <is>
-          <t>L293: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paul Houde, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Denise Johnson, Ã©cole consolidÃ©e, Donnelly ..</t>
-        </is>
-      </c>
+      <c r="J48" s="1" t="inlineStr"/>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
@@ -3204,16 +2884,8 @@
       <c r="G49" s="1" t="inlineStr"/>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
-      <c r="J49" s="1" t="inlineStr">
-        <is>
-          <t>L296: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Juliette B Ã© rub Ã©, Beaumont</t>
-        </is>
-      </c>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ¼lberte Mencke, Ã©cole consolidÃ©e, Falher ...</t>
-        </is>
-      </c>
+      <c r="J49" s="1" t="inlineStr"/>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
@@ -3229,7 +2901,7 @@
       <c r="P49" s="1" t="inlineStr"/>
       <c r="Q49" s="1" t="inlineStr">
         <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jean-Louis Champagne, Ã©cole Thibeault ..</t>
+          <t>L53: punctuation artifact: repeated periods :: Jean-Louis Champagne, école Thibeault ..</t>
         </is>
       </c>
       <c r="R49" s="1" t="inlineStr"/>
@@ -3251,16 +2923,8 @@
       <c r="G50" s="1" t="inlineStr"/>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
-      <c r="J50" s="1" t="inlineStr">
-        <is>
-          <t>L327: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å�£</t>
-        </is>
-      </c>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L105: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© Martineau, Ã©cole consolidÃ©e, Falher ....</t>
-        </is>
-      </c>
+      <c r="J50" s="1" t="inlineStr"/>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
@@ -3276,7 +2940,7 @@
       <c r="P50" s="1" t="inlineStr"/>
       <c r="Q50" s="1" t="inlineStr">
         <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Georges Lajoie, ThÃ©rien ................</t>
+          <t>L54: punctuation artifact: repeated periods :: Georges Lajoie, Thérien ................</t>
         </is>
       </c>
       <c r="R50" s="1" t="inlineStr"/>
@@ -3298,16 +2962,8 @@
       <c r="G51" s="1" t="inlineStr"/>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
-      <c r="J51" s="1" t="inlineStr">
-        <is>
-          <t>L350: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: l Ã© e, Donnelly</t>
-        </is>
-      </c>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Jeannine Emard, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="J51" s="1" t="inlineStr"/>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
@@ -3345,16 +3001,8 @@
       <c r="G52" s="1" t="inlineStr"/>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
-      <c r="J52" s="1" t="inlineStr">
-        <is>
-          <t>L372: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Robert Dame, Ã©cole Grandin ..................</t>
-        </is>
-      </c>
+      <c r="J52" s="1" t="inlineStr"/>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
@@ -3392,16 +3040,8 @@
       <c r="G53" s="1" t="inlineStr"/>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
-      <c r="J53" s="1" t="inlineStr">
-        <is>
-          <t>L383: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Albert Laplante, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Denis Gallant, Ã©cole Grandin .........</t>
-        </is>
-      </c>
+      <c r="J53" s="1" t="inlineStr"/>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
@@ -3439,16 +3079,8 @@
       <c r="G54" s="1" t="inlineStr"/>
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
-      <c r="J54" s="1" t="inlineStr">
-        <is>
-          <t>L397: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Jeannine nier, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L115: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Bernard KÃ©roack, Ã©cole Grandin...............</t>
-        </is>
-      </c>
+      <c r="J54" s="1" t="inlineStr"/>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
@@ -3486,16 +3118,8 @@
       <c r="G55" s="1" t="inlineStr"/>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
-      <c r="J55" s="1" t="inlineStr">
-        <is>
-          <t>L407: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Jeanne Charlier, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L116: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marguerite Albinati, Ã©cole consolidÃ©e, Falher ...</t>
-        </is>
-      </c>
+      <c r="J55" s="1" t="inlineStr"/>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
@@ -3511,7 +3135,7 @@
       <c r="P55" s="1" t="inlineStr"/>
       <c r="Q55" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeannine Chalifoux, Ã©cole Thibeault .....</t>
+          <t>L59: punctuation artifact: repeated periods :: Jeannine Chalifoux, école Thibeault .....</t>
         </is>
       </c>
       <c r="R55" s="1" t="inlineStr"/>
@@ -3533,16 +3157,8 @@
       <c r="G56" s="1" t="inlineStr"/>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
-      <c r="J56" s="1" t="inlineStr">
-        <is>
-          <t>L427: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Colette Morin, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L117: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Maurice Riopel, Ã©cole Thibeault ..</t>
-        </is>
-      </c>
+      <c r="J56" s="1" t="inlineStr"/>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
@@ -3558,7 +3174,7 @@
       <c r="P56" s="1" t="inlineStr"/>
       <c r="Q56" s="1" t="inlineStr">
         <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Paul LabontÃ©. Ã©cole Thibeault .......</t>
+          <t>L61: punctuation artifact: repeated periods :: Paul Labonté. école Thibeault .......</t>
         </is>
       </c>
       <c r="R56" s="1" t="inlineStr"/>
@@ -3580,16 +3196,8 @@
       <c r="G57" s="1" t="inlineStr"/>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
-      <c r="J57" s="1" t="inlineStr">
-        <is>
-          <t>L429: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Georges Pilon, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L119: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Tanguay, Ã©cole consolidÃ©e, Donnelly ...</t>
-        </is>
-      </c>
+      <c r="J57" s="1" t="inlineStr"/>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
@@ -3605,7 +3213,7 @@
       <c r="P57" s="1" t="inlineStr"/>
       <c r="Q57" s="1" t="inlineStr">
         <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Guy Bachand, Ã©cole Thibeault ........</t>
+          <t>L62: punctuation artifact: repeated periods :: Guy Bachand, école Thibeault ........</t>
         </is>
       </c>
       <c r="R57" s="1" t="inlineStr"/>
@@ -3627,16 +3235,8 @@
       <c r="G58" s="1" t="inlineStr"/>
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
-      <c r="J58" s="1" t="inlineStr">
-        <is>
-          <t>L452: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: UldÃ©ric R Rochette, Tangente.</t>
-        </is>
-      </c>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L120: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roger DesfossÃ©s, Ã©cole consolidÃ©e, Falher ...</t>
-        </is>
-      </c>
+      <c r="J58" s="1" t="inlineStr"/>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
@@ -3652,7 +3252,7 @@
       <c r="P58" s="1" t="inlineStr"/>
       <c r="Q58" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: AdÃ¨le Legault, Bonnyville ...........</t>
+          <t>L63: punctuation artifact: repeated periods :: Adèle Legault, Bonnyville ...........</t>
         </is>
       </c>
       <c r="R58" s="1" t="inlineStr"/>
@@ -3674,16 +3274,8 @@
       <c r="G59" s="1" t="inlineStr"/>
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
-      <c r="J59" s="1" t="inlineStr">
-        <is>
-          <t>L454: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: Ir Ã¨ ne Lussier, Tangente</t>
-        </is>
-      </c>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L122: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Norman Courchesne, Ã©cole consolidÃ©e: Falher</t>
-        </is>
-      </c>
+      <c r="J59" s="1" t="inlineStr"/>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
@@ -3721,16 +3313,8 @@
       <c r="G60" s="1" t="inlineStr"/>
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
-      <c r="J60" s="1" t="inlineStr">
-        <is>
-          <t>L478: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: Ir Ã¨ ne Bruneau, ecole consolid Ã© e, Falher</t>
-        </is>
-      </c>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L123: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©o RÃ©millard, Legal ........................</t>
-        </is>
-      </c>
+      <c r="J60" s="1" t="inlineStr"/>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
@@ -3768,16 +3352,8 @@
       <c r="G61" s="1" t="inlineStr"/>
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
-      <c r="J61" s="1" t="inlineStr">
-        <is>
-          <t>L480: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Th Ã© rese Paquette, Bonnyville</t>
-        </is>
-      </c>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ©rard Aquin, Ã©cole Thibeault ...............</t>
-        </is>
-      </c>
+      <c r="J61" s="1" t="inlineStr"/>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
@@ -3793,7 +3369,7 @@
       <c r="P61" s="1" t="inlineStr"/>
       <c r="Q61" s="1" t="inlineStr">
         <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Gemma Girard, Ã©cole Grandin ...</t>
+          <t>L67: punctuation artifact: repeated periods :: Gemma Girard, école Grandin ...</t>
         </is>
       </c>
       <c r="R61" s="1" t="inlineStr"/>
@@ -3815,16 +3391,8 @@
       <c r="G62" s="1" t="inlineStr"/>
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
-      <c r="J62" s="1" t="inlineStr">
-        <is>
-          <t>L512: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Constance H Ã© bert, Legal</t>
-        </is>
-      </c>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L125: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Hermas Martin, ThÃ©rien ......................</t>
-        </is>
-      </c>
+      <c r="J62" s="1" t="inlineStr"/>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
@@ -3840,7 +3408,7 @@
       <c r="P62" s="1" t="inlineStr"/>
       <c r="Q62" s="1" t="inlineStr">
         <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© Picard, Ã©cole Grandin ...</t>
+          <t>L68: punctuation artifact: repeated periods :: André Picard, école Grandin ...</t>
         </is>
       </c>
       <c r="R62" s="1" t="inlineStr"/>
@@ -3862,16 +3430,8 @@
       <c r="G63" s="1" t="inlineStr"/>
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
-      <c r="J63" s="1" t="inlineStr">
-        <is>
-          <t>L520: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Rachel Labonte, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L130: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Claire Gratton, ThÃ©rien ...................-.....</t>
-        </is>
-      </c>
+      <c r="J63" s="1" t="inlineStr"/>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
@@ -3887,7 +3447,7 @@
       <c r="P63" s="1" t="inlineStr"/>
       <c r="Q63" s="1" t="inlineStr">
         <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©da Bonin, La Corey ........................</t>
+          <t>L69: punctuation artifact: repeated periods :: Léda Bonin, La Corey ........................</t>
         </is>
       </c>
       <c r="R63" s="1" t="inlineStr"/>
@@ -3909,16 +3469,8 @@
       <c r="G64" s="1" t="inlineStr"/>
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
-      <c r="J64" s="1" t="inlineStr">
-        <is>
-          <t>L522: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Patricia B Ã© land. ecole Thibeault</t>
-        </is>
-      </c>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L136: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Elizabeth Nadon, La Corey .................â€ž.....</t>
-        </is>
-      </c>
+      <c r="J64" s="1" t="inlineStr"/>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
@@ -3956,16 +3508,8 @@
       <c r="G65" s="1" t="inlineStr"/>
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
-      <c r="J65" s="1" t="inlineStr">
-        <is>
-          <t>L572: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ren Ã© Cote, ecole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L138: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rose-Anna Paquette, Ã©cole consolidÃ©e, Donnelly ..</t>
-        </is>
-      </c>
+      <c r="J65" s="1" t="inlineStr"/>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
@@ -4003,16 +3547,8 @@
       <c r="G66" s="1" t="inlineStr"/>
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
-      <c r="J66" s="1" t="inlineStr">
-        <is>
-          <t>L601: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: GÃ©rard Sauvageau. ecole consolidee, Falher .</t>
-        </is>
-      </c>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L140: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roland TieuliÃ©, Legal ...........................</t>
-        </is>
-      </c>
+      <c r="J66" s="1" t="inlineStr"/>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
@@ -4028,7 +3564,7 @@
       <c r="P66" s="1" t="inlineStr"/>
       <c r="Q66" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marie-Rose Garneau, Ã©cole Dunrobin ..........</t>
+          <t>L73: punctuation artifact: repeated periods :: Marie-Rose Garneau, école Dunrobin ..........</t>
         </is>
       </c>
       <c r="R66" s="1" t="inlineStr"/>
@@ -4050,16 +3586,8 @@
       <c r="G67" s="1" t="inlineStr"/>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
-      <c r="J67" s="1" t="inlineStr">
-        <is>
-          <t>L617: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Raymond Labrecque, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L159: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Carmela ChÃ©nard, Tangente ......................</t>
-        </is>
-      </c>
+      <c r="J67" s="1" t="inlineStr"/>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
@@ -4097,16 +3625,8 @@
       <c r="G68" s="1" t="inlineStr"/>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr"/>
-      <c r="J68" s="1" t="inlineStr">
-        <is>
-          <t>L626: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roland B Ã© rub Ã©. Beaumont</t>
-        </is>
-      </c>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L163: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: 63 AurÃ¨le Morneau, Bonnyville ...................</t>
-        </is>
-      </c>
+      <c r="J68" s="1" t="inlineStr"/>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
@@ -4144,16 +3664,8 @@
       <c r="G69" s="1" t="inlineStr"/>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr"/>
-      <c r="J69" s="1" t="inlineStr">
-        <is>
-          <t>L630: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Claudette B Ã© rub Ã©, Beaumont</t>
-        </is>
-      </c>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L165: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 62 Juliette Houle, Ã©cole Thibeault ..............</t>
-        </is>
-      </c>
+      <c r="J69" s="1" t="inlineStr"/>
+      <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
@@ -4169,7 +3681,7 @@
       <c r="P69" s="1" t="inlineStr"/>
       <c r="Q69" s="1" t="inlineStr">
         <is>
-          <t>L76: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: HÃ©lÃ¨ne Richard, Bonnyville ..................</t>
+          <t>L76: punctuation artifact: repeated periods :: Hélène Richard, Bonnyville ..................</t>
         </is>
       </c>
       <c r="R69" s="1" t="inlineStr"/>
@@ -4191,16 +3703,8 @@
       <c r="G70" s="1" t="inlineStr"/>
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr"/>
-      <c r="J70" s="1" t="inlineStr">
-        <is>
-          <t>L632: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: G Ã© rard Magnan, couvent Notre-Dame</t>
-        </is>
-      </c>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L171: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Maurice McNamara, Ã©cole Grandin .................</t>
-        </is>
-      </c>
+      <c r="J70" s="1" t="inlineStr"/>
+      <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
@@ -4238,16 +3742,8 @@
       <c r="G71" s="1" t="inlineStr"/>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr"/>
-      <c r="J71" s="1" t="inlineStr">
-        <is>
-          <t>L638: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Gemma Girard, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L173: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Elizabeth Meunier, Ã©cole Thibeault .............</t>
-        </is>
-      </c>
+      <c r="J71" s="1" t="inlineStr"/>
+      <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
@@ -4263,7 +3759,7 @@
       <c r="P71" s="1" t="inlineStr"/>
       <c r="Q71" s="1" t="inlineStr">
         <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoinette Casavant, Ã©cole Dunrobin .........</t>
+          <t>L78: punctuation artifact: repeated periods :: Antoinette Casavant, école Dunrobin .........</t>
         </is>
       </c>
       <c r="R71" s="1" t="inlineStr"/>
@@ -4285,16 +3781,8 @@
       <c r="G72" s="1" t="inlineStr"/>
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr"/>
-      <c r="J72" s="1" t="inlineStr">
-        <is>
-          <t>L643: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Andr Ã© Picard, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L178: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile VallÃ©e, Beaumont ....................</t>
-        </is>
-      </c>
+      <c r="J72" s="1" t="inlineStr"/>
+      <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
@@ -4310,7 +3798,7 @@
       <c r="P72" s="1" t="inlineStr"/>
       <c r="Q72" s="1" t="inlineStr">
         <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GisÃ¨le Aubin, Ã©cole consolidÃ©e, Falher ......</t>
+          <t>L80: punctuation artifact: repeated periods :: Gisèle Aubin, école consolidée, Falher ......</t>
         </is>
       </c>
       <c r="R72" s="1" t="inlineStr"/>
@@ -4332,16 +3820,8 @@
       <c r="G73" s="1" t="inlineStr"/>
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr"/>
-      <c r="J73" s="1" t="inlineStr">
-        <is>
-          <t>L645: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Fran Ã§ coise Turcotte, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L180: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: LÃ©andre Dansereau, Beaumont</t>
-        </is>
-      </c>
+      <c r="J73" s="1" t="inlineStr"/>
+      <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
@@ -4357,7 +3837,7 @@
       <c r="P73" s="1" t="inlineStr"/>
       <c r="Q73" s="1" t="inlineStr">
         <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Hector Letourneau, Ã©cole Grandin ............</t>
+          <t>L81: punctuation artifact: repeated periods :: Hector Letourneau, école Grandin ............</t>
         </is>
       </c>
       <c r="R73" s="1" t="inlineStr"/>
@@ -4379,16 +3859,8 @@
       <c r="G74" s="1" t="inlineStr"/>
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr"/>
-      <c r="J74" s="1" t="inlineStr">
-        <is>
-          <t>L648: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Leda Bonin, La Corey â€¦ .</t>
-        </is>
-      </c>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L182: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ©rald Royer, Beaumont .........................</t>
-        </is>
-      </c>
+      <c r="J74" s="1" t="inlineStr"/>
+      <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
@@ -4426,16 +3898,8 @@
       <c r="G75" s="1" t="inlineStr"/>
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr"/>
-      <c r="J75" s="1" t="inlineStr">
-        <is>
-          <t>L652: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ronald Patry, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L186: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 59 Laurier Rousseau, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J75" s="1" t="inlineStr"/>
+      <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
@@ -4473,16 +3937,8 @@
       <c r="G76" s="1" t="inlineStr"/>
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr"/>
-      <c r="J76" s="1" t="inlineStr">
-        <is>
-          <t>L675: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Marcel Arcand, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L194: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 57 Claude Proulx, Ã©cole consolidÃ©e, Falher .</t>
-        </is>
-      </c>
+      <c r="J76" s="1" t="inlineStr"/>
+      <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
@@ -4520,16 +3976,8 @@
       <c r="G77" s="1" t="inlineStr"/>
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr"/>
-      <c r="J77" s="1" t="inlineStr">
-        <is>
-          <t>L688: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Antoinette Casavant, Ã©cole Dunrobin . .</t>
-        </is>
-      </c>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L198: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Marcel LabontÃ©, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J77" s="1" t="inlineStr"/>
+      <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
@@ -4567,16 +4015,8 @@
       <c r="G78" s="1" t="inlineStr"/>
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr"/>
-      <c r="J78" s="1" t="inlineStr">
-        <is>
-          <t>L693: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Philippe Lemire, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L200: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Della BÃ©langer, Plamondon .......................</t>
-        </is>
-      </c>
+      <c r="J78" s="1" t="inlineStr"/>
+      <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
@@ -4614,16 +4054,8 @@
       <c r="G79" s="1" t="inlineStr"/>
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr"/>
-      <c r="J79" s="1" t="inlineStr">
-        <is>
-          <t>L728: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ad Ã© elard Seguin, Bonnyville</t>
-        </is>
-      </c>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L204: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Augustine Thibault, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="J79" s="1" t="inlineStr"/>
+      <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
@@ -4639,7 +4071,7 @@
       <c r="P79" s="1" t="inlineStr"/>
       <c r="Q79" s="1" t="inlineStr">
         <is>
-          <t>L89: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Mercier, Fort Kent ...................</t>
+          <t>L89: punctuation artifact: repeated periods :: Cécile Mercier, Fort Kent ...................</t>
         </is>
       </c>
       <c r="R79" s="1" t="inlineStr"/>
@@ -4661,16 +4093,8 @@
       <c r="G80" s="1" t="inlineStr"/>
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr"/>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>L733: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ren Ã© Bruneau, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>L212: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: ThÃ©rÃ¨se Courchesne, pensionnat de l'Assomption</t>
-        </is>
-      </c>
+      <c r="J80" s="1" t="inlineStr"/>
+      <c r="K80" s="1" t="inlineStr"/>
       <c r="L80" s="1" t="inlineStr"/>
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
@@ -4686,7 +4110,7 @@
       <c r="P80" s="1" t="inlineStr"/>
       <c r="Q80" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roger Dusseault, Ã©cole consolidÃ©e, Falher ...</t>
+          <t>L90: punctuation artifact: repeated periods :: Roger Dusseault, école consolidée, Falher ...</t>
         </is>
       </c>
       <c r="R80" s="1" t="inlineStr"/>
@@ -4708,16 +4132,8 @@
       <c r="G81" s="1" t="inlineStr"/>
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr"/>
-      <c r="J81" s="1" t="inlineStr">
-        <is>
-          <t>L736: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Eug Ã© nie Forcier, ecole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>L216: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: CÃ©cile BussiÃ¨re, pensionnat de l'Assomption ..........64</t>
-        </is>
-      </c>
+      <c r="J81" s="1" t="inlineStr"/>
+      <c r="K81" s="1" t="inlineStr"/>
       <c r="L81" s="1" t="inlineStr"/>
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
@@ -4755,16 +4171,8 @@
       <c r="G82" s="1" t="inlineStr"/>
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr"/>
-      <c r="J82" s="1" t="inlineStr">
-        <is>
-          <t>L752: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roger Dusseault, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K82" s="1" t="inlineStr">
-        <is>
-          <t>L222: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Paul Roy, Ã©cole consolidÃ©e, Donnelly .......</t>
-        </is>
-      </c>
+      <c r="J82" s="1" t="inlineStr"/>
+      <c r="K82" s="1" t="inlineStr"/>
       <c r="L82" s="1" t="inlineStr"/>
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
@@ -4802,16 +4210,8 @@
       <c r="G83" s="1" t="inlineStr"/>
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr"/>
-      <c r="J83" s="1" t="inlineStr">
-        <is>
-          <t>L755: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Robert B Ã© rub. Beaumont</t>
-        </is>
-      </c>
-      <c r="K83" s="1" t="inlineStr">
-        <is>
-          <t>L224: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Roy, Fort Kent ......................</t>
-        </is>
-      </c>
+      <c r="J83" s="1" t="inlineStr"/>
+      <c r="K83" s="1" t="inlineStr"/>
       <c r="L83" s="1" t="inlineStr"/>
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
@@ -4849,16 +4249,8 @@
       <c r="G84" s="1" t="inlineStr"/>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr"/>
-      <c r="J84" s="1" t="inlineStr">
-        <is>
-          <t>L760: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pierrette Lauzon, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K84" s="1" t="inlineStr">
-        <is>
-          <t>L228: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Joseph Girard, Ã©cole Grandin ...............</t>
-        </is>
-      </c>
+      <c r="J84" s="1" t="inlineStr"/>
+      <c r="K84" s="1" t="inlineStr"/>
       <c r="L84" s="1" t="inlineStr"/>
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
@@ -4874,7 +4266,7 @@
       <c r="P84" s="1" t="inlineStr"/>
       <c r="Q84" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoinette Brien, Ã©cole consolidÃ©e, Falher ..</t>
+          <t>L94: punctuation artifact: repeated periods :: Antoinette Brien, école consolidée, Falher ..</t>
         </is>
       </c>
       <c r="R84" s="1" t="inlineStr"/>
@@ -4896,16 +4288,8 @@
       <c r="G85" s="1" t="inlineStr"/>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr"/>
-      <c r="J85" s="1" t="inlineStr">
-        <is>
-          <t>L763: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Raymond Petrin, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K85" s="1" t="inlineStr">
-        <is>
-          <t>L234: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: AndrÃ© Fortier, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="J85" s="1" t="inlineStr"/>
+      <c r="K85" s="1" t="inlineStr"/>
       <c r="L85" s="1" t="inlineStr"/>
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
@@ -4921,7 +4305,7 @@
       <c r="P85" s="1" t="inlineStr"/>
       <c r="Q85" s="1" t="inlineStr">
         <is>
-          <t>L95: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roger Loiseau, Ã©cole consolidÃ©e, Falher .....</t>
+          <t>L95: punctuation artifact: repeated periods :: Roger Loiseau, école consolidée, Falher .....</t>
         </is>
       </c>
       <c r="R85" s="1" t="inlineStr"/>
@@ -4943,16 +4327,8 @@
       <c r="G86" s="1" t="inlineStr"/>
       <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr"/>
-      <c r="J86" s="1" t="inlineStr">
-        <is>
-          <t>L774: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: G Ã© rald Lapointe, Ã© cole consolid Ã© e, Donne</t>
-        </is>
-      </c>
-      <c r="K86" s="1" t="inlineStr">
-        <is>
-          <t>L238: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Raymond Roy, Ã©cole consolidÃ©e, Falher ................60</t>
-        </is>
-      </c>
+      <c r="J86" s="1" t="inlineStr"/>
+      <c r="K86" s="1" t="inlineStr"/>
       <c r="L86" s="1" t="inlineStr"/>
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
@@ -4990,16 +4366,8 @@
       <c r="G87" s="1" t="inlineStr"/>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr"/>
-      <c r="J87" s="1" t="inlineStr">
-        <is>
-          <t>L775: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roger Loiseau, Ã© ccle consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K87" s="1" t="inlineStr">
-        <is>
-          <t>L240: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Laurier Arcand, Ã©cole Grandin ........................60</t>
-        </is>
-      </c>
+      <c r="J87" s="1" t="inlineStr"/>
+      <c r="K87" s="1" t="inlineStr"/>
       <c r="L87" s="1" t="inlineStr"/>
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
@@ -5037,16 +4405,8 @@
       <c r="G88" s="1" t="inlineStr"/>
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr"/>
-      <c r="J88" s="1" t="inlineStr">
-        <is>
-          <t>L777: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: G Ã© rard-Meunier, cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K88" s="1" t="inlineStr">
-        <is>
-          <t>L242: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Pariseau, Ã©cole consolidÃ©e, Donnelly ..........</t>
-        </is>
-      </c>
+      <c r="J88" s="1" t="inlineStr"/>
+      <c r="K88" s="1" t="inlineStr"/>
       <c r="L88" s="1" t="inlineStr"/>
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
@@ -5084,16 +4444,8 @@
       <c r="G89" s="1" t="inlineStr"/>
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr"/>
-      <c r="J89" s="1" t="inlineStr">
-        <is>
-          <t>L790: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ren Ã© Maurier, Legal</t>
-        </is>
-      </c>
-      <c r="K89" s="1" t="inlineStr">
-        <is>
-          <t>L244: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT, U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeannine CÃ´tÃ©, Ã©cole consolidÃ©e, Donnelly ............</t>
-        </is>
-      </c>
+      <c r="J89" s="1" t="inlineStr"/>
+      <c r="K89" s="1" t="inlineStr"/>
       <c r="L89" s="1" t="inlineStr"/>
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
@@ -5131,16 +4483,8 @@
       <c r="G90" s="1" t="inlineStr"/>
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr"/>
-      <c r="J90" s="1" t="inlineStr">
-        <is>
-          <t>L793: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Billy Dubois, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K90" s="1" t="inlineStr">
-        <is>
-          <t>L250: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 86 Denise Maure, Ã©cole consolidÃ©e, Falher .............</t>
-        </is>
-      </c>
+      <c r="J90" s="1" t="inlineStr"/>
+      <c r="K90" s="1" t="inlineStr"/>
       <c r="L90" s="1" t="inlineStr"/>
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
@@ -5156,7 +4500,7 @@
       <c r="P90" s="1" t="inlineStr"/>
       <c r="Q90" s="1" t="inlineStr">
         <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Garneau, Ã©cole Dunrobin ..............</t>
+          <t>L100: punctuation artifact: repeated periods :: Cécile Garneau, école Dunrobin ..............</t>
         </is>
       </c>
       <c r="R90" s="1" t="inlineStr"/>
@@ -5178,16 +4522,8 @@
       <c r="G91" s="1" t="inlineStr"/>
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr"/>
-      <c r="J91" s="1" t="inlineStr">
-        <is>
-          <t>L805: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Andr Ã© La Brie, Fort Kent</t>
-        </is>
-      </c>
-      <c r="K91" s="1" t="inlineStr">
-        <is>
-          <t>L264: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 85 Yolande Garneau, Ã©cole Granlin .....................</t>
-        </is>
-      </c>
+      <c r="J91" s="1" t="inlineStr"/>
+      <c r="K91" s="1" t="inlineStr"/>
       <c r="L91" s="1" t="inlineStr"/>
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
@@ -5203,7 +4539,7 @@
       <c r="P91" s="1" t="inlineStr"/>
       <c r="Q91" s="1" t="inlineStr">
         <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rita Laplante, Ã©cole Dunrobin ...............</t>
+          <t>L101: punctuation artifact: repeated periods :: Rita Laplante, école Dunrobin ...............</t>
         </is>
       </c>
       <c r="R91" s="1" t="inlineStr"/>
@@ -5225,16 +4561,8 @@
       <c r="G92" s="1" t="inlineStr"/>
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr"/>
-      <c r="J92" s="1" t="inlineStr">
-        <is>
-          <t>L806: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Rita Lapiante, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K92" s="1" t="inlineStr">
-        <is>
-          <t>L268: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ©rard Levasseur, Ã©cole Grandin ......................</t>
-        </is>
-      </c>
+      <c r="J92" s="1" t="inlineStr"/>
+      <c r="K92" s="1" t="inlineStr"/>
       <c r="L92" s="1" t="inlineStr"/>
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
@@ -5250,7 +4578,7 @@
       <c r="P92" s="1" t="inlineStr"/>
       <c r="Q92" s="1" t="inlineStr">
         <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©ona Verreault, Tangente ...................</t>
+          <t>L102: punctuation artifact: repeated periods :: Léona Verreault, Tangente ...................</t>
         </is>
       </c>
       <c r="R92" s="1" t="inlineStr"/>
@@ -5272,16 +4600,8 @@
       <c r="G93" s="1" t="inlineStr"/>
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr"/>
-      <c r="J93" s="1" t="inlineStr">
-        <is>
-          <t>L814: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Denise Johnson, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K93" s="1" t="inlineStr">
-        <is>
-          <t>L270: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Yvette Normand, ThÃ©rien ..............................</t>
-        </is>
-      </c>
+      <c r="J93" s="1" t="inlineStr"/>
+      <c r="K93" s="1" t="inlineStr"/>
       <c r="L93" s="1" t="inlineStr"/>
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
@@ -5297,7 +4617,7 @@
       <c r="P93" s="1" t="inlineStr"/>
       <c r="Q93" s="1" t="inlineStr">
         <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Denise Johnson, Ã©cole consolidÃ©e, Donnelly ..</t>
+          <t>L103: punctuation artifact: repeated periods :: Denise Johnson, école consolidée, Donnelly ..</t>
         </is>
       </c>
       <c r="R93" s="1" t="inlineStr"/>
@@ -5319,16 +4639,8 @@
       <c r="G94" s="1" t="inlineStr"/>
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr"/>
-      <c r="J94" s="1" t="inlineStr">
-        <is>
-          <t>L821: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Giberte Mencke, Ã©cole consolidee, Falher . .</t>
-        </is>
-      </c>
-      <c r="K94" s="1" t="inlineStr">
-        <is>
-          <t>L272: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Raymond Sylvestre, Ã©cole Thibeault ...................</t>
-        </is>
-      </c>
+      <c r="J94" s="1" t="inlineStr"/>
+      <c r="K94" s="1" t="inlineStr"/>
       <c r="L94" s="1" t="inlineStr"/>
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
@@ -5344,7 +4656,7 @@
       <c r="P94" s="1" t="inlineStr"/>
       <c r="Q94" s="1" t="inlineStr">
         <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ¼lberte Mencke, Ã©cole consolidÃ©e, Falher ...</t>
+          <t>L104: punctuation artifact: repeated periods :: Gülberte Mencke, école consolidée, Falher ...</t>
         </is>
       </c>
       <c r="R94" s="1" t="inlineStr"/>
@@ -5366,16 +4678,8 @@
       <c r="G95" s="1" t="inlineStr"/>
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr"/>
-      <c r="J95" s="1" t="inlineStr">
-        <is>
-          <t>L823: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: C Ã© cile Isabel, ecole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K95" s="1" t="inlineStr">
-        <is>
-          <t>L274: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 85 CÃ©cile Doucet. Tangente ............................</t>
-        </is>
-      </c>
+      <c r="J95" s="1" t="inlineStr"/>
+      <c r="K95" s="1" t="inlineStr"/>
       <c r="L95" s="1" t="inlineStr"/>
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
@@ -5391,7 +4695,7 @@
       <c r="P95" s="1" t="inlineStr"/>
       <c r="Q95" s="1" t="inlineStr">
         <is>
-          <t>L105: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© Martineau, Ã©cole consolidÃ©e, Falher ....</t>
+          <t>L105: punctuation artifact: repeated periods :: André Martineau, école consolidée, Falher ....</t>
         </is>
       </c>
       <c r="R95" s="1" t="inlineStr"/>
@@ -5413,16 +4717,8 @@
       <c r="G96" s="1" t="inlineStr"/>
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr"/>
-      <c r="J96" s="1" t="inlineStr">
-        <is>
-          <t>L826: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Andr Ã© Martineau, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K96" s="1" t="inlineStr">
-        <is>
-          <t>L282: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Rodrigue HÃ©bert. Saint-Vincent 79</t>
-        </is>
-      </c>
+      <c r="J96" s="1" t="inlineStr"/>
+      <c r="K96" s="1" t="inlineStr"/>
       <c r="L96" s="1" t="inlineStr"/>
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
@@ -5438,7 +4734,7 @@
       <c r="P96" s="1" t="inlineStr"/>
       <c r="Q96" s="1" t="inlineStr">
         <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Robert Dame, Ã©cole Grandin ..................</t>
+          <t>L107: punctuation artifact: repeated periods :: Robert Dame, école Grandin ..................</t>
         </is>
       </c>
       <c r="R96" s="1" t="inlineStr"/>
@@ -5460,16 +4756,8 @@
       <c r="G97" s="1" t="inlineStr"/>
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr"/>
-      <c r="J97" s="1" t="inlineStr">
-        <is>
-          <t>L828: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: C Ã© eine Coulombe, ecole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K97" s="1" t="inlineStr">
-        <is>
-          <t>L284: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Suzanne VallÃ©e, Bonnyville .....................79</t>
-        </is>
-      </c>
+      <c r="J97" s="1" t="inlineStr"/>
+      <c r="K97" s="1" t="inlineStr"/>
       <c r="L97" s="1" t="inlineStr"/>
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
@@ -5485,7 +4773,7 @@
       <c r="P97" s="1" t="inlineStr"/>
       <c r="Q97" s="1" t="inlineStr">
         <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Denis Gallant, Ã©cole Grandin .........</t>
+          <t>L109: punctuation artifact: repeated periods :: Denis Gallant, école Grandin .........</t>
         </is>
       </c>
       <c r="R97" s="1" t="inlineStr"/>
@@ -5507,16 +4795,8 @@
       <c r="G98" s="1" t="inlineStr"/>
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr"/>
-      <c r="J98" s="1" t="inlineStr">
-        <is>
-          <t>L830: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ren Ã© Fortin, Tangente</t>
-        </is>
-      </c>
-      <c r="K98" s="1" t="inlineStr">
-        <is>
-          <t>L286: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Antoinette BÃ©dard, Tangente ....................79</t>
-        </is>
-      </c>
+      <c r="J98" s="1" t="inlineStr"/>
+      <c r="K98" s="1" t="inlineStr"/>
       <c r="L98" s="1" t="inlineStr"/>
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
@@ -5554,16 +4834,8 @@
       <c r="G99" s="1" t="inlineStr"/>
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr"/>
-      <c r="J99" s="1" t="inlineStr">
-        <is>
-          <t>L831: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Jeannine Emard, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K99" s="1" t="inlineStr">
-        <is>
-          <t>L288: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paul-AndrÃ© Cloutier, Ã©cole consolidÃ©e, Donnelly 79</t>
-        </is>
-      </c>
+      <c r="J99" s="1" t="inlineStr"/>
+      <c r="K99" s="1" t="inlineStr"/>
       <c r="L99" s="1" t="inlineStr"/>
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
@@ -5601,16 +4873,8 @@
       <c r="G100" s="1" t="inlineStr"/>
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr"/>
-      <c r="J100" s="1" t="inlineStr">
-        <is>
-          <t>L840: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Denis Gallant, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K100" s="1" t="inlineStr">
-        <is>
-          <t>L290: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: LÃ©ona Saint-Jean, Legal ........................78</t>
-        </is>
-      </c>
+      <c r="J100" s="1" t="inlineStr"/>
+      <c r="K100" s="1" t="inlineStr"/>
       <c r="L100" s="1" t="inlineStr"/>
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
@@ -5648,16 +4912,8 @@
       <c r="G101" s="1" t="inlineStr"/>
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr"/>
-      <c r="J101" s="1" t="inlineStr">
-        <is>
-          <t>L849: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Michel Voyer, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K101" s="1" t="inlineStr">
-        <is>
-          <t>L292: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Constance HÃ©bert, Legal ........................78</t>
-        </is>
-      </c>
+      <c r="J101" s="1" t="inlineStr"/>
+      <c r="K101" s="1" t="inlineStr"/>
       <c r="L101" s="1" t="inlineStr"/>
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
@@ -5695,16 +4951,8 @@
       <c r="G102" s="1" t="inlineStr"/>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr"/>
-      <c r="J102" s="1" t="inlineStr">
-        <is>
-          <t>L866: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Bernard roack, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K102" s="1" t="inlineStr">
-        <is>
-          <t>L294: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rollande Boulet, Ã©cole consolidÃ©e, Donnelly ..</t>
-        </is>
-      </c>
+      <c r="J102" s="1" t="inlineStr"/>
+      <c r="K102" s="1" t="inlineStr"/>
       <c r="L102" s="1" t="inlineStr"/>
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
@@ -5720,7 +4968,7 @@
       <c r="P102" s="1" t="inlineStr"/>
       <c r="Q102" s="1" t="inlineStr">
         <is>
-          <t>L115: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Bernard KÃ©roack, Ã©cole Grandin...............</t>
+          <t>L115: punctuation artifact: repeated periods :: Bernard Kéroack, école Grandin...............</t>
         </is>
       </c>
       <c r="R102" s="1" t="inlineStr"/>
@@ -5742,16 +4990,8 @@
       <c r="G103" s="1" t="inlineStr"/>
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr"/>
-      <c r="J103" s="1" t="inlineStr">
-        <is>
-          <t>L868: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Madeleine G Ã© linas, pensionnat de I'Assomption</t>
-        </is>
-      </c>
-      <c r="K103" s="1" t="inlineStr">
-        <is>
-          <t>L296: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: RÃ©ginald Lussier, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="J103" s="1" t="inlineStr"/>
+      <c r="K103" s="1" t="inlineStr"/>
       <c r="L103" s="1" t="inlineStr"/>
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
@@ -5767,7 +5007,7 @@
       <c r="P103" s="1" t="inlineStr"/>
       <c r="Q103" s="1" t="inlineStr">
         <is>
-          <t>L116: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marguerite Albinati, Ã©cole consolidÃ©e, Falher ...</t>
+          <t>L116: punctuation artifact: repeated periods :: Marguerite Albinati, école consolidée, Falher ...</t>
         </is>
       </c>
       <c r="R103" s="1" t="inlineStr"/>
@@ -5789,16 +5029,8 @@
       <c r="G104" s="1" t="inlineStr"/>
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr"/>
-      <c r="J104" s="1" t="inlineStr">
-        <is>
-          <t>L870: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paul Boulet, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K104" s="1" t="inlineStr">
-        <is>
-          <t>L298: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: Annette LaverdiÃ¨re, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="J104" s="1" t="inlineStr"/>
+      <c r="K104" s="1" t="inlineStr"/>
       <c r="L104" s="1" t="inlineStr"/>
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr">
@@ -5814,7 +5046,7 @@
       <c r="P104" s="1" t="inlineStr"/>
       <c r="Q104" s="1" t="inlineStr">
         <is>
-          <t>L117: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Maurice Riopel, Ã©cole Thibeault ..</t>
+          <t>L117: punctuation artifact: repeated periods :: Maurice Riopel, école Thibeault ..</t>
         </is>
       </c>
       <c r="R104" s="1" t="inlineStr"/>
@@ -5836,16 +5068,8 @@
       <c r="G105" s="1" t="inlineStr"/>
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr"/>
-      <c r="J105" s="1" t="inlineStr">
-        <is>
-          <t>L875: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Denise Plaquin, Th Ã© rien</t>
-        </is>
-      </c>
-      <c r="K105" s="1" t="inlineStr">
-        <is>
-          <t>L300: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rachel LabontÃ©, Ã©cole Thibeault ...........</t>
-        </is>
-      </c>
+      <c r="J105" s="1" t="inlineStr"/>
+      <c r="K105" s="1" t="inlineStr"/>
       <c r="L105" s="1" t="inlineStr"/>
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr">
@@ -5861,7 +5085,7 @@
       <c r="P105" s="1" t="inlineStr"/>
       <c r="Q105" s="1" t="inlineStr">
         <is>
-          <t>L119: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Tanguay, Ã©cole consolidÃ©e, Donnelly ...</t>
+          <t>L119: punctuation artifact: repeated periods :: Thérèse Tanguay, école consolidée, Donnelly ...</t>
         </is>
       </c>
       <c r="R105" s="1" t="inlineStr"/>
@@ -5883,16 +5107,8 @@
       <c r="G106" s="1" t="inlineStr"/>
       <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr"/>
-      <c r="J106" s="1" t="inlineStr">
-        <is>
-          <t>L880: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Th Ã© rese Tanguay, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K106" s="1" t="inlineStr">
-        <is>
-          <t>L302: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Patricia BÃ©land. Ã©cole Thibeault ...........</t>
-        </is>
-      </c>
+      <c r="J106" s="1" t="inlineStr"/>
+      <c r="K106" s="1" t="inlineStr"/>
       <c r="L106" s="1" t="inlineStr"/>
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr">
@@ -5908,7 +5124,7 @@
       <c r="P106" s="1" t="inlineStr"/>
       <c r="Q106" s="1" t="inlineStr">
         <is>
-          <t>L120: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roger DesfossÃ©s, Ã©cole consolidÃ©e, Falher ...</t>
+          <t>L120: punctuation artifact: repeated periods :: Roger Desfossés, école consolidée, Falher ...</t>
         </is>
       </c>
       <c r="R106" s="1" t="inlineStr"/>
@@ -5930,16 +5146,8 @@
       <c r="G107" s="1" t="inlineStr"/>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr"/>
-      <c r="J107" s="1" t="inlineStr">
-        <is>
-          <t>L882: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lorraine B Ã© rub. Beaumont</t>
-        </is>
-      </c>
-      <c r="K107" s="1" t="inlineStr">
-        <is>
-          <t>L306: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©onard LabontÃ©, Ã©cole Thibeault .........</t>
-        </is>
-      </c>
+      <c r="J107" s="1" t="inlineStr"/>
+      <c r="K107" s="1" t="inlineStr"/>
       <c r="L107" s="1" t="inlineStr"/>
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr">
@@ -5955,7 +5163,7 @@
       <c r="P107" s="1" t="inlineStr"/>
       <c r="Q107" s="1" t="inlineStr">
         <is>
-          <t>L123: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©o RÃ©millard, Legal ........................</t>
+          <t>L123: punctuation artifact: repeated periods :: Léo Rémillard, Legal ........................</t>
         </is>
       </c>
       <c r="R107" s="1" t="inlineStr"/>
@@ -5977,16 +5185,8 @@
       <c r="G108" s="1" t="inlineStr"/>
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr"/>
-      <c r="J108" s="1" t="inlineStr">
-        <is>
-          <t>L884: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Claude B Ã© rub, Beaumont</t>
-        </is>
-      </c>
-      <c r="K108" s="1" t="inlineStr">
-        <is>
-          <t>L314: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: IrÃ¨ne Caouette, Bonnyville ................</t>
-        </is>
-      </c>
+      <c r="J108" s="1" t="inlineStr"/>
+      <c r="K108" s="1" t="inlineStr"/>
       <c r="L108" s="1" t="inlineStr"/>
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr">
@@ -6002,7 +5202,7 @@
       <c r="P108" s="1" t="inlineStr"/>
       <c r="Q108" s="1" t="inlineStr">
         <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ©rard Aquin, Ã©cole Thibeault ...............</t>
+          <t>L124: punctuation artifact: repeated periods :: Gérard Aquin, école Thibeault ...............</t>
         </is>
       </c>
       <c r="R108" s="1" t="inlineStr"/>
@@ -6024,21 +5224,13 @@
       <c r="G109" s="1" t="inlineStr"/>
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr"/>
-      <c r="J109" s="1" t="inlineStr">
-        <is>
-          <t>L885: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roger Desfoss, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K109" s="1" t="inlineStr">
-        <is>
-          <t>L316: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Sylvia Yakimchuk, ThÃ©rien Village ........</t>
-        </is>
-      </c>
+      <c r="J109" s="1" t="inlineStr"/>
+      <c r="K109" s="1" t="inlineStr"/>
       <c r="L109" s="1" t="inlineStr"/>
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr">
         <is>
-          <t>L210: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L210: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O109" s="1" t="inlineStr">
@@ -6049,7 +5241,7 @@
       <c r="P109" s="1" t="inlineStr"/>
       <c r="Q109" s="1" t="inlineStr">
         <is>
-          <t>L125: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Hermas Martin, ThÃ©rien ......................</t>
+          <t>L125: punctuation artifact: repeated periods :: Hermas Martin, Thérien ......................</t>
         </is>
       </c>
       <c r="R109" s="1" t="inlineStr"/>
@@ -6071,21 +5263,13 @@
       <c r="G110" s="1" t="inlineStr"/>
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr"/>
-      <c r="J110" s="1" t="inlineStr">
-        <is>
-          <t>L887: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Alberta Labonte, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K110" s="1" t="inlineStr">
-        <is>
-          <t>L322: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lucille MahÃ©, Legal .......</t>
-        </is>
-      </c>
+      <c r="J110" s="1" t="inlineStr"/>
+      <c r="K110" s="1" t="inlineStr"/>
       <c r="L110" s="1" t="inlineStr"/>
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr">
         <is>
-          <t>L211: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L211: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O110" s="1" t="inlineStr">
@@ -6118,16 +5302,8 @@
       <c r="G111" s="1" t="inlineStr"/>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr"/>
-      <c r="J111" s="1" t="inlineStr">
-        <is>
-          <t>L889: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: H Ã© Ã©lÃ¨ne Chouinard, La Corey</t>
-        </is>
-      </c>
-      <c r="K111" s="1" t="inlineStr">
-        <is>
-          <t>L324: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: FranÃ§ois Blackburn, Ã©cole Grandin ........</t>
-        </is>
-      </c>
+      <c r="J111" s="1" t="inlineStr"/>
+      <c r="K111" s="1" t="inlineStr"/>
       <c r="L111" s="1" t="inlineStr"/>
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr">
@@ -6165,16 +5341,8 @@
       <c r="G112" s="1" t="inlineStr"/>
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr"/>
-      <c r="J112" s="1" t="inlineStr">
-        <is>
-          <t>L890: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Norman Courchesne, Ã© cole consolidee; Falher</t>
-        </is>
-      </c>
-      <c r="K112" s="1" t="inlineStr">
-        <is>
-          <t>L330: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): eThibeault (odd internal casing) :: Lorraine Tellier, Ã©col eThibeault .........</t>
-        </is>
-      </c>
+      <c r="J112" s="1" t="inlineStr"/>
+      <c r="K112" s="1" t="inlineStr"/>
       <c r="L112" s="1" t="inlineStr"/>
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr">
@@ -6212,16 +5380,8 @@
       <c r="G113" s="1" t="inlineStr"/>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr"/>
-      <c r="J113" s="1" t="inlineStr">
-        <is>
-          <t>L892: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Fleurette Rousseau, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K113" s="1" t="inlineStr">
-        <is>
-          <t>L340: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Portelance. Tangente ..............</t>
-        </is>
-      </c>
+      <c r="J113" s="1" t="inlineStr"/>
+      <c r="K113" s="1" t="inlineStr"/>
       <c r="L113" s="1" t="inlineStr"/>
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr">
@@ -6237,7 +5397,7 @@
       <c r="P113" s="1" t="inlineStr"/>
       <c r="Q113" s="1" t="inlineStr">
         <is>
-          <t>L130: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Claire Gratton, ThÃ©rien ...................-.....</t>
+          <t>L130: punctuation artifact: repeated periods :: Claire Gratton, Thérien ...................-.....</t>
         </is>
       </c>
       <c r="R113" s="1" t="inlineStr"/>
@@ -6259,16 +5419,8 @@
       <c r="G114" s="1" t="inlineStr"/>
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr"/>
-      <c r="J114" s="1" t="inlineStr">
-        <is>
-          <t>L897: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: L Ã© o R Ã© millard, Legal</t>
-        </is>
-      </c>
-      <c r="K114" s="1" t="inlineStr">
-        <is>
-          <t>L342: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pierre Lacroix, Ã©cole consolidÃ©e, Donnelly .</t>
-        </is>
-      </c>
+      <c r="J114" s="1" t="inlineStr"/>
+      <c r="K114" s="1" t="inlineStr"/>
       <c r="L114" s="1" t="inlineStr"/>
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr">
@@ -6306,16 +5458,8 @@
       <c r="G115" s="1" t="inlineStr"/>
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr"/>
-      <c r="J115" s="1" t="inlineStr">
-        <is>
-          <t>L900: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: G Ã© rard Aquin, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K115" s="1" t="inlineStr">
-        <is>
-          <t>L346: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: |Normand SÃ©guin, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="J115" s="1" t="inlineStr"/>
+      <c r="K115" s="1" t="inlineStr"/>
       <c r="L115" s="1" t="inlineStr"/>
       <c r="M115" s="1" t="inlineStr"/>
       <c r="N115" s="1" t="inlineStr">
@@ -6353,16 +5497,8 @@
       <c r="G116" s="1" t="inlineStr"/>
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr"/>
-      <c r="J116" s="1" t="inlineStr">
-        <is>
-          <t>L923: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Etiennette S Ã© guin, Bonnyville</t>
-        </is>
-      </c>
-      <c r="K116" s="1" t="inlineStr">
-        <is>
-          <t>L350: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marielle BÃ©land, Bonnyville ................</t>
-        </is>
-      </c>
+      <c r="J116" s="1" t="inlineStr"/>
+      <c r="K116" s="1" t="inlineStr"/>
       <c r="L116" s="1" t="inlineStr"/>
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr">
@@ -6400,16 +5536,8 @@
       <c r="G117" s="1" t="inlineStr"/>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr"/>
-      <c r="J117" s="1" t="inlineStr">
-        <is>
-          <t>L938: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: L Ã© vis Chiasson, Sainte-Lina</t>
-        </is>
-      </c>
-      <c r="K117" s="1" t="inlineStr">
-        <is>
-          <t>L352: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roger Thibault, Ã©cole consolidÃ©e, Donnelly ...</t>
-        </is>
-      </c>
+      <c r="J117" s="1" t="inlineStr"/>
+      <c r="K117" s="1" t="inlineStr"/>
       <c r="L117" s="1" t="inlineStr"/>
       <c r="M117" s="1" t="inlineStr"/>
       <c r="N117" s="1" t="inlineStr">
@@ -6425,7 +5553,7 @@
       <c r="P117" s="1" t="inlineStr"/>
       <c r="Q117" s="1" t="inlineStr">
         <is>
-          <t>L136: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Elizabeth Nadon, La Corey .................â€ž.....</t>
+          <t>L136: punctuation artifact: repeated periods :: Elizabeth Nadon, La Corey .................„.....</t>
         </is>
       </c>
       <c r="R117" s="1" t="inlineStr"/>
@@ -6447,16 +5575,8 @@
       <c r="G118" s="1" t="inlineStr"/>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr"/>
-      <c r="J118" s="1" t="inlineStr">
-        <is>
-          <t>L943: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Carole Lefebvre, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K118" s="1" t="inlineStr">
-        <is>
-          <t>L354: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00B4 ACUTE ACCENT :: RenÃ© CÃ´tÃ©, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="J118" s="1" t="inlineStr"/>
+      <c r="K118" s="1" t="inlineStr"/>
       <c r="L118" s="1" t="inlineStr"/>
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr">
@@ -6472,7 +5592,7 @@
       <c r="P118" s="1" t="inlineStr"/>
       <c r="Q118" s="1" t="inlineStr">
         <is>
-          <t>L138: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rose-Anna Paquette, Ã©cole consolidÃ©e, Donnelly ..</t>
+          <t>L138: punctuation artifact: repeated periods :: Rose-Anna Paquette, école consolidée, Donnelly ..</t>
         </is>
       </c>
       <c r="R118" s="1" t="inlineStr"/>
@@ -6494,16 +5614,8 @@
       <c r="G119" s="1" t="inlineStr"/>
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr"/>
-      <c r="J119" s="1" t="inlineStr">
-        <is>
-          <t>L962: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: d Ã© e, Donnelly</t>
-        </is>
-      </c>
-      <c r="K119" s="1" t="inlineStr">
-        <is>
-          <t>L357: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ! Germaine Ethier, Ã©cole Thibault ..........</t>
-        </is>
-      </c>
+      <c r="J119" s="1" t="inlineStr"/>
+      <c r="K119" s="1" t="inlineStr"/>
       <c r="L119" s="1" t="inlineStr"/>
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr">
@@ -6541,16 +5653,8 @@
       <c r="G120" s="1" t="inlineStr"/>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr"/>
-      <c r="J120" s="1" t="inlineStr">
-        <is>
-          <t>L974: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: id Ã© e, Falher</t>
-        </is>
-      </c>
-      <c r="K120" s="1" t="inlineStr">
-        <is>
-          <t>L359: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: |Raymond Ouellette. ThÃ©rien Village........</t>
-        </is>
-      </c>
+      <c r="J120" s="1" t="inlineStr"/>
+      <c r="K120" s="1" t="inlineStr"/>
       <c r="L120" s="1" t="inlineStr"/>
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr">
@@ -6566,7 +5670,7 @@
       <c r="P120" s="1" t="inlineStr"/>
       <c r="Q120" s="1" t="inlineStr">
         <is>
-          <t>L140: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roland TieuliÃ©, Legal ...........................</t>
+          <t>L140: punctuation artifact: repeated periods :: Roland Tieulié, Legal ...........................</t>
         </is>
       </c>
       <c r="R120" s="1" t="inlineStr"/>
@@ -6588,16 +5692,8 @@
       <c r="G121" s="1" t="inlineStr"/>
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr"/>
-      <c r="J121" s="1" t="inlineStr">
-        <is>
-          <t>L979: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: id Ã© e, Donnelly</t>
-        </is>
-      </c>
-      <c r="K121" s="1" t="inlineStr">
-        <is>
-          <t>L363: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: | Madeleine Brissette, Ã©cole Grandin........</t>
-        </is>
-      </c>
+      <c r="J121" s="1" t="inlineStr"/>
+      <c r="K121" s="1" t="inlineStr"/>
       <c r="L121" s="1" t="inlineStr"/>
       <c r="M121" s="1" t="inlineStr"/>
       <c r="N121" s="1" t="inlineStr">
@@ -6635,16 +5731,8 @@
       <c r="G122" s="1" t="inlineStr"/>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr"/>
-      <c r="J122" s="1" t="inlineStr">
-        <is>
-          <t>L997: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: l Ã© e, Donnelly</t>
-        </is>
-      </c>
-      <c r="K122" s="1" t="inlineStr">
-        <is>
-          <t>L369: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Maurice Despins, Ã©cole Dunrobin. Vimy</t>
-        </is>
-      </c>
+      <c r="J122" s="1" t="inlineStr"/>
+      <c r="K122" s="1" t="inlineStr"/>
       <c r="L122" s="1" t="inlineStr"/>
       <c r="M122" s="1" t="inlineStr"/>
       <c r="N122" s="1" t="inlineStr">
@@ -6682,16 +5770,8 @@
       <c r="G123" s="1" t="inlineStr"/>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr"/>
-      <c r="J123" s="1" t="inlineStr">
-        <is>
-          <t>L1028: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Noel Ch Ã© nard, Tangente</t>
-        </is>
-      </c>
-      <c r="K123" s="1" t="inlineStr">
-        <is>
-          <t>L371: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Aurore Martel, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J123" s="1" t="inlineStr"/>
+      <c r="K123" s="1" t="inlineStr"/>
       <c r="L123" s="1" t="inlineStr"/>
       <c r="M123" s="1" t="inlineStr"/>
       <c r="N123" s="1" t="inlineStr">
@@ -6729,16 +5809,8 @@
       <c r="G124" s="1" t="inlineStr"/>
       <c r="H124" s="1" t="inlineStr"/>
       <c r="I124" s="1" t="inlineStr"/>
-      <c r="J124" s="1" t="inlineStr">
-        <is>
-          <t>L1040: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Andr Ã© Beaupr Ã©, Bonnyville</t>
-        </is>
-      </c>
-      <c r="K124" s="1" t="inlineStr">
-        <is>
-          <t>L452: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Albert Laplante, Ã©cole Dunrobin ............</t>
-        </is>
-      </c>
+      <c r="J124" s="1" t="inlineStr"/>
+      <c r="K124" s="1" t="inlineStr"/>
       <c r="L124" s="1" t="inlineStr"/>
       <c r="M124" s="1" t="inlineStr"/>
       <c r="N124" s="1" t="inlineStr">
@@ -6776,16 +5848,8 @@
       <c r="G125" s="1" t="inlineStr"/>
       <c r="H125" s="1" t="inlineStr"/>
       <c r="I125" s="1" t="inlineStr"/>
-      <c r="J125" s="1" t="inlineStr">
-        <is>
-          <t>L1057: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Claude Charrois, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K125" s="1" t="inlineStr">
-        <is>
-          <t>L454: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Yvette Deslauriers, Ã©cole Thibeault.</t>
-        </is>
-      </c>
+      <c r="J125" s="1" t="inlineStr"/>
+      <c r="K125" s="1" t="inlineStr"/>
       <c r="L125" s="1" t="inlineStr"/>
       <c r="M125" s="1" t="inlineStr"/>
       <c r="N125" s="1" t="inlineStr">
@@ -6801,7 +5865,7 @@
       <c r="P125" s="1" t="inlineStr"/>
       <c r="Q125" s="1" t="inlineStr">
         <is>
-          <t>L159: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Carmela ChÃ©nard, Tangente ......................</t>
+          <t>L159: punctuation artifact: repeated periods :: Carmela Chénard, Tangente ......................</t>
         </is>
       </c>
       <c r="R125" s="1" t="inlineStr"/>
@@ -6823,16 +5887,8 @@
       <c r="G126" s="1" t="inlineStr"/>
       <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr"/>
-      <c r="J126" s="1" t="inlineStr">
-        <is>
-          <t>L1077: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Gr Ã© goire Ouellet, La Corey</t>
-        </is>
-      </c>
-      <c r="K126" s="1" t="inlineStr">
-        <is>
-          <t>L458: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Laurier Coulombe, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="J126" s="1" t="inlineStr"/>
+      <c r="K126" s="1" t="inlineStr"/>
       <c r="L126" s="1" t="inlineStr"/>
       <c r="M126" s="1" t="inlineStr"/>
       <c r="N126" s="1" t="inlineStr">
@@ -6848,7 +5904,7 @@
       <c r="P126" s="1" t="inlineStr"/>
       <c r="Q126" s="1" t="inlineStr">
         <is>
-          <t>L163: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: 63 AurÃ¨le Morneau, Bonnyville ...................</t>
+          <t>L163: punctuation artifact: repeated periods :: 63 Aurèle Morneau, Bonnyville ...................</t>
         </is>
       </c>
       <c r="R126" s="1" t="inlineStr"/>
@@ -6870,16 +5926,8 @@
       <c r="G127" s="1" t="inlineStr"/>
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr"/>
-      <c r="J127" s="1" t="inlineStr">
-        <is>
-          <t>L1099: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Th Ã© rese Jubinville, Saint-Paul</t>
-        </is>
-      </c>
-      <c r="K127" s="1" t="inlineStr">
-        <is>
-          <t>L460: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pauline Sabourin, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="J127" s="1" t="inlineStr"/>
+      <c r="K127" s="1" t="inlineStr"/>
       <c r="L127" s="1" t="inlineStr"/>
       <c r="M127" s="1" t="inlineStr"/>
       <c r="N127" s="1" t="inlineStr">
@@ -6895,7 +5943,7 @@
       <c r="P127" s="1" t="inlineStr"/>
       <c r="Q127" s="1" t="inlineStr">
         <is>
-          <t>L165: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 62 Juliette Houle, Ã©cole Thibeault ..............</t>
+          <t>L165: punctuation artifact: repeated periods :: 62 Juliette Houle, école Thibeault ..............</t>
         </is>
       </c>
       <c r="R127" s="1" t="inlineStr"/>
@@ -6917,16 +5965,8 @@
       <c r="G128" s="1" t="inlineStr"/>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr"/>
-      <c r="J128" s="1" t="inlineStr">
-        <is>
-          <t>L1108: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Andr Ã© Bouchard, Tangente</t>
-        </is>
-      </c>
-      <c r="K128" s="1" t="inlineStr">
-        <is>
-          <t>L466: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Jeannine ChÃ©nier, Ã©cole Grandin</t>
-        </is>
-      </c>
+      <c r="J128" s="1" t="inlineStr"/>
+      <c r="K128" s="1" t="inlineStr"/>
       <c r="L128" s="1" t="inlineStr"/>
       <c r="M128" s="1" t="inlineStr"/>
       <c r="N128" s="1" t="inlineStr">
@@ -6964,16 +6004,8 @@
       <c r="G129" s="1" t="inlineStr"/>
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr"/>
-      <c r="J129" s="1" t="inlineStr">
-        <is>
-          <t>L1111: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Th Ã© rese Rochette. Tangente</t>
-        </is>
-      </c>
-      <c r="K129" s="1" t="inlineStr">
-        <is>
-          <t>L468: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rita Guibault, ThÃ©rien Village ...................</t>
-        </is>
-      </c>
+      <c r="J129" s="1" t="inlineStr"/>
+      <c r="K129" s="1" t="inlineStr"/>
       <c r="L129" s="1" t="inlineStr"/>
       <c r="M129" s="1" t="inlineStr"/>
       <c r="N129" s="1" t="inlineStr">
@@ -7011,16 +6043,8 @@
       <c r="G130" s="1" t="inlineStr"/>
       <c r="H130" s="1" t="inlineStr"/>
       <c r="I130" s="1" t="inlineStr"/>
-      <c r="J130" s="1" t="inlineStr">
-        <is>
-          <t>L1112: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ren Ã© Lussier, Tangente</t>
-        </is>
-      </c>
-      <c r="K130" s="1" t="inlineStr">
-        <is>
-          <t>L476: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeanne Charlier, Ã©cole Dunrobin ...................</t>
-        </is>
-      </c>
+      <c r="J130" s="1" t="inlineStr"/>
+      <c r="K130" s="1" t="inlineStr"/>
       <c r="L130" s="1" t="inlineStr"/>
       <c r="M130" s="1" t="inlineStr"/>
       <c r="N130" s="1" t="inlineStr">
@@ -7036,7 +6060,7 @@
       <c r="P130" s="1" t="inlineStr"/>
       <c r="Q130" s="1" t="inlineStr">
         <is>
-          <t>L171: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Maurice McNamara, Ã©cole Grandin .................</t>
+          <t>L171: punctuation artifact: repeated periods :: Maurice McNamara, école Grandin .................</t>
         </is>
       </c>
       <c r="R130" s="1" t="inlineStr"/>
@@ -7058,16 +6082,8 @@
       <c r="G131" s="1" t="inlineStr"/>
       <c r="H131" s="1" t="inlineStr"/>
       <c r="I131" s="1" t="inlineStr"/>
-      <c r="J131" s="1" t="inlineStr">
-        <is>
-          <t>L1116: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Th Ã© rese Gauthier, Plamondon</t>
-        </is>
-      </c>
-      <c r="K131" s="1" t="inlineStr">
-        <is>
-          <t>L478: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: FranÃ§oise Trottier, Ã©cole Thibeault ...............</t>
-        </is>
-      </c>
+      <c r="J131" s="1" t="inlineStr"/>
+      <c r="K131" s="1" t="inlineStr"/>
       <c r="L131" s="1" t="inlineStr"/>
       <c r="M131" s="1" t="inlineStr"/>
       <c r="N131" s="1" t="inlineStr">
@@ -7083,7 +6099,7 @@
       <c r="P131" s="1" t="inlineStr"/>
       <c r="Q131" s="1" t="inlineStr">
         <is>
-          <t>L173: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Elizabeth Meunier, Ã©cole Thibeault .............</t>
+          <t>L173: punctuation artifact: repeated periods :: Elizabeth Meunier, école Thibeault .............</t>
         </is>
       </c>
       <c r="R131" s="1" t="inlineStr"/>
@@ -7105,16 +6121,8 @@
       <c r="G132" s="1" t="inlineStr"/>
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr"/>
-      <c r="J132" s="1" t="inlineStr">
-        <is>
-          <t>L1122: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Rom Ã© o Dechaine, Sainte-Lina</t>
-        </is>
-      </c>
-      <c r="K132" s="1" t="inlineStr">
-        <is>
-          <t>L480: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marcelle BÃ©langer, Plamondon ......................</t>
-        </is>
-      </c>
+      <c r="J132" s="1" t="inlineStr"/>
+      <c r="K132" s="1" t="inlineStr"/>
       <c r="L132" s="1" t="inlineStr"/>
       <c r="M132" s="1" t="inlineStr"/>
       <c r="N132" s="1" t="inlineStr">
@@ -7130,7 +6138,7 @@
       <c r="P132" s="1" t="inlineStr"/>
       <c r="Q132" s="1" t="inlineStr">
         <is>
-          <t>L178: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile VallÃ©e, Beaumont ....................</t>
+          <t>L178: punctuation artifact: repeated periods :: Cécile Vallée, Beaumont ....................</t>
         </is>
       </c>
       <c r="R132" s="1" t="inlineStr"/>
@@ -7152,16 +6160,8 @@
       <c r="G133" s="1" t="inlineStr"/>
       <c r="H133" s="1" t="inlineStr"/>
       <c r="I133" s="1" t="inlineStr"/>
-      <c r="J133" s="1" t="inlineStr">
-        <is>
-          <t>L1124: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Th Ã© rese Bouchard, Tangente</t>
-        </is>
-      </c>
-      <c r="K133" s="1" t="inlineStr">
-        <is>
-          <t>L482: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Elsie Loch, ThÃ©rien Village .......................</t>
-        </is>
-      </c>
+      <c r="J133" s="1" t="inlineStr"/>
+      <c r="K133" s="1" t="inlineStr"/>
       <c r="L133" s="1" t="inlineStr"/>
       <c r="M133" s="1" t="inlineStr"/>
       <c r="N133" s="1" t="inlineStr">
@@ -7177,7 +6177,7 @@
       <c r="P133" s="1" t="inlineStr"/>
       <c r="Q133" s="1" t="inlineStr">
         <is>
-          <t>L182: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ©rald Royer, Beaumont .........................</t>
+          <t>L182: punctuation artifact: repeated periods :: Gérald Royer, Beaumont .........................</t>
         </is>
       </c>
       <c r="R133" s="1" t="inlineStr"/>
@@ -7199,16 +6199,8 @@
       <c r="G134" s="1" t="inlineStr"/>
       <c r="H134" s="1" t="inlineStr"/>
       <c r="I134" s="1" t="inlineStr"/>
-      <c r="J134" s="1" t="inlineStr">
-        <is>
-          <t>L1144: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ren Ã© Magant, Sainte-Lina.</t>
-        </is>
-      </c>
-      <c r="K134" s="1" t="inlineStr">
-        <is>
-          <t>L496: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Colette Morin, Ã©cole Grandin</t>
-        </is>
-      </c>
+      <c r="J134" s="1" t="inlineStr"/>
+      <c r="K134" s="1" t="inlineStr"/>
       <c r="L134" s="1" t="inlineStr"/>
       <c r="M134" s="1" t="inlineStr"/>
       <c r="N134" s="1" t="inlineStr">
@@ -7246,16 +6238,8 @@
       <c r="G135" s="1" t="inlineStr"/>
       <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr"/>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>L1160: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Marc Voyer, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K135" s="1" t="inlineStr">
-        <is>
-          <t>L498: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Georges Pilon, Ã©cole Grandin ......................</t>
-        </is>
-      </c>
+      <c r="J135" s="1" t="inlineStr"/>
+      <c r="K135" s="1" t="inlineStr"/>
       <c r="L135" s="1" t="inlineStr"/>
       <c r="M135" s="1" t="inlineStr"/>
       <c r="N135" s="1" t="inlineStr">
@@ -7293,16 +6277,8 @@
       <c r="G136" s="1" t="inlineStr"/>
       <c r="H136" s="1" t="inlineStr"/>
       <c r="I136" s="1" t="inlineStr"/>
-      <c r="J136" s="1" t="inlineStr">
-        <is>
-          <t>L1161: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Gerard l'Abb Ã©, ecole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K136" s="1" t="inlineStr">
-        <is>
-          <t>L500: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Henri VallÃ©e, Beaumont ............................</t>
-        </is>
-      </c>
+      <c r="J136" s="1" t="inlineStr"/>
+      <c r="K136" s="1" t="inlineStr"/>
       <c r="L136" s="1" t="inlineStr"/>
       <c r="M136" s="1" t="inlineStr"/>
       <c r="N136" s="1" t="inlineStr">
@@ -7318,7 +6294,7 @@
       <c r="P136" s="1" t="inlineStr"/>
       <c r="Q136" s="1" t="inlineStr">
         <is>
-          <t>L200: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Della BÃ©langer, Plamondon .......................</t>
+          <t>L200: punctuation artifact: repeated periods :: Della Bélanger, Plamondon .......................</t>
         </is>
       </c>
       <c r="R136" s="1" t="inlineStr"/>
@@ -7340,16 +6316,8 @@
       <c r="G137" s="1" t="inlineStr"/>
       <c r="H137" s="1" t="inlineStr"/>
       <c r="I137" s="1" t="inlineStr"/>
-      <c r="J137" s="1" t="inlineStr">
-        <is>
-          <t>L1163: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Gilbert Proulx, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K137" s="1" t="inlineStr">
-        <is>
-          <t>L514: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: GÃ©rard Laplante, Couvent Notre-Dame</t>
-        </is>
-      </c>
+      <c r="J137" s="1" t="inlineStr"/>
+      <c r="K137" s="1" t="inlineStr"/>
       <c r="L137" s="1" t="inlineStr"/>
       <c r="M137" s="1" t="inlineStr"/>
       <c r="N137" s="1" t="inlineStr">
@@ -7387,16 +6355,8 @@
       <c r="G138" s="1" t="inlineStr"/>
       <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr"/>
-      <c r="J138" s="1" t="inlineStr">
-        <is>
-          <t>L1173: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ren Ã© Despins, Ã© cole consolid, Falher</t>
-        </is>
-      </c>
-      <c r="K138" s="1" t="inlineStr">
-        <is>
-          <t>L518: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Marcel BÃ©dard, Tangente</t>
-        </is>
-      </c>
+      <c r="J138" s="1" t="inlineStr"/>
+      <c r="K138" s="1" t="inlineStr"/>
       <c r="L138" s="1" t="inlineStr"/>
       <c r="M138" s="1" t="inlineStr"/>
       <c r="N138" s="1" t="inlineStr">
@@ -7434,16 +6394,8 @@
       <c r="G139" s="1" t="inlineStr"/>
       <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="1" t="inlineStr"/>
-      <c r="J139" s="1" t="inlineStr">
-        <is>
-          <t>L1189: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Jacques Voyer, Ã©cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K139" s="1" t="inlineStr">
-        <is>
-          <t>L520: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: UldÃ©ric Rochette, Tangente</t>
-        </is>
-      </c>
+      <c r="J139" s="1" t="inlineStr"/>
+      <c r="K139" s="1" t="inlineStr"/>
       <c r="L139" s="1" t="inlineStr"/>
       <c r="M139" s="1" t="inlineStr"/>
       <c r="N139" s="1" t="inlineStr">
@@ -7481,16 +6433,8 @@
       <c r="G140" s="1" t="inlineStr"/>
       <c r="H140" s="1" t="inlineStr"/>
       <c r="I140" s="1" t="inlineStr"/>
-      <c r="J140" s="1" t="inlineStr">
-        <is>
-          <t>L1193: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: B Ã© atrice Hurtubise, Saint-Paul</t>
-        </is>
-      </c>
-      <c r="K140" s="1" t="inlineStr">
-        <is>
-          <t>L522: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: IrÃ¨ne Lussier, Tangente</t>
-        </is>
-      </c>
+      <c r="J140" s="1" t="inlineStr"/>
+      <c r="K140" s="1" t="inlineStr"/>
       <c r="L140" s="1" t="inlineStr"/>
       <c r="M140" s="1" t="inlineStr"/>
       <c r="N140" s="1" t="inlineStr">
@@ -7528,16 +6472,8 @@
       <c r="G141" s="1" t="inlineStr"/>
       <c r="H141" s="1" t="inlineStr"/>
       <c r="I141" s="1" t="inlineStr"/>
-      <c r="J141" s="1" t="inlineStr">
-        <is>
-          <t>L1203: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roland Seguin, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K141" s="1" t="inlineStr">
-        <is>
-          <t>L528: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roch Proulx, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="J141" s="1" t="inlineStr"/>
+      <c r="K141" s="1" t="inlineStr"/>
       <c r="L141" s="1" t="inlineStr"/>
       <c r="M141" s="1" t="inlineStr"/>
       <c r="N141" s="1" t="inlineStr">
@@ -7575,16 +6511,8 @@
       <c r="G142" s="1" t="inlineStr"/>
       <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr"/>
-      <c r="J142" s="1" t="inlineStr">
-        <is>
-          <t>L1205: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: jeanne I'Oiseau, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K142" s="1" t="inlineStr">
-        <is>
-          <t>L532: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Yvette Thivierge, Ã©cole Grandin</t>
-        </is>
-      </c>
+      <c r="J142" s="1" t="inlineStr"/>
+      <c r="K142" s="1" t="inlineStr"/>
       <c r="L142" s="1" t="inlineStr"/>
       <c r="M142" s="1" t="inlineStr"/>
       <c r="N142" s="1" t="inlineStr">
@@ -7622,16 +6550,8 @@
       <c r="G143" s="1" t="inlineStr"/>
       <c r="H143" s="1" t="inlineStr"/>
       <c r="I143" s="1" t="inlineStr"/>
-      <c r="J143" s="1" t="inlineStr">
-        <is>
-          <t>L1207: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Edouard Garneau, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K143" s="1" t="inlineStr">
-        <is>
-          <t>L534: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©on Handfield, Beaumont ..........................</t>
-        </is>
-      </c>
+      <c r="J143" s="1" t="inlineStr"/>
+      <c r="K143" s="1" t="inlineStr"/>
       <c r="L143" s="1" t="inlineStr"/>
       <c r="M143" s="1" t="inlineStr"/>
       <c r="N143" s="1" t="inlineStr">
@@ -7647,7 +6567,7 @@
       <c r="P143" s="1" t="inlineStr"/>
       <c r="Q143" s="1" t="inlineStr">
         <is>
-          <t>L222: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Paul Roy, Ã©cole consolidÃ©e, Donnelly .......</t>
+          <t>L222: punctuation artifact: repeated periods :: Paul Roy, école consolidée, Donnelly .......</t>
         </is>
       </c>
       <c r="R143" s="1" t="inlineStr"/>
@@ -7669,16 +6589,8 @@
       <c r="G144" s="1" t="inlineStr"/>
       <c r="H144" s="1" t="inlineStr"/>
       <c r="I144" s="1" t="inlineStr"/>
-      <c r="J144" s="1" t="inlineStr">
-        <is>
-          <t>L1213: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Gertrude Brochu. Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K144" s="1" t="inlineStr">
-        <is>
-          <t>L537: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Eveline PichÃ©, pensionnat de l'Assomption</t>
-        </is>
-      </c>
+      <c r="J144" s="1" t="inlineStr"/>
+      <c r="K144" s="1" t="inlineStr"/>
       <c r="L144" s="1" t="inlineStr"/>
       <c r="M144" s="1" t="inlineStr"/>
       <c r="N144" s="1" t="inlineStr">
@@ -7694,7 +6606,7 @@
       <c r="P144" s="1" t="inlineStr"/>
       <c r="Q144" s="1" t="inlineStr">
         <is>
-          <t>L224: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Roy, Fort Kent ......................</t>
+          <t>L224: punctuation artifact: repeated periods :: Cécile Roy, Fort Kent ......................</t>
         </is>
       </c>
       <c r="R144" s="1" t="inlineStr"/>
@@ -7716,21 +6628,13 @@
       <c r="G145" s="1" t="inlineStr"/>
       <c r="H145" s="1" t="inlineStr"/>
       <c r="I145" s="1" t="inlineStr"/>
-      <c r="J145" s="1" t="inlineStr">
-        <is>
-          <t>L1227: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: 8 å“� 8</t>
-        </is>
-      </c>
-      <c r="K145" s="1" t="inlineStr">
-        <is>
-          <t>L544: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: IrÃ¨ne Bruneau, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="J145" s="1" t="inlineStr"/>
+      <c r="K145" s="1" t="inlineStr"/>
       <c r="L145" s="1" t="inlineStr"/>
       <c r="M145" s="1" t="inlineStr"/>
       <c r="N145" s="1" t="inlineStr">
         <is>
-          <t>L327: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å�£</t>
+          <t>L327: stray/suspicious non-ASCII glyph(s): U+53E3 CJK UNIFIED IDEOGRAPH-53E3 | isolated marker/symbol line :: 口</t>
         </is>
       </c>
       <c r="O145" s="1" t="inlineStr">
@@ -7763,16 +6667,8 @@
       <c r="G146" s="1" t="inlineStr"/>
       <c r="H146" s="1" t="inlineStr"/>
       <c r="I146" s="1" t="inlineStr"/>
-      <c r="J146" s="1" t="inlineStr">
-        <is>
-          <t>L1237: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lilianne Doran, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K146" s="1" t="inlineStr">
-        <is>
-          <t>L546: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Paquette, Bonnyville ......................</t>
-        </is>
-      </c>
+      <c r="J146" s="1" t="inlineStr"/>
+      <c r="K146" s="1" t="inlineStr"/>
       <c r="L146" s="1" t="inlineStr"/>
       <c r="M146" s="1" t="inlineStr"/>
       <c r="N146" s="1" t="inlineStr">
@@ -7788,7 +6684,7 @@
       <c r="P146" s="1" t="inlineStr"/>
       <c r="Q146" s="1" t="inlineStr">
         <is>
-          <t>L228: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Joseph Girard, Ã©cole Grandin ...............</t>
+          <t>L228: punctuation artifact: repeated periods :: Joseph Girard, école Grandin ...............</t>
         </is>
       </c>
       <c r="R146" s="1" t="inlineStr"/>
@@ -7810,16 +6706,8 @@
       <c r="G147" s="1" t="inlineStr"/>
       <c r="H147" s="1" t="inlineStr"/>
       <c r="I147" s="1" t="inlineStr"/>
-      <c r="J147" s="1" t="inlineStr">
-        <is>
-          <t>L1238: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER, U+00A5 YEN SIGN :: å�� ç”· å¥¶ å‡º å‡º</t>
-        </is>
-      </c>
-      <c r="K147" s="1" t="inlineStr">
-        <is>
-          <t>L552: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: PhilomÃ¨ne Frigon, Saint-Vincent ...................</t>
-        </is>
-      </c>
+      <c r="J147" s="1" t="inlineStr"/>
+      <c r="K147" s="1" t="inlineStr"/>
       <c r="L147" s="1" t="inlineStr"/>
       <c r="M147" s="1" t="inlineStr"/>
       <c r="N147" s="1" t="inlineStr">
@@ -7857,16 +6745,8 @@
       <c r="G148" s="1" t="inlineStr"/>
       <c r="H148" s="1" t="inlineStr"/>
       <c r="I148" s="1" t="inlineStr"/>
-      <c r="J148" s="1" t="inlineStr">
-        <is>
-          <t>L1242: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Th Ã© rese nard. Tangente</t>
-        </is>
-      </c>
-      <c r="K148" s="1" t="inlineStr">
-        <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Alice Dame, Ã©cole Grandin .........................</t>
-        </is>
-      </c>
+      <c r="J148" s="1" t="inlineStr"/>
+      <c r="K148" s="1" t="inlineStr"/>
       <c r="L148" s="1" t="inlineStr"/>
       <c r="M148" s="1" t="inlineStr"/>
       <c r="N148" s="1" t="inlineStr">
@@ -7904,16 +6784,8 @@
       <c r="G149" s="1" t="inlineStr"/>
       <c r="H149" s="1" t="inlineStr"/>
       <c r="I149" s="1" t="inlineStr"/>
-      <c r="J149" s="1" t="inlineStr">
-        <is>
-          <t>L1244: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Denise Despins, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K149" s="1" t="inlineStr">
-        <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Alfred ThÃ©berge, Legal ............................</t>
-        </is>
-      </c>
+      <c r="J149" s="1" t="inlineStr"/>
+      <c r="K149" s="1" t="inlineStr"/>
       <c r="L149" s="1" t="inlineStr"/>
       <c r="M149" s="1" t="inlineStr"/>
       <c r="N149" s="1" t="inlineStr">
@@ -7929,7 +6801,7 @@
       <c r="P149" s="1" t="inlineStr"/>
       <c r="Q149" s="1" t="inlineStr">
         <is>
-          <t>L242: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Pariseau, Ã©cole consolidÃ©e, Donnelly ..........</t>
+          <t>L242: punctuation artifact: repeated periods :: Cécile Pariseau, école consolidée, Donnelly ..........</t>
         </is>
       </c>
       <c r="R149" s="1" t="inlineStr"/>
@@ -7951,16 +6823,8 @@
       <c r="G150" s="1" t="inlineStr"/>
       <c r="H150" s="1" t="inlineStr"/>
       <c r="I150" s="1" t="inlineStr"/>
-      <c r="J150" s="1" t="inlineStr">
-        <is>
-          <t>L1246: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Antonia Villeneuve, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K150" s="1" t="inlineStr">
-        <is>
-          <t>L566: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Bonin, La Corey ............................</t>
-        </is>
-      </c>
+      <c r="J150" s="1" t="inlineStr"/>
+      <c r="K150" s="1" t="inlineStr"/>
       <c r="L150" s="1" t="inlineStr"/>
       <c r="M150" s="1" t="inlineStr"/>
       <c r="N150" s="1" t="inlineStr">
@@ -7976,7 +6840,7 @@
       <c r="P150" s="1" t="inlineStr"/>
       <c r="Q150" s="1" t="inlineStr">
         <is>
-          <t>L244: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT, U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeannine CÃ´tÃ©, Ã©cole consolidÃ©e, Donnelly ............</t>
+          <t>L244: punctuation artifact: repeated periods :: Jeannine Côté, école consolidée, Donnelly ............</t>
         </is>
       </c>
       <c r="R150" s="1" t="inlineStr"/>
@@ -7998,16 +6862,8 @@
       <c r="G151" s="1" t="inlineStr"/>
       <c r="H151" s="1" t="inlineStr"/>
       <c r="I151" s="1" t="inlineStr"/>
-      <c r="J151" s="1" t="inlineStr">
-        <is>
-          <t>L1250: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Diane Ouellette, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K151" s="1" t="inlineStr">
-        <is>
-          <t>L568: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: I NoÃ«l ChÃ©nard, Tangente ........................</t>
-        </is>
-      </c>
+      <c r="J151" s="1" t="inlineStr"/>
+      <c r="K151" s="1" t="inlineStr"/>
       <c r="L151" s="1" t="inlineStr"/>
       <c r="M151" s="1" t="inlineStr"/>
       <c r="N151" s="1" t="inlineStr">
@@ -8045,16 +6901,8 @@
       <c r="G152" s="1" t="inlineStr"/>
       <c r="H152" s="1" t="inlineStr"/>
       <c r="I152" s="1" t="inlineStr"/>
-      <c r="J152" s="1" t="inlineStr">
-        <is>
-          <t>L1282: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA :: ä¸Š</t>
-        </is>
-      </c>
-      <c r="K152" s="1" t="inlineStr">
-        <is>
-          <t>L570: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Anita St-Arneault, Ã©cole Grandin ................</t>
-        </is>
-      </c>
+      <c r="J152" s="1" t="inlineStr"/>
+      <c r="K152" s="1" t="inlineStr"/>
       <c r="L152" s="1" t="inlineStr"/>
       <c r="M152" s="1" t="inlineStr"/>
       <c r="N152" s="1" t="inlineStr">
@@ -8092,16 +6940,8 @@
       <c r="G153" s="1" t="inlineStr"/>
       <c r="H153" s="1" t="inlineStr"/>
       <c r="I153" s="1" t="inlineStr"/>
-      <c r="J153" s="1" t="inlineStr">
-        <is>
-          <t>L1287: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Rose-Anna Paquette, Ã© cole consolidee, Donnelly.</t>
-        </is>
-      </c>
-      <c r="K153" s="1" t="inlineStr">
-        <is>
-          <t>L572: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Claudette Turcotte, Ã©cole Grandin</t>
-        </is>
-      </c>
+      <c r="J153" s="1" t="inlineStr"/>
+      <c r="K153" s="1" t="inlineStr"/>
       <c r="L153" s="1" t="inlineStr"/>
       <c r="M153" s="1" t="inlineStr"/>
       <c r="N153" s="1" t="inlineStr">
@@ -8117,7 +6957,7 @@
       <c r="P153" s="1" t="inlineStr"/>
       <c r="Q153" s="1" t="inlineStr">
         <is>
-          <t>L250: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 86 Denise Maure, Ã©cole consolidÃ©e, Falher .............</t>
+          <t>L250: punctuation artifact: repeated periods :: 86 Denise Maure, école consolidée, Falher .............</t>
         </is>
       </c>
       <c r="R153" s="1" t="inlineStr"/>
@@ -8139,16 +6979,8 @@
       <c r="G154" s="1" t="inlineStr"/>
       <c r="H154" s="1" t="inlineStr"/>
       <c r="I154" s="1" t="inlineStr"/>
-      <c r="J154" s="1" t="inlineStr">
-        <is>
-          <t>L1293: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roland TieuliÃ©, Legal .</t>
-        </is>
-      </c>
-      <c r="K154" s="1" t="inlineStr">
-        <is>
-          <t>L574: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lorette Tellier, Ã©cole Thibeault ................</t>
-        </is>
-      </c>
+      <c r="J154" s="1" t="inlineStr"/>
+      <c r="K154" s="1" t="inlineStr"/>
       <c r="L154" s="1" t="inlineStr"/>
       <c r="M154" s="1" t="inlineStr"/>
       <c r="N154" s="1" t="inlineStr">
@@ -8186,16 +7018,8 @@
       <c r="G155" s="1" t="inlineStr"/>
       <c r="H155" s="1" t="inlineStr"/>
       <c r="I155" s="1" t="inlineStr"/>
-      <c r="J155" s="1" t="inlineStr">
-        <is>
-          <t>L1304: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: miÃ¨re, une courte biographie de trois</t>
-        </is>
-      </c>
-      <c r="K155" s="1" t="inlineStr">
-        <is>
-          <t>L578: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: CÃ©cile Collins, Fort Kent</t>
-        </is>
-      </c>
+      <c r="J155" s="1" t="inlineStr"/>
+      <c r="K155" s="1" t="inlineStr"/>
       <c r="L155" s="1" t="inlineStr"/>
       <c r="M155" s="1" t="inlineStr"/>
       <c r="N155" s="1" t="inlineStr">
@@ -8233,16 +7057,8 @@
       <c r="G156" s="1" t="inlineStr"/>
       <c r="H156" s="1" t="inlineStr"/>
       <c r="I156" s="1" t="inlineStr"/>
-      <c r="J156" s="1" t="inlineStr">
-        <is>
-          <t>L1305: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER, U+00A9 COPYRIGHT SIGN :: des n Å� tres qui ont fond Ã© des villes aux</t>
-        </is>
-      </c>
-      <c r="K156" s="1" t="inlineStr">
-        <is>
-          <t>L580: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© BeauprÃ©, Bonnyville .......................</t>
-        </is>
-      </c>
+      <c r="J156" s="1" t="inlineStr"/>
+      <c r="K156" s="1" t="inlineStr"/>
       <c r="L156" s="1" t="inlineStr"/>
       <c r="M156" s="1" t="inlineStr"/>
       <c r="N156" s="1" t="inlineStr">
@@ -8280,16 +7096,8 @@
       <c r="G157" s="1" t="inlineStr"/>
       <c r="H157" s="1" t="inlineStr"/>
       <c r="I157" s="1" t="inlineStr"/>
-      <c r="J157" s="1" t="inlineStr">
-        <is>
-          <t>L1307: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: double/multiple hyphen :: les noms sont inscrits dans le dÃ©velop--</t>
-        </is>
-      </c>
-      <c r="K157" s="1" t="inlineStr">
-        <is>
-          <t>L584: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: GÃ©rald Dusseault, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="J157" s="1" t="inlineStr"/>
+      <c r="K157" s="1" t="inlineStr"/>
       <c r="L157" s="1" t="inlineStr"/>
       <c r="M157" s="1" t="inlineStr"/>
       <c r="N157" s="1" t="inlineStr">
@@ -8327,16 +7135,8 @@
       <c r="G158" s="1" t="inlineStr"/>
       <c r="H158" s="1" t="inlineStr"/>
       <c r="I158" s="1" t="inlineStr"/>
-      <c r="J158" s="1" t="inlineStr">
-        <is>
-          <t>L1308: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: pement de la grande r Ã© publique am Ã© ri-</t>
-        </is>
-      </c>
-      <c r="K158" s="1" t="inlineStr">
-        <is>
-          <t>L586: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roland Carriere, Ã©cole Dunrobin .................</t>
-        </is>
-      </c>
+      <c r="J158" s="1" t="inlineStr"/>
+      <c r="K158" s="1" t="inlineStr"/>
       <c r="L158" s="1" t="inlineStr"/>
       <c r="M158" s="1" t="inlineStr"/>
       <c r="N158" s="1" t="inlineStr">
@@ -8374,16 +7174,8 @@
       <c r="G159" s="1" t="inlineStr"/>
       <c r="H159" s="1" t="inlineStr"/>
       <c r="I159" s="1" t="inlineStr"/>
-      <c r="J159" s="1" t="inlineStr">
-        <is>
-          <t>L1314: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Personne n'a manifest Ã© plus d'esprit</t>
-        </is>
-      </c>
-      <c r="K159" s="1" t="inlineStr">
-        <is>
-          <t>L588: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lilianne Houle, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J159" s="1" t="inlineStr"/>
+      <c r="K159" s="1" t="inlineStr"/>
       <c r="L159" s="1" t="inlineStr"/>
       <c r="M159" s="1" t="inlineStr"/>
       <c r="N159" s="1" t="inlineStr">
@@ -8421,16 +7213,8 @@
       <c r="G160" s="1" t="inlineStr"/>
       <c r="H160" s="1" t="inlineStr"/>
       <c r="I160" s="1" t="inlineStr"/>
-      <c r="J160" s="1" t="inlineStr">
-        <is>
-          <t>L1315: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: d'initiative dans le d Ã© veloppement de</t>
-        </is>
-      </c>
-      <c r="K160" s="1" t="inlineStr">
-        <is>
-          <t>L590: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: HervÃ© Ouellette, Sainte-Lina ....................</t>
-        </is>
-      </c>
+      <c r="J160" s="1" t="inlineStr"/>
+      <c r="K160" s="1" t="inlineStr"/>
       <c r="L160" s="1" t="inlineStr"/>
       <c r="M160" s="1" t="inlineStr"/>
       <c r="N160" s="1" t="inlineStr">
@@ -8446,7 +7230,7 @@
       <c r="P160" s="1" t="inlineStr"/>
       <c r="Q160" s="1" t="inlineStr">
         <is>
-          <t>L264: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 85 Yolande Garneau, Ã©cole Granlin .....................</t>
+          <t>L264: punctuation artifact: repeated periods :: 85 Yolande Garneau, école Granlin .....................</t>
         </is>
       </c>
       <c r="R160" s="1" t="inlineStr"/>
@@ -8468,16 +7252,8 @@
       <c r="G161" s="1" t="inlineStr"/>
       <c r="H161" s="1" t="inlineStr"/>
       <c r="I161" s="1" t="inlineStr"/>
-      <c r="J161" s="1" t="inlineStr">
-        <is>
-          <t>L1316: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: I'Ouest am Ã© ricain que les frÃ¨res Beau-</t>
-        </is>
-      </c>
-      <c r="K161" s="1" t="inlineStr">
-        <is>
-          <t>L596: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Claude Charrois, Ã©cole Grandin</t>
-        </is>
-      </c>
+      <c r="J161" s="1" t="inlineStr"/>
+      <c r="K161" s="1" t="inlineStr"/>
       <c r="L161" s="1" t="inlineStr"/>
       <c r="M161" s="1" t="inlineStr"/>
       <c r="N161" s="1" t="inlineStr">
@@ -8515,16 +7291,8 @@
       <c r="G162" s="1" t="inlineStr"/>
       <c r="H162" s="1" t="inlineStr"/>
       <c r="I162" s="1" t="inlineStr"/>
-      <c r="J162" s="1" t="inlineStr">
-        <is>
-          <t>L1320: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: arriÃ¨re presque aussi Ã©tonnante. Il na-</t>
-        </is>
-      </c>
-      <c r="K162" s="1" t="inlineStr">
-        <is>
-          <t>L602: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Juliette Williams, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J162" s="1" t="inlineStr"/>
+      <c r="K162" s="1" t="inlineStr"/>
       <c r="L162" s="1" t="inlineStr"/>
       <c r="M162" s="1" t="inlineStr"/>
       <c r="N162" s="1" t="inlineStr">
@@ -8540,7 +7308,7 @@
       <c r="P162" s="1" t="inlineStr"/>
       <c r="Q162" s="1" t="inlineStr">
         <is>
-          <t>L268: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ©rard Levasseur, Ã©cole Grandin ......................</t>
+          <t>L268: punctuation artifact: repeated periods :: Gérard Levasseur, école Grandin ......................</t>
         </is>
       </c>
       <c r="R162" s="1" t="inlineStr"/>
@@ -8562,16 +7330,8 @@
       <c r="G163" s="1" t="inlineStr"/>
       <c r="H163" s="1" t="inlineStr"/>
       <c r="I163" s="1" t="inlineStr"/>
-      <c r="J163" s="1" t="inlineStr">
-        <is>
-          <t>L1325: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: double/multiple hyphen :: des San-Fran partitÃ©s par les dÃ©pour--</t>
-        </is>
-      </c>
-      <c r="K163" s="1" t="inlineStr">
-        <is>
-          <t>L604: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Philippe HÃ©bert, Saint-Vincent ..................</t>
-        </is>
-      </c>
+      <c r="J163" s="1" t="inlineStr"/>
+      <c r="K163" s="1" t="inlineStr"/>
       <c r="L163" s="1" t="inlineStr"/>
       <c r="M163" s="1" t="inlineStr"/>
       <c r="N163" s="1" t="inlineStr">
@@ -8587,7 +7347,7 @@
       <c r="P163" s="1" t="inlineStr"/>
       <c r="Q163" s="1" t="inlineStr">
         <is>
-          <t>L270: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Yvette Normand, ThÃ©rien ..............................</t>
+          <t>L270: punctuation artifact: repeated periods :: Yvette Normand, Thérien ..............................</t>
         </is>
       </c>
       <c r="R163" s="1" t="inlineStr"/>
@@ -8609,16 +7369,8 @@
       <c r="G164" s="1" t="inlineStr"/>
       <c r="H164" s="1" t="inlineStr"/>
       <c r="I164" s="1" t="inlineStr"/>
-      <c r="J164" s="1" t="inlineStr">
-        <is>
-          <t>L1327: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: double/multiple hyphen :: gnala en fondant une agence de goÃ©let--</t>
-        </is>
-      </c>
-      <c r="K164" s="1" t="inlineStr">
-        <is>
-          <t>L606: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GisÃ¨le SÃ©guin, Bonnyville........................</t>
-        </is>
-      </c>
+      <c r="J164" s="1" t="inlineStr"/>
+      <c r="K164" s="1" t="inlineStr"/>
       <c r="L164" s="1" t="inlineStr"/>
       <c r="M164" s="1" t="inlineStr"/>
       <c r="N164" s="1" t="inlineStr">
@@ -8634,7 +7386,7 @@
       <c r="P164" s="1" t="inlineStr"/>
       <c r="Q164" s="1" t="inlineStr">
         <is>
-          <t>L272: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Raymond Sylvestre, Ã©cole Thibeault ...................</t>
+          <t>L272: punctuation artifact: repeated periods :: Raymond Sylvestre, école Thibeault ...................</t>
         </is>
       </c>
       <c r="R164" s="1" t="inlineStr"/>
@@ -8656,16 +7408,8 @@
       <c r="G165" s="1" t="inlineStr"/>
       <c r="H165" s="1" t="inlineStr"/>
       <c r="I165" s="1" t="inlineStr"/>
-      <c r="J165" s="1" t="inlineStr">
-        <is>
-          <t>L1330: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: compagnie de son frÃ¨re, Prudent, iil or-</t>
-        </is>
-      </c>
-      <c r="K165" s="1" t="inlineStr">
-        <is>
-          <t>L610: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: AdÃ¨le Couture, Bonnyville .......................</t>
-        </is>
-      </c>
+      <c r="J165" s="1" t="inlineStr"/>
+      <c r="K165" s="1" t="inlineStr"/>
       <c r="L165" s="1" t="inlineStr"/>
       <c r="M165" s="1" t="inlineStr"/>
       <c r="N165" s="1" t="inlineStr">
@@ -8681,7 +7425,7 @@
       <c r="P165" s="1" t="inlineStr"/>
       <c r="Q165" s="1" t="inlineStr">
         <is>
-          <t>L274: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 85 CÃ©cile Doucet. Tangente ............................</t>
+          <t>L274: punctuation artifact: repeated periods :: 85 Cécile Doucet. Tangente ............................</t>
         </is>
       </c>
       <c r="R165" s="1" t="inlineStr"/>
@@ -8703,16 +7447,8 @@
       <c r="G166" s="1" t="inlineStr"/>
       <c r="H166" s="1" t="inlineStr"/>
       <c r="I166" s="1" t="inlineStr"/>
-      <c r="J166" s="1" t="inlineStr">
-        <is>
-          <t>L1335: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Los Angeles deux ann Ã© es plus tard. La</t>
-        </is>
-      </c>
-      <c r="K166" s="1" t="inlineStr">
-        <is>
-          <t>L614: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Gordon Miniely, ThÃ©rien Village</t>
-        </is>
-      </c>
+      <c r="J166" s="1" t="inlineStr"/>
+      <c r="K166" s="1" t="inlineStr"/>
       <c r="L166" s="1" t="inlineStr"/>
       <c r="M166" s="1" t="inlineStr"/>
       <c r="N166" s="1" t="inlineStr">
@@ -8750,16 +7486,8 @@
       <c r="G167" s="1" t="inlineStr"/>
       <c r="H167" s="1" t="inlineStr"/>
       <c r="I167" s="1" t="inlineStr"/>
-      <c r="J167" s="1" t="inlineStr">
-        <is>
-          <t>L1336: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: terrible guerre de s Ã© cession lui permit</t>
-        </is>
-      </c>
-      <c r="K167" s="1" t="inlineStr">
-        <is>
-          <t>L616: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ;GrÃ©goire Ouellet, La Corey</t>
-        </is>
-      </c>
+      <c r="J167" s="1" t="inlineStr"/>
+      <c r="K167" s="1" t="inlineStr"/>
       <c r="L167" s="1" t="inlineStr"/>
       <c r="M167" s="1" t="inlineStr"/>
       <c r="N167" s="1" t="inlineStr">
@@ -8775,7 +7503,7 @@
       <c r="P167" s="1" t="inlineStr"/>
       <c r="Q167" s="1" t="inlineStr">
         <is>
-          <t>L294: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rollande Boulet, Ã©cole consolidÃ©e, Donnelly ..</t>
+          <t>L294: punctuation artifact: repeated periods :: Rollande Boulet, école consolidée, Donnelly ..</t>
         </is>
       </c>
       <c r="R167" s="1" t="inlineStr"/>
@@ -8797,16 +7525,8 @@
       <c r="G168" s="1" t="inlineStr"/>
       <c r="H168" s="1" t="inlineStr"/>
       <c r="I168" s="1" t="inlineStr"/>
-      <c r="J168" s="1" t="inlineStr">
-        <is>
-          <t>L1337: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT :: de jouer un rÃ´le important. Il devint</t>
-        </is>
-      </c>
-      <c r="K168" s="1" t="inlineStr">
-        <is>
-          <t>L618: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ! Jeannette Sylvestre, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J168" s="1" t="inlineStr"/>
+      <c r="K168" s="1" t="inlineStr"/>
       <c r="L168" s="1" t="inlineStr"/>
       <c r="M168" s="1" t="inlineStr"/>
       <c r="N168" s="1" t="inlineStr">
@@ -8822,7 +7542,7 @@
       <c r="P168" s="1" t="inlineStr"/>
       <c r="Q168" s="1" t="inlineStr">
         <is>
-          <t>L300: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rachel LabontÃ©, Ã©cole Thibeault ...........</t>
+          <t>L300: punctuation artifact: repeated periods :: Rachel Labonté, école Thibeault ...........</t>
         </is>
       </c>
       <c r="R168" s="1" t="inlineStr"/>
@@ -8844,16 +7564,8 @@
       <c r="G169" s="1" t="inlineStr"/>
       <c r="H169" s="1" t="inlineStr"/>
       <c r="I169" s="1" t="inlineStr"/>
-      <c r="J169" s="1" t="inlineStr">
-        <is>
-          <t>L1338: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: r Ã© guli Ã¨ re. Il suivit, en cette qualit Ã©, les</t>
-        </is>
-      </c>
-      <c r="K169" s="1" t="inlineStr">
-        <is>
-          <t>L621: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: â€¢ IrÃ¨ne Lambert, Bonnyville .....................</t>
-        </is>
-      </c>
+      <c r="J169" s="1" t="inlineStr"/>
+      <c r="K169" s="1" t="inlineStr"/>
       <c r="L169" s="1" t="inlineStr"/>
       <c r="M169" s="1" t="inlineStr"/>
       <c r="N169" s="1" t="inlineStr">
@@ -8869,7 +7581,7 @@
       <c r="P169" s="1" t="inlineStr"/>
       <c r="Q169" s="1" t="inlineStr">
         <is>
-          <t>L302: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Patricia BÃ©land. Ã©cole Thibeault ...........</t>
+          <t>L302: punctuation artifact: repeated periods :: Patricia Béland. école Thibeault ...........</t>
         </is>
       </c>
       <c r="R169" s="1" t="inlineStr"/>
@@ -8891,16 +7603,8 @@
       <c r="G170" s="1" t="inlineStr"/>
       <c r="H170" s="1" t="inlineStr"/>
       <c r="I170" s="1" t="inlineStr"/>
-      <c r="J170" s="1" t="inlineStr">
-        <is>
-          <t>L1339: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: rÃ©giments qui se rendaient a Washing-</t>
-        </is>
-      </c>
-      <c r="K170" s="1" t="inlineStr">
-        <is>
-          <t>L623: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 1C (letter/digit mix) :: 1CÃ©cile Lacombe, Bonnyville.................</t>
-        </is>
-      </c>
+      <c r="J170" s="1" t="inlineStr"/>
+      <c r="K170" s="1" t="inlineStr"/>
       <c r="L170" s="1" t="inlineStr"/>
       <c r="M170" s="1" t="inlineStr"/>
       <c r="N170" s="1" t="inlineStr">
@@ -8938,16 +7642,8 @@
       <c r="G171" s="1" t="inlineStr"/>
       <c r="H171" s="1" t="inlineStr"/>
       <c r="I171" s="1" t="inlineStr"/>
-      <c r="J171" s="1" t="inlineStr">
-        <is>
-          <t>L1341: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: vres avec l'Etat. Il est vrai que ce n 'Ã© tait</t>
-        </is>
-      </c>
-      <c r="K171" s="1" t="inlineStr">
-        <is>
-          <t>L635: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ..61 i Vivianne Nobert, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="J171" s="1" t="inlineStr"/>
+      <c r="K171" s="1" t="inlineStr"/>
       <c r="L171" s="1" t="inlineStr"/>
       <c r="M171" s="1" t="inlineStr"/>
       <c r="N171" s="1" t="inlineStr">
@@ -8963,7 +7659,7 @@
       <c r="P171" s="1" t="inlineStr"/>
       <c r="Q171" s="1" t="inlineStr">
         <is>
-          <t>L306: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©onard LabontÃ©, Ã©cole Thibeault .........</t>
+          <t>L306: punctuation artifact: repeated periods :: Léonard Labonté, école Thibeault .........</t>
         </is>
       </c>
       <c r="R171" s="1" t="inlineStr"/>
@@ -8985,16 +7681,8 @@
       <c r="G172" s="1" t="inlineStr"/>
       <c r="H172" s="1" t="inlineStr"/>
       <c r="I172" s="1" t="inlineStr"/>
-      <c r="J172" s="1" t="inlineStr">
-        <is>
-          <t>L1345: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: a Independence. Il dÃ©couvrit un nou-</t>
-        </is>
-      </c>
-      <c r="K172" s="1" t="inlineStr">
-        <is>
-          <t>L637: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: 61 ThÃ©rÃ¨se Jubinville, Saint-Paul</t>
-        </is>
-      </c>
+      <c r="J172" s="1" t="inlineStr"/>
+      <c r="K172" s="1" t="inlineStr"/>
       <c r="L172" s="1" t="inlineStr"/>
       <c r="M172" s="1" t="inlineStr"/>
       <c r="N172" s="1" t="inlineStr">
@@ -9032,16 +7720,8 @@
       <c r="G173" s="1" t="inlineStr"/>
       <c r="H173" s="1" t="inlineStr"/>
       <c r="I173" s="1" t="inlineStr"/>
-      <c r="J173" s="1" t="inlineStr">
-        <is>
-          <t>L1346: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: veau procÃ©dÃ© pour la fonte des mine-</t>
-        </is>
-      </c>
-      <c r="K173" s="1" t="inlineStr">
-        <is>
-          <t>L645: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 581 AndrÃ© Bouchard, Tangente ..........</t>
-        </is>
-      </c>
+      <c r="J173" s="1" t="inlineStr"/>
+      <c r="K173" s="1" t="inlineStr"/>
       <c r="L173" s="1" t="inlineStr"/>
       <c r="M173" s="1" t="inlineStr"/>
       <c r="N173" s="1" t="inlineStr">
@@ -9079,16 +7759,8 @@
       <c r="G174" s="1" t="inlineStr"/>
       <c r="H174" s="1" t="inlineStr"/>
       <c r="I174" s="1" t="inlineStr"/>
-      <c r="J174" s="1" t="inlineStr">
-        <is>
-          <t>L1348: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: lui assurÃ¨rent un revenu considÃ©rable.</t>
-        </is>
-      </c>
-      <c r="K174" s="1" t="inlineStr">
-        <is>
-          <t>L679: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lorraine Lussier, Ã©cole consolidÃ©e, Donnelly 77</t>
-        </is>
-      </c>
+      <c r="J174" s="1" t="inlineStr"/>
+      <c r="K174" s="1" t="inlineStr"/>
       <c r="L174" s="1" t="inlineStr"/>
       <c r="M174" s="1" t="inlineStr"/>
       <c r="N174" s="1" t="inlineStr">
@@ -9126,16 +7798,8 @@
       <c r="G175" s="1" t="inlineStr"/>
       <c r="H175" s="1" t="inlineStr"/>
       <c r="I175" s="1" t="inlineStr"/>
-      <c r="J175" s="1" t="inlineStr">
-        <is>
-          <t>L1353: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: aussi les menaces de la ruine dÃ©faisait.</t>
-        </is>
-      </c>
-      <c r="K175" s="1" t="inlineStr">
-        <is>
-          <t>L681: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: GÃ©rard Casavant, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="J175" s="1" t="inlineStr"/>
+      <c r="K175" s="1" t="inlineStr"/>
       <c r="L175" s="1" t="inlineStr"/>
       <c r="M175" s="1" t="inlineStr"/>
       <c r="N175" s="1" t="inlineStr">
@@ -9151,7 +7815,7 @@
       <c r="P175" s="1" t="inlineStr"/>
       <c r="Q175" s="1" t="inlineStr">
         <is>
-          <t>L314: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: IrÃ¨ne Caouette, Bonnyville ................</t>
+          <t>L314: punctuation artifact: repeated periods :: Irène Caouette, Bonnyville ................</t>
         </is>
       </c>
       <c r="R175" s="1" t="inlineStr"/>
@@ -9173,16 +7837,8 @@
       <c r="G176" s="1" t="inlineStr"/>
       <c r="H176" s="1" t="inlineStr"/>
       <c r="I176" s="1" t="inlineStr"/>
-      <c r="J176" s="1" t="inlineStr">
-        <is>
-          <t>L1355: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: eut a subir, il r Ã© ussit a se constituer une</t>
-        </is>
-      </c>
-      <c r="K176" s="1" t="inlineStr">
-        <is>
-          <t>L687: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Maurice Chevalier, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J176" s="1" t="inlineStr"/>
+      <c r="K176" s="1" t="inlineStr"/>
       <c r="L176" s="1" t="inlineStr"/>
       <c r="M176" s="1" t="inlineStr"/>
       <c r="N176" s="1" t="inlineStr">
@@ -9198,7 +7854,7 @@
       <c r="P176" s="1" t="inlineStr"/>
       <c r="Q176" s="1" t="inlineStr">
         <is>
-          <t>L316: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Sylvia Yakimchuk, ThÃ©rien Village ........</t>
+          <t>L316: punctuation artifact: repeated periods :: Sylvia Yakimchuk, Thérien Village ........</t>
         </is>
       </c>
       <c r="R176" s="1" t="inlineStr"/>
@@ -9220,16 +7876,8 @@
       <c r="G177" s="1" t="inlineStr"/>
       <c r="H177" s="1" t="inlineStr"/>
       <c r="I177" s="1" t="inlineStr"/>
-      <c r="J177" s="1" t="inlineStr">
-        <is>
-          <t>L1358: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Quatre jeunes gens ont pass Ã© la moi-</t>
-        </is>
-      </c>
-      <c r="K177" s="1" t="inlineStr">
-        <is>
-          <t>L689: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Annette Comeau, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J177" s="1" t="inlineStr"/>
+      <c r="K177" s="1" t="inlineStr"/>
       <c r="L177" s="1" t="inlineStr"/>
       <c r="M177" s="1" t="inlineStr"/>
       <c r="N177" s="1" t="inlineStr">
@@ -9267,16 +7915,8 @@
       <c r="G178" s="1" t="inlineStr"/>
       <c r="H178" s="1" t="inlineStr"/>
       <c r="I178" s="1" t="inlineStr"/>
-      <c r="J178" s="1" t="inlineStr">
-        <is>
-          <t>L1359: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ti Ã© de la nuit Ã jouer. En se s Ã© parant,! v</t>
-        </is>
-      </c>
-      <c r="K178" s="1" t="inlineStr">
-        <is>
-          <t>L690: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: LÃ©a Ricard, couvent Notre-Dame</t>
-        </is>
-      </c>
+      <c r="J178" s="1" t="inlineStr"/>
+      <c r="K178" s="1" t="inlineStr"/>
       <c r="L178" s="1" t="inlineStr"/>
       <c r="M178" s="1" t="inlineStr"/>
       <c r="N178" s="1" t="inlineStr">
@@ -9314,16 +7954,8 @@
       <c r="G179" s="1" t="inlineStr"/>
       <c r="H179" s="1" t="inlineStr"/>
       <c r="I179" s="1" t="inlineStr"/>
-      <c r="J179" s="1" t="inlineStr">
-        <is>
-          <t>L1361: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: chac a gagnÃ© 40 francs, et que per-</t>
-        </is>
-      </c>
-      <c r="K179" s="1" t="inlineStr">
-        <is>
-          <t>L696: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: EvangÃ©line Gillon, Tangente .................</t>
-        </is>
-      </c>
+      <c r="J179" s="1" t="inlineStr"/>
+      <c r="K179" s="1" t="inlineStr"/>
       <c r="L179" s="1" t="inlineStr"/>
       <c r="M179" s="1" t="inlineStr"/>
       <c r="N179" s="1" t="inlineStr">
@@ -9339,7 +7971,7 @@
       <c r="P179" s="1" t="inlineStr"/>
       <c r="Q179" s="1" t="inlineStr">
         <is>
-          <t>L322: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lucille MahÃ©, Legal .......</t>
+          <t>L322: punctuation artifact: repeated periods :: Lucille Mahé, Legal .......</t>
         </is>
       </c>
       <c r="R179" s="1" t="inlineStr"/>
@@ -9361,16 +7993,8 @@
       <c r="G180" s="1" t="inlineStr"/>
       <c r="H180" s="1" t="inlineStr"/>
       <c r="I180" s="1" t="inlineStr"/>
-      <c r="J180" s="1" t="inlineStr">
-        <is>
-          <t>L1367: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Autre fondateur de ville am Ã© ricaine,</t>
-        </is>
-      </c>
-      <c r="K180" s="1" t="inlineStr">
-        <is>
-          <t>L698: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Euclide BÃ©rubÃ©, Beaumont .........</t>
-        </is>
-      </c>
+      <c r="J180" s="1" t="inlineStr"/>
+      <c r="K180" s="1" t="inlineStr"/>
       <c r="L180" s="1" t="inlineStr"/>
       <c r="M180" s="1" t="inlineStr"/>
       <c r="N180" s="1" t="inlineStr">
@@ -9386,7 +8010,7 @@
       <c r="P180" s="1" t="inlineStr"/>
       <c r="Q180" s="1" t="inlineStr">
         <is>
-          <t>L324: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: FranÃ§ois Blackburn, Ã©cole Grandin ........</t>
+          <t>L324: punctuation artifact: repeated periods :: François Blackburn, école Grandin ........</t>
         </is>
       </c>
       <c r="R180" s="1" t="inlineStr"/>
@@ -9408,16 +8032,8 @@
       <c r="G181" s="1" t="inlineStr"/>
       <c r="H181" s="1" t="inlineStr"/>
       <c r="I181" s="1" t="inlineStr"/>
-      <c r="J181" s="1" t="inlineStr">
-        <is>
-          <t>L1373: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ite et finit par s 'Ã© tablir, en 1853, Ã Supe-</t>
-        </is>
-      </c>
-      <c r="K181" s="1" t="inlineStr">
-        <is>
-          <t>L702: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: LÃ©o Ouellette, Ste-Lina</t>
-        </is>
-      </c>
+      <c r="J181" s="1" t="inlineStr"/>
+      <c r="K181" s="1" t="inlineStr"/>
       <c r="L181" s="1" t="inlineStr"/>
       <c r="M181" s="1" t="inlineStr"/>
       <c r="N181" s="1" t="inlineStr">
@@ -9455,16 +8071,8 @@
       <c r="G182" s="1" t="inlineStr"/>
       <c r="H182" s="1" t="inlineStr"/>
       <c r="I182" s="1" t="inlineStr"/>
-      <c r="J182" s="1" t="inlineStr">
-        <is>
-          <t>L1374: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: nom, crit Tass Ã©, mais l'ann Ã© e suivante, ; h</t>
-        </is>
-      </c>
-      <c r="K182" s="1" t="inlineStr">
-        <is>
-          <t>L712: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paul Houde, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="J182" s="1" t="inlineStr"/>
+      <c r="K182" s="1" t="inlineStr"/>
       <c r="L182" s="1" t="inlineStr"/>
       <c r="M182" s="1" t="inlineStr"/>
       <c r="N182" s="1" t="inlineStr">
@@ -9502,21 +8110,13 @@
       <c r="G183" s="1" t="inlineStr"/>
       <c r="H183" s="1" t="inlineStr"/>
       <c r="I183" s="1" t="inlineStr"/>
-      <c r="J183" s="1" t="inlineStr">
-        <is>
-          <t>L1377: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: geaient rien moins qu'a dÃ©troner Chica-</t>
-        </is>
-      </c>
-      <c r="K183" s="1" t="inlineStr">
-        <is>
-          <t>L714: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Marguerite Sabourin, Ã©cole Grandin</t>
-        </is>
-      </c>
+      <c r="J183" s="1" t="inlineStr"/>
+      <c r="K183" s="1" t="inlineStr"/>
       <c r="L183" s="1" t="inlineStr"/>
       <c r="M183" s="1" t="inlineStr"/>
       <c r="N183" s="1" t="inlineStr">
         <is>
-          <t>L372: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L372: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O183" s="1" t="inlineStr">
@@ -9527,7 +8127,7 @@
       <c r="P183" s="1" t="inlineStr"/>
       <c r="Q183" s="1" t="inlineStr">
         <is>
-          <t>L330: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): eThibeault (odd internal casing) :: Lorraine Tellier, Ã©col eThibeault .........</t>
+          <t>L330: punctuation artifact: repeated periods | suspicious token(s): eThibeault (odd internal casing) :: Lorraine Tellier, écol eThibeault .........</t>
         </is>
       </c>
       <c r="R183" s="1" t="inlineStr"/>
@@ -9549,16 +8149,8 @@
       <c r="G184" s="1" t="inlineStr"/>
       <c r="H184" s="1" t="inlineStr"/>
       <c r="I184" s="1" t="inlineStr"/>
-      <c r="J184" s="1" t="inlineStr">
-        <is>
-          <t>L1379: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: l Ã© e a devenir l'entrepot des produits du</t>
-        </is>
-      </c>
-      <c r="K184" s="1" t="inlineStr">
-        <is>
-          <t>L718: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Juliette BÃ©rubÃ©, Beaumont</t>
-        </is>
-      </c>
+      <c r="J184" s="1" t="inlineStr"/>
+      <c r="K184" s="1" t="inlineStr"/>
       <c r="L184" s="1" t="inlineStr"/>
       <c r="M184" s="1" t="inlineStr"/>
       <c r="N184" s="1" t="inlineStr">
@@ -9596,16 +8188,8 @@
       <c r="G185" s="1" t="inlineStr"/>
       <c r="H185" s="1" t="inlineStr"/>
       <c r="I185" s="1" t="inlineStr"/>
-      <c r="J185" s="1" t="inlineStr">
-        <is>
-          <t>L1380: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Nord-Ouest, le port le plus fr Ã© quent Ã© de</t>
-        </is>
-      </c>
-      <c r="K185" s="1" t="inlineStr">
-        <is>
-          <t>L724: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paul Lemire, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="J185" s="1" t="inlineStr"/>
+      <c r="K185" s="1" t="inlineStr"/>
       <c r="L185" s="1" t="inlineStr"/>
       <c r="M185" s="1" t="inlineStr"/>
       <c r="N185" s="1" t="inlineStr">
@@ -9621,7 +8205,7 @@
       <c r="P185" s="1" t="inlineStr"/>
       <c r="Q185" s="1" t="inlineStr">
         <is>
-          <t>L334: punctuation artifact: repeated periods :: NoÃ«l Jacob, Tangente ..........</t>
+          <t>L334: punctuation artifact: repeated periods :: Noël Jacob, Tangente ..........</t>
         </is>
       </c>
       <c r="R185" s="1" t="inlineStr"/>
@@ -9643,16 +8227,8 @@
       <c r="G186" s="1" t="inlineStr"/>
       <c r="H186" s="1" t="inlineStr"/>
       <c r="I186" s="1" t="inlineStr"/>
-      <c r="J186" s="1" t="inlineStr">
-        <is>
-          <t>L1381: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: tous les lacs. Ils n'avaient pas song Ã© que</t>
-        </is>
-      </c>
-      <c r="K186" s="1" t="inlineStr">
-        <is>
-          <t>L732: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Dolores Comeau, Ã©cole consolidÃ©e, Falher ....</t>
-        </is>
-      </c>
+      <c r="J186" s="1" t="inlineStr"/>
+      <c r="K186" s="1" t="inlineStr"/>
       <c r="L186" s="1" t="inlineStr"/>
       <c r="M186" s="1" t="inlineStr"/>
       <c r="N186" s="1" t="inlineStr">
@@ -9690,16 +8266,8 @@
       <c r="G187" s="1" t="inlineStr"/>
       <c r="H187" s="1" t="inlineStr"/>
       <c r="I187" s="1" t="inlineStr"/>
-      <c r="J187" s="1" t="inlineStr">
-        <is>
-          <t>L1382: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: la Cit Ã© du Supe rieur n'avait pas encore</t>
-        </is>
-      </c>
-      <c r="K187" s="1" t="inlineStr">
-        <is>
-          <t>L738: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Yolande Robert, Ã©cole Thibeault .............</t>
-        </is>
-      </c>
+      <c r="J187" s="1" t="inlineStr"/>
+      <c r="K187" s="1" t="inlineStr"/>
       <c r="L187" s="1" t="inlineStr"/>
       <c r="M187" s="1" t="inlineStr"/>
       <c r="N187" s="1" t="inlineStr">
@@ -9737,16 +8305,8 @@
       <c r="G188" s="1" t="inlineStr"/>
       <c r="H188" s="1" t="inlineStr"/>
       <c r="I188" s="1" t="inlineStr"/>
-      <c r="J188" s="1" t="inlineStr">
-        <is>
-          <t>L1383: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: derri Ã¨ re elle de campagnes cultiv, ni</t>
-        </is>
-      </c>
-      <c r="K188" s="1" t="inlineStr">
-        <is>
-          <t>L740: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: GÃ©rard Magnan, couvent Notre-Dame</t>
-        </is>
-      </c>
+      <c r="J188" s="1" t="inlineStr"/>
+      <c r="K188" s="1" t="inlineStr"/>
       <c r="L188" s="1" t="inlineStr"/>
       <c r="M188" s="1" t="inlineStr"/>
       <c r="N188" s="1" t="inlineStr">
@@ -9762,7 +8322,7 @@
       <c r="P188" s="1" t="inlineStr"/>
       <c r="Q188" s="1" t="inlineStr">
         <is>
-          <t>L340: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Portelance. Tangente ..............</t>
+          <t>L340: punctuation artifact: repeated periods :: Thérèse Portelance. Tangente ..............</t>
         </is>
       </c>
       <c r="R188" s="1" t="inlineStr"/>
@@ -9784,16 +8344,8 @@
       <c r="G189" s="1" t="inlineStr"/>
       <c r="H189" s="1" t="inlineStr"/>
       <c r="I189" s="1" t="inlineStr"/>
-      <c r="J189" s="1" t="inlineStr">
-        <is>
-          <t>L1384: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: me une voie ferrÃ©e. Aussi elle est pas-</t>
-        </is>
-      </c>
-      <c r="K189" s="1" t="inlineStr">
-        <is>
-          <t>L748: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Ronald Patry, Ã©cole Thibeault .....</t>
-        </is>
-      </c>
+      <c r="J189" s="1" t="inlineStr"/>
+      <c r="K189" s="1" t="inlineStr"/>
       <c r="L189" s="1" t="inlineStr"/>
       <c r="M189" s="1" t="inlineStr"/>
       <c r="N189" s="1" t="inlineStr">
@@ -9831,16 +8383,8 @@
       <c r="G190" s="1" t="inlineStr"/>
       <c r="H190" s="1" t="inlineStr"/>
       <c r="I190" s="1" t="inlineStr"/>
-      <c r="J190" s="1" t="inlineStr">
-        <is>
-          <t>L1387: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: " Lefebvre Ã© tait l'un des plus intr Ã© pi- d</t>
-        </is>
-      </c>
-      <c r="K190" s="1" t="inlineStr">
-        <is>
-          <t>L759: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Charles Bachand, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J190" s="1" t="inlineStr"/>
+      <c r="K190" s="1" t="inlineStr"/>
       <c r="L190" s="1" t="inlineStr"/>
       <c r="M190" s="1" t="inlineStr"/>
       <c r="N190" s="1" t="inlineStr">
@@ -9878,16 +8422,8 @@
       <c r="G191" s="1" t="inlineStr"/>
       <c r="H191" s="1" t="inlineStr"/>
       <c r="I191" s="1" t="inlineStr"/>
-      <c r="J191" s="1" t="inlineStr">
-        <is>
-          <t>L1388: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ses jambes. La diligence Ã© tait inconnue iti</t>
-        </is>
-      </c>
-      <c r="K191" s="1" t="inlineStr">
-        <is>
-          <t>L770: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 89 Roger Pariseau, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="J191" s="1" t="inlineStr"/>
+      <c r="K191" s="1" t="inlineStr"/>
       <c r="L191" s="1" t="inlineStr"/>
       <c r="M191" s="1" t="inlineStr"/>
       <c r="N191" s="1" t="inlineStr">
@@ -9903,7 +8439,7 @@
       <c r="P191" s="1" t="inlineStr"/>
       <c r="Q191" s="1" t="inlineStr">
         <is>
-          <t>L350: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marielle BÃ©land, Bonnyville ................</t>
+          <t>L350: punctuation artifact: repeated periods :: Marielle Béland, Bonnyville ................</t>
         </is>
       </c>
       <c r="R191" s="1" t="inlineStr"/>
@@ -9925,16 +8461,8 @@
       <c r="G192" s="1" t="inlineStr"/>
       <c r="H192" s="1" t="inlineStr"/>
       <c r="I192" s="1" t="inlineStr"/>
-      <c r="J192" s="1" t="inlineStr">
-        <is>
-          <t>L1390: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: lac Sup Ã© rieur." Les voyageurs ne pou-</t>
-        </is>
-      </c>
-      <c r="K192" s="1" t="inlineStr">
-        <is>
-          <t>L772: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Georges Bachand, Ã©cole Dunrobin.</t>
-        </is>
-      </c>
+      <c r="J192" s="1" t="inlineStr"/>
+      <c r="K192" s="1" t="inlineStr"/>
       <c r="L192" s="1" t="inlineStr"/>
       <c r="M192" s="1" t="inlineStr"/>
       <c r="N192" s="1" t="inlineStr">
@@ -9950,7 +8478,7 @@
       <c r="P192" s="1" t="inlineStr"/>
       <c r="Q192" s="1" t="inlineStr">
         <is>
-          <t>L352: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roger Thibault, Ã©cole consolidÃ©e, Donnelly ...</t>
+          <t>L352: punctuation artifact: repeated periods :: Roger Thibault, école consolidée, Donnelly ...</t>
         </is>
       </c>
       <c r="R192" s="1" t="inlineStr"/>
@@ -9972,16 +8500,8 @@
       <c r="G193" s="1" t="inlineStr"/>
       <c r="H193" s="1" t="inlineStr"/>
       <c r="I193" s="1" t="inlineStr"/>
-      <c r="J193" s="1" t="inlineStr">
-        <is>
-          <t>L1396: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: es les fatigues de la journ Ã© e. Parmi ceux</t>
-        </is>
-      </c>
-      <c r="K193" s="1" t="inlineStr">
-        <is>
-          <t>L774: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Robert Sabourin, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="J193" s="1" t="inlineStr"/>
+      <c r="K193" s="1" t="inlineStr"/>
       <c r="L193" s="1" t="inlineStr"/>
       <c r="M193" s="1" t="inlineStr"/>
       <c r="N193" s="1" t="inlineStr">
@@ -10019,16 +8539,8 @@
       <c r="G194" s="1" t="inlineStr"/>
       <c r="H194" s="1" t="inlineStr"/>
       <c r="I194" s="1" t="inlineStr"/>
-      <c r="J194" s="1" t="inlineStr">
-        <is>
-          <t>L1402: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: a son extraire habil Ã©. n m</t>
-        </is>
-      </c>
-      <c r="K194" s="1" t="inlineStr">
-        <is>
-          <t>L780: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Albert Anctil, Ã©cole Thibeault ...........</t>
-        </is>
-      </c>
+      <c r="J194" s="1" t="inlineStr"/>
+      <c r="K194" s="1" t="inlineStr"/>
       <c r="L194" s="1" t="inlineStr"/>
       <c r="M194" s="1" t="inlineStr"/>
       <c r="N194" s="1" t="inlineStr">
@@ -10044,7 +8556,7 @@
       <c r="P194" s="1" t="inlineStr"/>
       <c r="Q194" s="1" t="inlineStr">
         <is>
-          <t>L357: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ! Germaine Ethier, Ã©cole Thibault ..........</t>
+          <t>L357: punctuation artifact: repeated periods :: ! Germaine Ethier, école Thibault ..........</t>
         </is>
       </c>
       <c r="R194" s="1" t="inlineStr"/>
@@ -10066,16 +8578,8 @@
       <c r="G195" s="1" t="inlineStr"/>
       <c r="H195" s="1" t="inlineStr"/>
       <c r="I195" s="1" t="inlineStr"/>
-      <c r="J195" s="1" t="inlineStr">
-        <is>
-          <t>L1403: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Superior-City, dans lâ€™automne de</t>
-        </is>
-      </c>
-      <c r="K195" s="1" t="inlineStr">
-        <is>
-          <t>L781: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Georges ThÃ©berge, Legal</t>
-        </is>
-      </c>
+      <c r="J195" s="1" t="inlineStr"/>
+      <c r="K195" s="1" t="inlineStr"/>
       <c r="L195" s="1" t="inlineStr"/>
       <c r="M195" s="1" t="inlineStr"/>
       <c r="N195" s="1" t="inlineStr">
@@ -10091,7 +8595,7 @@
       <c r="P195" s="1" t="inlineStr"/>
       <c r="Q195" s="1" t="inlineStr">
         <is>
-          <t>L359: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: |Raymond Ouellette. ThÃ©rien Village........</t>
+          <t>L359: punctuation artifact: repeated periods :: |Raymond Ouellette. Thérien Village........</t>
         </is>
       </c>
       <c r="R195" s="1" t="inlineStr"/>
@@ -10113,16 +8617,8 @@
       <c r="G196" s="1" t="inlineStr"/>
       <c r="H196" s="1" t="inlineStr"/>
       <c r="I196" s="1" t="inlineStr"/>
-      <c r="J196" s="1" t="inlineStr">
-        <is>
-          <t>L1405: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN :: ç±³</t>
-        </is>
-      </c>
-      <c r="K196" s="1" t="inlineStr">
-        <is>
-          <t>L783: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Alice Aquin, Ã©cole Thibeault ................</t>
-        </is>
-      </c>
+      <c r="J196" s="1" t="inlineStr"/>
+      <c r="K196" s="1" t="inlineStr"/>
       <c r="L196" s="1" t="inlineStr"/>
       <c r="M196" s="1" t="inlineStr"/>
       <c r="N196" s="1" t="inlineStr">
@@ -10160,16 +8656,8 @@
       <c r="G197" s="1" t="inlineStr"/>
       <c r="H197" s="1" t="inlineStr"/>
       <c r="I197" s="1" t="inlineStr"/>
-      <c r="J197" s="1" t="inlineStr">
-        <is>
-          <t>L1407: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pierre M Ã© nard</t>
-        </is>
-      </c>
-      <c r="K197" s="1" t="inlineStr">
-        <is>
-          <t>L785: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: i Colette BÃ©dard, Tangente</t>
-        </is>
-      </c>
+      <c r="J197" s="1" t="inlineStr"/>
+      <c r="K197" s="1" t="inlineStr"/>
       <c r="L197" s="1" t="inlineStr"/>
       <c r="M197" s="1" t="inlineStr"/>
       <c r="N197" s="1" t="inlineStr">
@@ -10185,7 +8673,7 @@
       <c r="P197" s="1" t="inlineStr"/>
       <c r="Q197" s="1" t="inlineStr">
         <is>
-          <t>L363: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: | Madeleine Brissette, Ã©cole Grandin........</t>
+          <t>L363: punctuation artifact: repeated periods :: | Madeleine Brissette, école Grandin........</t>
         </is>
       </c>
       <c r="R197" s="1" t="inlineStr"/>
@@ -10207,16 +8695,8 @@
       <c r="G198" s="1" t="inlineStr"/>
       <c r="H198" s="1" t="inlineStr"/>
       <c r="I198" s="1" t="inlineStr"/>
-      <c r="J198" s="1" t="inlineStr">
-        <is>
-          <t>L1410: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: sont illustr Ã© s aux Etats-Unis, il</t>
-        </is>
-      </c>
-      <c r="K198" s="1" t="inlineStr">
-        <is>
-          <t>L873: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: JosÃ©phine L'Heureux, pensionnat de l'Assomption 51</t>
-        </is>
-      </c>
+      <c r="J198" s="1" t="inlineStr"/>
+      <c r="K198" s="1" t="inlineStr"/>
       <c r="L198" s="1" t="inlineStr"/>
       <c r="M198" s="1" t="inlineStr"/>
       <c r="N198" s="1" t="inlineStr">
@@ -10254,16 +8734,8 @@
       <c r="G199" s="1" t="inlineStr"/>
       <c r="H199" s="1" t="inlineStr"/>
       <c r="I199" s="1" t="inlineStr"/>
-      <c r="J199" s="1" t="inlineStr">
-        <is>
-          <t>L1412: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: M Ã© nard.</t>
-        </is>
-      </c>
-      <c r="K199" s="1" t="inlineStr">
-        <is>
-          <t>L877: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: LÃ©o Faucher, Saint-Paul ........................50</t>
-        </is>
-      </c>
+      <c r="J199" s="1" t="inlineStr"/>
+      <c r="K199" s="1" t="inlineStr"/>
       <c r="L199" s="1" t="inlineStr"/>
       <c r="M199" s="1" t="inlineStr"/>
       <c r="N199" s="1" t="inlineStr">
@@ -10301,16 +8773,8 @@
       <c r="G200" s="1" t="inlineStr"/>
       <c r="H200" s="1" t="inlineStr"/>
       <c r="I200" s="1" t="inlineStr"/>
-      <c r="J200" s="1" t="inlineStr">
-        <is>
-          <t>L1413: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Il naquit Ã Qu Ã© bec en 1767. A</t>
-        </is>
-      </c>
-      <c r="K200" s="1" t="inlineStr">
-        <is>
-          <t>L881: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Normand Maisonneuve, Ã©cole consolidÃ©e, Donnelly 50</t>
-        </is>
-      </c>
+      <c r="J200" s="1" t="inlineStr"/>
+      <c r="K200" s="1" t="inlineStr"/>
       <c r="L200" s="1" t="inlineStr"/>
       <c r="M200" s="1" t="inlineStr"/>
       <c r="N200" s="1" t="inlineStr">
@@ -10348,16 +8812,8 @@
       <c r="G201" s="1" t="inlineStr"/>
       <c r="H201" s="1" t="inlineStr"/>
       <c r="I201" s="1" t="inlineStr"/>
-      <c r="J201" s="1" t="inlineStr">
-        <is>
-          <t>L1415: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dans la soci Ã© t Ã© commerciale Lis</t>
-        </is>
-      </c>
-      <c r="K201" s="1" t="inlineStr">
-        <is>
-          <t>L954: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Laurette PrÃ©fentaine, Legal ........</t>
-        </is>
-      </c>
+      <c r="J201" s="1" t="inlineStr"/>
+      <c r="K201" s="1" t="inlineStr"/>
       <c r="L201" s="1" t="inlineStr"/>
       <c r="M201" s="1" t="inlineStr"/>
       <c r="N201" s="1" t="inlineStr">
@@ -10395,16 +8851,8 @@
       <c r="G202" s="1" t="inlineStr"/>
       <c r="H202" s="1" t="inlineStr"/>
       <c r="I202" s="1" t="inlineStr"/>
-      <c r="J202" s="1" t="inlineStr">
-        <is>
-          <t>L1416: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dont ies rations s 'Ã© tendaient</t>
-        </is>
-      </c>
-      <c r="K202" s="1" t="inlineStr">
-        <is>
-          <t>L964: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ferdinand Coulombe, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="J202" s="1" t="inlineStr"/>
+      <c r="K202" s="1" t="inlineStr"/>
       <c r="L202" s="1" t="inlineStr"/>
       <c r="M202" s="1" t="inlineStr"/>
       <c r="N202" s="1" t="inlineStr">
@@ -10442,16 +8890,8 @@
       <c r="G203" s="1" t="inlineStr"/>
       <c r="H203" s="1" t="inlineStr"/>
       <c r="I203" s="1" t="inlineStr"/>
-      <c r="J203" s="1" t="inlineStr">
-        <is>
-          <t>L1417: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: qu'aux Rocheuses. Nomm Ã© plus</t>
-        </is>
-      </c>
-      <c r="K203" s="1" t="inlineStr">
-        <is>
-          <t>L966: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Robert Despins, Ã©cole Dunrobin .......</t>
-        </is>
-      </c>
+      <c r="J203" s="1" t="inlineStr"/>
+      <c r="K203" s="1" t="inlineStr"/>
       <c r="L203" s="1" t="inlineStr"/>
       <c r="M203" s="1" t="inlineStr"/>
       <c r="N203" s="1" t="inlineStr">
@@ -10489,16 +8929,8 @@
       <c r="G204" s="1" t="inlineStr"/>
       <c r="H204" s="1" t="inlineStr"/>
       <c r="I204" s="1" t="inlineStr"/>
-      <c r="J204" s="1" t="inlineStr">
-        <is>
-          <t>L1419: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: des Etats-Unis, il r Ã© ussit a con</t>
-        </is>
-      </c>
-      <c r="K204" s="1" t="inlineStr">
-        <is>
-          <t>L972: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Huguette HÃ©tu. Bonnyville .....................</t>
-        </is>
-      </c>
+      <c r="J204" s="1" t="inlineStr"/>
+      <c r="K204" s="1" t="inlineStr"/>
       <c r="L204" s="1" t="inlineStr"/>
       <c r="M204" s="1" t="inlineStr"/>
       <c r="N204" s="1" t="inlineStr">
@@ -10536,16 +8968,8 @@
       <c r="G205" s="1" t="inlineStr"/>
       <c r="H205" s="1" t="inlineStr"/>
       <c r="I205" s="1" t="inlineStr"/>
-      <c r="J205" s="1" t="inlineStr">
-        <is>
-          <t>L1430: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: r Ã© e presque l Ã© gendaire jusqu</t>
-        </is>
-      </c>
-      <c r="K205" s="1" t="inlineStr">
-        <is>
-          <t>L974: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Doris Aubin, Ã©cole consolidÃ©e, Falher .........</t>
-        </is>
-      </c>
+      <c r="J205" s="1" t="inlineStr"/>
+      <c r="K205" s="1" t="inlineStr"/>
       <c r="L205" s="1" t="inlineStr"/>
       <c r="M205" s="1" t="inlineStr"/>
       <c r="N205" s="1" t="inlineStr">
@@ -10583,16 +9007,8 @@
       <c r="G206" s="1" t="inlineStr"/>
       <c r="H206" s="1" t="inlineStr"/>
       <c r="I206" s="1" t="inlineStr"/>
-      <c r="J206" s="1" t="inlineStr">
-        <is>
-          <t>L1431: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Parkman a d Ã© sign Ã© Pierre</t>
-        </is>
-      </c>
-      <c r="K206" s="1" t="inlineStr">
-        <is>
-          <t>L978: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rosemary Heppeler, Ã©cole Thibeault ............</t>
-        </is>
-      </c>
+      <c r="J206" s="1" t="inlineStr"/>
+      <c r="K206" s="1" t="inlineStr"/>
       <c r="L206" s="1" t="inlineStr"/>
       <c r="M206" s="1" t="inlineStr"/>
       <c r="N206" s="1" t="inlineStr">
@@ -10630,16 +9046,8 @@
       <c r="G207" s="1" t="inlineStr"/>
       <c r="H207" s="1" t="inlineStr"/>
       <c r="I207" s="1" t="inlineStr"/>
-      <c r="J207" s="1" t="inlineStr">
-        <is>
-          <t>L1432: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: s, comme " le v Ã© rable patriarche</t>
-        </is>
-      </c>
-      <c r="K207" s="1" t="inlineStr">
-        <is>
-          <t>L982: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roland BÃ©rubÃ©. Beaumont .......................</t>
-        </is>
-      </c>
+      <c r="J207" s="1" t="inlineStr"/>
+      <c r="K207" s="1" t="inlineStr"/>
       <c r="L207" s="1" t="inlineStr"/>
       <c r="M207" s="1" t="inlineStr"/>
       <c r="N207" s="1" t="inlineStr">
@@ -10677,16 +9085,8 @@
       <c r="G208" s="1" t="inlineStr"/>
       <c r="H208" s="1" t="inlineStr"/>
       <c r="I208" s="1" t="inlineStr"/>
-      <c r="J208" s="1" t="inlineStr">
-        <is>
-          <t>L1438: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Nous avons donn Ã©, la semaine der- munitionnaire des vivres pour l'armee</t>
-        </is>
-      </c>
-      <c r="K208" s="1" t="inlineStr">
-        <is>
-          <t>L984: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Claudette BÃ©rubÃ©, Beaumont ....................</t>
-        </is>
-      </c>
+      <c r="J208" s="1" t="inlineStr"/>
+      <c r="K208" s="1" t="inlineStr"/>
       <c r="L208" s="1" t="inlineStr"/>
       <c r="M208" s="1" t="inlineStr"/>
       <c r="N208" s="1" t="inlineStr">
@@ -10724,16 +9124,8 @@
       <c r="G209" s="1" t="inlineStr"/>
       <c r="H209" s="1" t="inlineStr"/>
       <c r="I209" s="1" t="inlineStr"/>
-      <c r="J209" s="1" t="inlineStr">
-        <is>
-          <t>L1443: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: nom, crit Tasse, mais l'ann Ã© e suivante, honneur a leur pays d'origine qu</t>
-        </is>
-      </c>
-      <c r="K209" s="1" t="inlineStr">
-        <is>
-          <t>L990: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: FranÃ§oise Turcotte, Ã©cole Grandin .............</t>
-        </is>
-      </c>
+      <c r="J209" s="1" t="inlineStr"/>
+      <c r="K209" s="1" t="inlineStr"/>
       <c r="L209" s="1" t="inlineStr"/>
       <c r="M209" s="1" t="inlineStr"/>
       <c r="N209" s="1" t="inlineStr">
@@ -10771,16 +9163,8 @@
       <c r="G210" s="1" t="inlineStr"/>
       <c r="H210" s="1" t="inlineStr"/>
       <c r="I210" s="1" t="inlineStr"/>
-      <c r="J210" s="1" t="inlineStr">
-        <is>
-          <t>L1445: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: qu'il s'agissait de porter des messages apr que l'on eut modifi Ã© sp Ã© c</t>
-        </is>
-      </c>
-      <c r="K210" s="1" t="inlineStr">
-        <is>
-          <t>L994: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Henri Roy, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="J210" s="1" t="inlineStr"/>
+      <c r="K210" s="1" t="inlineStr"/>
       <c r="L210" s="1" t="inlineStr"/>
       <c r="M210" s="1" t="inlineStr"/>
       <c r="N210" s="1" t="inlineStr">
@@ -10818,16 +9202,8 @@
       <c r="G211" s="1" t="inlineStr"/>
       <c r="H211" s="1" t="inlineStr"/>
       <c r="I211" s="1" t="inlineStr"/>
-      <c r="J211" s="1" t="inlineStr">
-        <is>
-          <t>L1449: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: - C'est que tous les quatre sont des les fatigues de la journÃ©e. Parmi ceux</t>
-        </is>
-      </c>
-      <c r="K211" s="1" t="inlineStr">
-        <is>
-          <t>L1002: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marcel Arcand, Ã©cole Grandin ..................</t>
-        </is>
-      </c>
+      <c r="J211" s="1" t="inlineStr"/>
+      <c r="K211" s="1" t="inlineStr"/>
       <c r="L211" s="1" t="inlineStr"/>
       <c r="M211" s="1" t="inlineStr"/>
       <c r="N211" s="1" t="inlineStr">
@@ -10865,16 +9241,8 @@
       <c r="G212" s="1" t="inlineStr"/>
       <c r="H212" s="1" t="inlineStr"/>
       <c r="I212" s="1" t="inlineStr"/>
-      <c r="J212" s="1" t="inlineStr">
-        <is>
-          <t>L1450: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: qui b Ã© neficierent de ses connaissances, comme " le v Ã© n Ã© rable patriarche</t>
-        </is>
-      </c>
-      <c r="K212" s="1" t="inlineStr">
-        <is>
-          <t>L1012: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Bernard HÃ©bert, Saint-Vincent .................</t>
-        </is>
-      </c>
+      <c r="J212" s="1" t="inlineStr"/>
+      <c r="K212" s="1" t="inlineStr"/>
       <c r="L212" s="1" t="inlineStr"/>
       <c r="M212" s="1" t="inlineStr"/>
       <c r="N212" s="1" t="inlineStr">
@@ -10912,16 +9280,8 @@
       <c r="G213" s="1" t="inlineStr"/>
       <c r="H213" s="1" t="inlineStr"/>
       <c r="I213" s="1" t="inlineStr"/>
-      <c r="J213" s="1" t="inlineStr">
-        <is>
-          <t>L1453: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: amÃ©ricain School-</t>
-        </is>
-      </c>
-      <c r="K213" s="1" t="inlineStr">
-        <is>
-          <t>L1014: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Tarcienne Meunier, Ã©cole Thibeault ............</t>
-        </is>
-      </c>
+      <c r="J213" s="1" t="inlineStr"/>
+      <c r="K213" s="1" t="inlineStr"/>
       <c r="L213" s="1" t="inlineStr"/>
       <c r="M213" s="1" t="inlineStr"/>
       <c r="N213" s="1" t="inlineStr">
@@ -10959,16 +9319,8 @@
       <c r="G214" s="1" t="inlineStr"/>
       <c r="H214" s="1" t="inlineStr"/>
       <c r="I214" s="1" t="inlineStr"/>
-      <c r="J214" s="1" t="inlineStr">
-        <is>
-          <t>L1454: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: pour p Ã© n Ã© trer au</t>
-        </is>
-      </c>
-      <c r="K214" s="1" t="inlineStr">
-        <is>
-          <t>L1024: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AdÃ©lard SÃ©guin, Bonnyville ....................</t>
-        </is>
-      </c>
+      <c r="J214" s="1" t="inlineStr"/>
+      <c r="K214" s="1" t="inlineStr"/>
       <c r="L214" s="1" t="inlineStr"/>
       <c r="M214" s="1" t="inlineStr"/>
       <c r="N214" s="1" t="inlineStr">
@@ -11006,16 +9358,8 @@
       <c r="G215" s="1" t="inlineStr"/>
       <c r="H215" s="1" t="inlineStr"/>
       <c r="I215" s="1" t="inlineStr"/>
-      <c r="J215" s="1" t="inlineStr">
-        <is>
-          <t>L1457: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN :: ne se tira que grÃ¢ce</t>
-        </is>
-      </c>
-      <c r="K215" s="1" t="inlineStr">
-        <is>
-          <t>L1026: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: RenÃ© Bruneau, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="J215" s="1" t="inlineStr"/>
+      <c r="K215" s="1" t="inlineStr"/>
       <c r="L215" s="1" t="inlineStr"/>
       <c r="M215" s="1" t="inlineStr"/>
       <c r="N215" s="1" t="inlineStr">
@@ -11053,16 +9397,8 @@
       <c r="G216" s="1" t="inlineStr"/>
       <c r="H216" s="1" t="inlineStr"/>
       <c r="I216" s="1" t="inlineStr"/>
-      <c r="J216" s="1" t="inlineStr">
-        <is>
-          <t>L1467: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: s s'Ã©tendaient jus-</t>
-        </is>
-      </c>
-      <c r="K216" s="1" t="inlineStr">
-        <is>
-          <t>L1028: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Carmen Tellier, Ã©cole Thibeault ...............</t>
-        </is>
-      </c>
+      <c r="J216" s="1" t="inlineStr"/>
+      <c r="K216" s="1" t="inlineStr"/>
       <c r="L216" s="1" t="inlineStr"/>
       <c r="M216" s="1" t="inlineStr"/>
       <c r="N216" s="1" t="inlineStr">
@@ -11100,16 +9436,8 @@
       <c r="G217" s="1" t="inlineStr"/>
       <c r="H217" s="1" t="inlineStr"/>
       <c r="I217" s="1" t="inlineStr"/>
-      <c r="J217" s="1" t="inlineStr">
-        <is>
-          <t>L1468: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: double/multiple hyphen :: ommÃ© plus tard a--</t>
-        </is>
-      </c>
-      <c r="K217" s="1" t="inlineStr">
-        <is>
-          <t>L1030: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Muriel Walker, Ã©cole Thibeault ...............</t>
-        </is>
-      </c>
+      <c r="J217" s="1" t="inlineStr"/>
+      <c r="K217" s="1" t="inlineStr"/>
       <c r="L217" s="1" t="inlineStr"/>
       <c r="M217" s="1" t="inlineStr"/>
       <c r="N217" s="1" t="inlineStr">
@@ -11147,16 +9475,8 @@
       <c r="G218" s="1" t="inlineStr"/>
       <c r="H218" s="1" t="inlineStr"/>
       <c r="I218" s="1" t="inlineStr"/>
-      <c r="J218" s="1" t="inlineStr">
-        <is>
-          <t>L1472: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: obtint un slÃ¨ge Ã la</t>
-        </is>
-      </c>
-      <c r="K218" s="1" t="inlineStr">
-        <is>
-          <t>L1036: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lilianne Sabourin, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="J218" s="1" t="inlineStr"/>
+      <c r="K218" s="1" t="inlineStr"/>
       <c r="L218" s="1" t="inlineStr"/>
       <c r="M218" s="1" t="inlineStr"/>
       <c r="N218" s="1" t="inlineStr">
@@ -11194,16 +9514,8 @@
       <c r="G219" s="1" t="inlineStr"/>
       <c r="H219" s="1" t="inlineStr"/>
       <c r="I219" s="1" t="inlineStr"/>
-      <c r="J219" s="1" t="inlineStr">
-        <is>
-          <t>L1474: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: nt comme pr Ã© sident</t>
-        </is>
-      </c>
-      <c r="K219" s="1" t="inlineStr">
-        <is>
-          <t>L1038: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Raymond PÃ©trin, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="J219" s="1" t="inlineStr"/>
+      <c r="K219" s="1" t="inlineStr"/>
       <c r="L219" s="1" t="inlineStr"/>
       <c r="M219" s="1" t="inlineStr"/>
       <c r="N219" s="1" t="inlineStr">
@@ -11241,16 +9553,8 @@
       <c r="G220" s="1" t="inlineStr"/>
       <c r="H220" s="1" t="inlineStr"/>
       <c r="I220" s="1" t="inlineStr"/>
-      <c r="J220" s="1" t="inlineStr">
-        <is>
-          <t>L1477: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: modifi Ã© sp Ã© cialement</t>
-        </is>
-      </c>
-      <c r="K220" s="1" t="inlineStr">
-        <is>
-          <t>L1042: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ©rard-Meunier, Ã©cole Thibeault ..</t>
-        </is>
-      </c>
+      <c r="J220" s="1" t="inlineStr"/>
+      <c r="K220" s="1" t="inlineStr"/>
       <c r="L220" s="1" t="inlineStr"/>
       <c r="M220" s="1" t="inlineStr"/>
       <c r="N220" s="1" t="inlineStr">
@@ -11288,16 +9592,8 @@
       <c r="G221" s="1" t="inlineStr"/>
       <c r="H221" s="1" t="inlineStr"/>
       <c r="I221" s="1" t="inlineStr"/>
-      <c r="J221" s="1" t="inlineStr">
-        <is>
-          <t>L1480: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ign Ã© Pierre M Ã© nard</t>
-        </is>
-      </c>
-      <c r="K221" s="1" t="inlineStr">
-        <is>
-          <t>L1081: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: GÃ©rard Sauvageau. Ã©cole consolidÃ©e, Falher ............71</t>
-        </is>
-      </c>
+      <c r="J221" s="1" t="inlineStr"/>
+      <c r="K221" s="1" t="inlineStr"/>
       <c r="L221" s="1" t="inlineStr"/>
       <c r="M221" s="1" t="inlineStr"/>
       <c r="N221" s="1" t="inlineStr">
@@ -11313,7 +9609,7 @@
       <c r="P221" s="1" t="inlineStr"/>
       <c r="Q221" s="1" t="inlineStr">
         <is>
-          <t>L452: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Albert Laplante, Ã©cole Dunrobin ............</t>
+          <t>L452: punctuation artifact: repeated periods :: Albert Laplante, école Dunrobin ............</t>
         </is>
       </c>
       <c r="R221" s="1" t="inlineStr"/>
@@ -11335,16 +9631,8 @@
       <c r="G222" s="1" t="inlineStr"/>
       <c r="H222" s="1" t="inlineStr"/>
       <c r="I222" s="1" t="inlineStr"/>
-      <c r="J222" s="1" t="inlineStr">
-        <is>
-          <t>L1484: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A2 CENT SIGN :: it su l'acqu Ã© rir grÃ¢ce</t>
-        </is>
-      </c>
-      <c r="K222" s="1" t="inlineStr">
-        <is>
-          <t>L1087: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Georges Voyer, Ã©cole Grandin ...........................70</t>
-        </is>
-      </c>
+      <c r="J222" s="1" t="inlineStr"/>
+      <c r="K222" s="1" t="inlineStr"/>
       <c r="L222" s="1" t="inlineStr"/>
       <c r="M222" s="1" t="inlineStr"/>
       <c r="N222" s="1" t="inlineStr">
@@ -11382,16 +9670,8 @@
       <c r="G223" s="1" t="inlineStr"/>
       <c r="H223" s="1" t="inlineStr"/>
       <c r="I223" s="1" t="inlineStr"/>
-      <c r="J223" s="1" t="inlineStr">
-        <is>
-          <t>L1488: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Une le Ã§ on de r Ã© alisme</t>
-        </is>
-      </c>
-      <c r="K223" s="1" t="inlineStr">
-        <is>
-          <t>L1095: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 7C (letter/digit mix) :: 89 Monique Roy. Ã©cole consolidÃ©e, Donnelly ............7C</t>
-        </is>
-      </c>
+      <c r="J223" s="1" t="inlineStr"/>
+      <c r="K223" s="1" t="inlineStr"/>
       <c r="L223" s="1" t="inlineStr"/>
       <c r="M223" s="1" t="inlineStr"/>
       <c r="N223" s="1" t="inlineStr">
@@ -11429,16 +9709,8 @@
       <c r="G224" s="1" t="inlineStr"/>
       <c r="H224" s="1" t="inlineStr"/>
       <c r="I224" s="1" t="inlineStr"/>
-      <c r="J224" s="1" t="inlineStr">
-        <is>
-          <t>L1493: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: pit. Le grand seigneur appr Ã© cia l'art:</t>
-        </is>
-      </c>
-      <c r="K224" s="1" t="inlineStr">
-        <is>
-          <t>L1097: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Raymond Labrecque, Ã©cole consolidÃ©e, Donnelly .........70</t>
-        </is>
-      </c>
+      <c r="J224" s="1" t="inlineStr"/>
+      <c r="K224" s="1" t="inlineStr"/>
       <c r="L224" s="1" t="inlineStr"/>
       <c r="M224" s="1" t="inlineStr"/>
       <c r="N224" s="1" t="inlineStr">
@@ -11476,16 +9748,8 @@
       <c r="G225" s="1" t="inlineStr"/>
       <c r="H225" s="1" t="inlineStr"/>
       <c r="I225" s="1" t="inlineStr"/>
-      <c r="J225" s="1" t="inlineStr">
-        <is>
-          <t>L1494: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de l'Italien; n Ã© anmoins, il releva un:</t>
-        </is>
-      </c>
-      <c r="K225" s="1" t="inlineStr">
-        <is>
-          <t>L1099: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Hector Huot, Ã©cole Dunrobin ............................70</t>
-        </is>
-      </c>
+      <c r="J225" s="1" t="inlineStr"/>
+      <c r="K225" s="1" t="inlineStr"/>
       <c r="L225" s="1" t="inlineStr"/>
       <c r="M225" s="1" t="inlineStr"/>
       <c r="N225" s="1" t="inlineStr">
@@ -11501,7 +9765,7 @@
       <c r="P225" s="1" t="inlineStr"/>
       <c r="Q225" s="1" t="inlineStr">
         <is>
-          <t>L468: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rita Guibault, ThÃ©rien Village ...................</t>
+          <t>L468: punctuation artifact: repeated periods :: Rita Guibault, Thérien Village ...................</t>
         </is>
       </c>
       <c r="R225" s="1" t="inlineStr"/>
@@ -11523,16 +9787,8 @@
       <c r="G226" s="1" t="inlineStr"/>
       <c r="H226" s="1" t="inlineStr"/>
       <c r="I226" s="1" t="inlineStr"/>
-      <c r="J226" s="1" t="inlineStr">
-        <is>
-          <t>L1495: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dÃ©faut qui le choquait: la pite sanglan-</t>
-        </is>
-      </c>
-      <c r="K226" s="1" t="inlineStr">
-        <is>
-          <t>L1101: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: GÃ©rard l'AbbÃ©, Ã©cole consolidÃ©e, Falher ................70</t>
-        </is>
-      </c>
+      <c r="J226" s="1" t="inlineStr"/>
+      <c r="K226" s="1" t="inlineStr"/>
       <c r="L226" s="1" t="inlineStr"/>
       <c r="M226" s="1" t="inlineStr"/>
       <c r="N226" s="1" t="inlineStr">
@@ -11570,16 +9826,8 @@
       <c r="G227" s="1" t="inlineStr"/>
       <c r="H227" s="1" t="inlineStr"/>
       <c r="I227" s="1" t="inlineStr"/>
-      <c r="J227" s="1" t="inlineStr">
-        <is>
-          <t>L1496: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: te n'Ã©tait pas telle qu'il fallait.</t>
-        </is>
-      </c>
-      <c r="K227" s="1" t="inlineStr">
-        <is>
-          <t>L1103: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Gilbert Proulx, Ã©cole consolidÃ©e, Falher ..............70</t>
-        </is>
-      </c>
+      <c r="J227" s="1" t="inlineStr"/>
+      <c r="K227" s="1" t="inlineStr"/>
       <c r="L227" s="1" t="inlineStr"/>
       <c r="M227" s="1" t="inlineStr"/>
       <c r="N227" s="1" t="inlineStr">
@@ -11595,7 +9843,7 @@
       <c r="P227" s="1" t="inlineStr"/>
       <c r="Q227" s="1" t="inlineStr">
         <is>
-          <t>L476: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeanne Charlier, Ã©cole Dunrobin ...................</t>
+          <t>L476: punctuation artifact: repeated periods :: Jeanne Charlier, école Dunrobin ...................</t>
         </is>
       </c>
       <c r="R227" s="1" t="inlineStr"/>
@@ -11617,16 +9865,8 @@
       <c r="G228" s="1" t="inlineStr"/>
       <c r="H228" s="1" t="inlineStr"/>
       <c r="I228" s="1" t="inlineStr"/>
-      <c r="J228" s="1" t="inlineStr">
-        <is>
-          <t>L1497: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A9 COPYRIGHT SIGN :: â€” Quand un homme est d Ã© capit Ã©, dit-</t>
-        </is>
-      </c>
-      <c r="K228" s="1" t="inlineStr">
-        <is>
-          <t>L1107: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Emma GagnÃ©, Sainte-Lina ................................70</t>
-        </is>
-      </c>
+      <c r="J228" s="1" t="inlineStr"/>
+      <c r="K228" s="1" t="inlineStr"/>
       <c r="L228" s="1" t="inlineStr"/>
       <c r="M228" s="1" t="inlineStr"/>
       <c r="N228" s="1" t="inlineStr">
@@ -11642,7 +9882,7 @@
       <c r="P228" s="1" t="inlineStr"/>
       <c r="Q228" s="1" t="inlineStr">
         <is>
-          <t>L478: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: FranÃ§oise Trottier, Ã©cole Thibeault ...............</t>
+          <t>L478: punctuation artifact: repeated periods :: Françoise Trottier, école Thibeault ...............</t>
         </is>
       </c>
       <c r="R228" s="1" t="inlineStr"/>
@@ -11664,16 +9904,8 @@
       <c r="G229" s="1" t="inlineStr"/>
       <c r="H229" s="1" t="inlineStr"/>
       <c r="I229" s="1" t="inlineStr"/>
-      <c r="J229" s="1" t="inlineStr">
-        <is>
-          <t>L1501: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: clave tomba et fut prÃ©sent a l'artiste</t>
-        </is>
-      </c>
-      <c r="K229" s="1" t="inlineStr">
-        <is>
-          <t>L1113: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: RenÃ© Despins, Ã©cole consolidÃ©e, Falher .................68</t>
-        </is>
-      </c>
+      <c r="J229" s="1" t="inlineStr"/>
+      <c r="K229" s="1" t="inlineStr"/>
       <c r="L229" s="1" t="inlineStr"/>
       <c r="M229" s="1" t="inlineStr"/>
       <c r="N229" s="1" t="inlineStr">
@@ -11689,7 +9921,7 @@
       <c r="P229" s="1" t="inlineStr"/>
       <c r="Q229" s="1" t="inlineStr">
         <is>
-          <t>L480: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marcelle BÃ©langer, Plamondon ......................</t>
+          <t>L480: punctuation artifact: repeated periods :: Marcelle Bélanger, Plamondon ......................</t>
         </is>
       </c>
       <c r="R229" s="1" t="inlineStr"/>
@@ -11711,16 +9943,8 @@
       <c r="G230" s="1" t="inlineStr"/>
       <c r="H230" s="1" t="inlineStr"/>
       <c r="I230" s="1" t="inlineStr"/>
-      <c r="J230" s="1" t="inlineStr">
-        <is>
-          <t>L1503: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Bellini fut tellement Ã© pouvant Ã©, qu'il</t>
-        </is>
-      </c>
-      <c r="K230" s="1" t="inlineStr">
-        <is>
-          <t>L1115: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roger Lauzon, Ã©cole consolidÃ©e, Falher .................68</t>
-        </is>
-      </c>
+      <c r="J230" s="1" t="inlineStr"/>
+      <c r="K230" s="1" t="inlineStr"/>
       <c r="L230" s="1" t="inlineStr"/>
       <c r="M230" s="1" t="inlineStr"/>
       <c r="N230" s="1" t="inlineStr">
@@ -11736,7 +9960,7 @@
       <c r="P230" s="1" t="inlineStr"/>
       <c r="Q230" s="1" t="inlineStr">
         <is>
-          <t>L482: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Elsie Loch, ThÃ©rien Village .......................</t>
+          <t>L482: punctuation artifact: repeated periods :: Elsie Loch, Thérien Village .......................</t>
         </is>
       </c>
       <c r="R230" s="1" t="inlineStr"/>
@@ -11758,16 +9982,8 @@
       <c r="G231" s="1" t="inlineStr"/>
       <c r="H231" s="1" t="inlineStr"/>
       <c r="I231" s="1" t="inlineStr"/>
-      <c r="J231" s="1" t="inlineStr">
-        <is>
-          <t>L1508: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dire autant que " tÃ©moin ", et pour avoir</t>
-        </is>
-      </c>
-      <c r="K231" s="1" t="inlineStr">
-        <is>
-          <t>L1268: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Denise Beauchamp, Ã©cole consolidÃ©e, Donnelly ......68</t>
-        </is>
-      </c>
+      <c r="J231" s="1" t="inlineStr"/>
+      <c r="K231" s="1" t="inlineStr"/>
       <c r="L231" s="1" t="inlineStr"/>
       <c r="M231" s="1" t="inlineStr"/>
       <c r="N231" s="1" t="inlineStr">
@@ -11805,16 +10021,8 @@
       <c r="G232" s="1" t="inlineStr"/>
       <c r="H232" s="1" t="inlineStr"/>
       <c r="I232" s="1" t="inlineStr"/>
-      <c r="J232" s="1" t="inlineStr">
-        <is>
-          <t>L1509: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ã© t Ã© tout tremp Ã© du sang des tiens,</t>
-        </is>
-      </c>
-      <c r="K232" s="1" t="inlineStr">
-        <is>
-          <t>L1270: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Emilia Collin, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="J232" s="1" t="inlineStr"/>
+      <c r="K232" s="1" t="inlineStr"/>
       <c r="L232" s="1" t="inlineStr"/>
       <c r="M232" s="1" t="inlineStr"/>
       <c r="N232" s="1" t="inlineStr">
@@ -11852,16 +10060,8 @@
       <c r="G233" s="1" t="inlineStr"/>
       <c r="H233" s="1" t="inlineStr"/>
       <c r="I233" s="1" t="inlineStr"/>
-      <c r="J233" s="1" t="inlineStr">
-        <is>
-          <t>L1512: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: " victimes ", quelquefois me trÃ¨s di-</t>
-        </is>
-      </c>
-      <c r="K233" s="1" t="inlineStr">
-        <is>
-          <t>L1272: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Fernande TieuliÃ©, Legal .................</t>
-        </is>
-      </c>
+      <c r="J233" s="1" t="inlineStr"/>
+      <c r="K233" s="1" t="inlineStr"/>
       <c r="L233" s="1" t="inlineStr"/>
       <c r="M233" s="1" t="inlineStr"/>
       <c r="N233" s="1" t="inlineStr">
@@ -11899,16 +10099,8 @@
       <c r="G234" s="1" t="inlineStr"/>
       <c r="H234" s="1" t="inlineStr"/>
       <c r="I234" s="1" t="inlineStr"/>
-      <c r="J234" s="1" t="inlineStr">
-        <is>
-          <t>L1513: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: gnes de piti Ã©; mais la v Ã© rit Ã© seule a des</t>
-        </is>
-      </c>
-      <c r="K234" s="1" t="inlineStr">
-        <is>
-          <t>L1274: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Guy Tessier, Ã©cole Grandin ..............</t>
-        </is>
-      </c>
+      <c r="J234" s="1" t="inlineStr"/>
+      <c r="K234" s="1" t="inlineStr"/>
       <c r="L234" s="1" t="inlineStr"/>
       <c r="M234" s="1" t="inlineStr"/>
       <c r="N234" s="1" t="inlineStr">
@@ -11946,16 +10138,8 @@
       <c r="G235" s="1" t="inlineStr"/>
       <c r="H235" s="1" t="inlineStr"/>
       <c r="I235" s="1" t="inlineStr"/>
-      <c r="J235" s="1" t="inlineStr">
-        <is>
-          <t>L1521: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: mort les autorit Ã© s avaient donn Ã© le nom</t>
-        </is>
-      </c>
-      <c r="K235" s="1" t="inlineStr">
-        <is>
-          <t>L1276: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jacques Voyer, Ã©cole Thibeault .........</t>
-        </is>
-      </c>
+      <c r="J235" s="1" t="inlineStr"/>
+      <c r="K235" s="1" t="inlineStr"/>
       <c r="L235" s="1" t="inlineStr"/>
       <c r="M235" s="1" t="inlineStr"/>
       <c r="N235" s="1" t="inlineStr">
@@ -11971,7 +10155,7 @@
       <c r="P235" s="1" t="inlineStr"/>
       <c r="Q235" s="1" t="inlineStr">
         <is>
-          <t>L498: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Georges Pilon, Ã©cole Grandin ......................</t>
+          <t>L498: punctuation artifact: repeated periods :: Georges Pilon, école Grandin ......................</t>
         </is>
       </c>
       <c r="R235" s="1" t="inlineStr"/>
@@ -11993,16 +10177,8 @@
       <c r="G236" s="1" t="inlineStr"/>
       <c r="H236" s="1" t="inlineStr"/>
       <c r="I236" s="1" t="inlineStr"/>
-      <c r="J236" s="1" t="inlineStr">
-        <is>
-          <t>L1522: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de M Ã© nard Ã l'un des comtes les plus</t>
-        </is>
-      </c>
-      <c r="K236" s="1" t="inlineStr">
-        <is>
-          <t>L1280: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: BÃ©atrice Hurtubise, Saint-Paul .......</t>
-        </is>
-      </c>
+      <c r="J236" s="1" t="inlineStr"/>
+      <c r="K236" s="1" t="inlineStr"/>
       <c r="L236" s="1" t="inlineStr"/>
       <c r="M236" s="1" t="inlineStr"/>
       <c r="N236" s="1" t="inlineStr">
@@ -12018,7 +10194,7 @@
       <c r="P236" s="1" t="inlineStr"/>
       <c r="Q236" s="1" t="inlineStr">
         <is>
-          <t>L500: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Henri VallÃ©e, Beaumont ............................</t>
+          <t>L500: punctuation artifact: repeated periods :: Henri Vallée, Beaumont ............................</t>
         </is>
       </c>
       <c r="R236" s="1" t="inlineStr"/>
@@ -12040,16 +10216,8 @@
       <c r="G237" s="1" t="inlineStr"/>
       <c r="H237" s="1" t="inlineStr"/>
       <c r="I237" s="1" t="inlineStr"/>
-      <c r="J237" s="1" t="inlineStr">
-        <is>
-          <t>L1526: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Loi sur la Taxation des Surplus de b Ã© n Ã© fices</t>
-        </is>
-      </c>
-      <c r="K237" s="1" t="inlineStr">
-        <is>
-          <t>L1290: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: !GÃ©rard Garand, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="J237" s="1" t="inlineStr"/>
+      <c r="K237" s="1" t="inlineStr"/>
       <c r="L237" s="1" t="inlineStr"/>
       <c r="M237" s="1" t="inlineStr"/>
       <c r="N237" s="1" t="inlineStr">
@@ -12087,16 +10255,8 @@
       <c r="G238" s="1" t="inlineStr"/>
       <c r="H238" s="1" t="inlineStr"/>
       <c r="I238" s="1" t="inlineStr"/>
-      <c r="J238" s="1" t="inlineStr">
-        <is>
-          <t>L1527: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Demgende concernant les b Ã© n Ã© fices normaux</t>
-        </is>
-      </c>
-      <c r="K238" s="1" t="inlineStr">
-        <is>
-          <t>L1292: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ...86 RÃ©al Demers, Beaumont..........................</t>
-        </is>
-      </c>
+      <c r="J238" s="1" t="inlineStr"/>
+      <c r="K238" s="1" t="inlineStr"/>
       <c r="L238" s="1" t="inlineStr"/>
       <c r="M238" s="1" t="inlineStr"/>
       <c r="N238" s="1" t="inlineStr">
@@ -12134,16 +10294,8 @@
       <c r="G239" s="1" t="inlineStr"/>
       <c r="H239" s="1" t="inlineStr"/>
       <c r="I239" s="1" t="inlineStr"/>
-      <c r="J239" s="1" t="inlineStr">
-        <is>
-          <t>L1529: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: De r Ã© centes modifications apport Ã© es a la loi ci-dessus</t>
-        </is>
-      </c>
-      <c r="K239" s="1" t="inlineStr">
-        <is>
-          <t>L1294: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Rita Beauchamp, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="J239" s="1" t="inlineStr"/>
+      <c r="K239" s="1" t="inlineStr"/>
       <c r="L239" s="1" t="inlineStr"/>
       <c r="M239" s="1" t="inlineStr"/>
       <c r="N239" s="1" t="inlineStr">
@@ -12181,16 +10333,8 @@
       <c r="G240" s="1" t="inlineStr"/>
       <c r="H240" s="1" t="inlineStr"/>
       <c r="I240" s="1" t="inlineStr"/>
-      <c r="J240" s="1" t="inlineStr">
-        <is>
-          <t>L1530: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: portent que toute demande concernant les b Ã© n Ã© fices</t>
-        </is>
-      </c>
-      <c r="K240" s="1" t="inlineStr">
-        <is>
-          <t>L1302: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ...861 Constant Maisonneuve, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="J240" s="1" t="inlineStr"/>
+      <c r="K240" s="1" t="inlineStr"/>
       <c r="L240" s="1" t="inlineStr"/>
       <c r="M240" s="1" t="inlineStr"/>
       <c r="N240" s="1" t="inlineStr">
@@ -12228,16 +10372,8 @@
       <c r="G241" s="1" t="inlineStr"/>
       <c r="H241" s="1" t="inlineStr"/>
       <c r="I241" s="1" t="inlineStr"/>
-      <c r="J241" s="1" t="inlineStr">
-        <is>
-          <t>L1540: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ment fÃ©dÃ©ral.</t>
-        </is>
-      </c>
-      <c r="K241" s="1" t="inlineStr">
-        <is>
-          <t>L1304: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ...86, Roland SÃ©guin, Ã©cole Dunrobin .................</t>
-        </is>
-      </c>
+      <c r="J241" s="1" t="inlineStr"/>
+      <c r="K241" s="1" t="inlineStr"/>
       <c r="L241" s="1" t="inlineStr"/>
       <c r="M241" s="1" t="inlineStr"/>
       <c r="N241" s="1" t="inlineStr">
@@ -12275,16 +10411,8 @@
       <c r="G242" s="1" t="inlineStr"/>
       <c r="H242" s="1" t="inlineStr"/>
       <c r="I242" s="1" t="inlineStr"/>
-      <c r="J242" s="1" t="inlineStr">
-        <is>
-          <t>L1541: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Les renseignements pertinents exig Ã© s dans la formule</t>
-        </is>
-      </c>
-      <c r="K242" s="1" t="inlineStr">
-        <is>
-          <t>L1310: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 86 RÃ©jeanne l'Oiseau, Ã©cole consolidÃ©e, Falher.</t>
-        </is>
-      </c>
+      <c r="J242" s="1" t="inlineStr"/>
+      <c r="K242" s="1" t="inlineStr"/>
       <c r="L242" s="1" t="inlineStr"/>
       <c r="M242" s="1" t="inlineStr"/>
       <c r="N242" s="1" t="inlineStr">
@@ -12300,7 +10428,7 @@
       <c r="P242" s="1" t="inlineStr"/>
       <c r="Q242" s="1" t="inlineStr">
         <is>
-          <t>L534: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©on Handfield, Beaumont ..........................</t>
+          <t>L534: punctuation artifact: repeated periods :: Léon Handfield, Beaumont ..........................</t>
         </is>
       </c>
       <c r="R242" s="1" t="inlineStr"/>
@@ -12322,16 +10450,8 @@
       <c r="G243" s="1" t="inlineStr"/>
       <c r="H243" s="1" t="inlineStr"/>
       <c r="I243" s="1" t="inlineStr"/>
-      <c r="J243" s="1" t="inlineStr">
-        <is>
-          <t>L1542: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: doivent tre inclus ou joints sous forme dâ€™annexe. Les</t>
-        </is>
-      </c>
-      <c r="K243" s="1" t="inlineStr">
-        <is>
-          <t>L1312: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 86Edouard (letter/digit mix) | localized OCR phrase divergence vs other OCR: "65 Edouard" vs "86Edouard" :: 86Edouard Garneau, Ã©cole Grandin ..........</t>
-        </is>
-      </c>
+      <c r="J243" s="1" t="inlineStr"/>
+      <c r="K243" s="1" t="inlineStr"/>
       <c r="L243" s="1" t="inlineStr"/>
       <c r="M243" s="1" t="inlineStr"/>
       <c r="N243" s="1" t="inlineStr">
@@ -12369,16 +10489,8 @@
       <c r="G244" s="1" t="inlineStr"/>
       <c r="H244" s="1" t="inlineStr"/>
       <c r="I244" s="1" t="inlineStr"/>
-      <c r="J244" s="1" t="inlineStr">
-        <is>
-          <t>L1543: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN, U+00A8 DIAERESIS :: formules dâ€™essai et les formules incompl Ã¨ tes, de me</t>
-        </is>
-      </c>
-      <c r="K244" s="1" t="inlineStr">
-        <is>
-          <t>L1376: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lorne BeauprÃ©, Bonnyville</t>
-        </is>
-      </c>
+      <c r="J244" s="1" t="inlineStr"/>
+      <c r="K244" s="1" t="inlineStr"/>
       <c r="L244" s="1" t="inlineStr"/>
       <c r="M244" s="1" t="inlineStr"/>
       <c r="N244" s="1" t="inlineStr">
@@ -12416,16 +10528,8 @@
       <c r="G245" s="1" t="inlineStr"/>
       <c r="H245" s="1" t="inlineStr"/>
       <c r="I245" s="1" t="inlineStr"/>
-      <c r="J245" s="1" t="inlineStr">
-        <is>
-          <t>L1545: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: accept Ã© es.</t>
-        </is>
-      </c>
-      <c r="K245" s="1" t="inlineStr">
-        <is>
-          <t>L1380: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Gertrude Brochu, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J245" s="1" t="inlineStr"/>
+      <c r="K245" s="1" t="inlineStr"/>
       <c r="L245" s="1" t="inlineStr"/>
       <c r="M245" s="1" t="inlineStr"/>
       <c r="N245" s="1" t="inlineStr">
@@ -12441,7 +10545,7 @@
       <c r="P245" s="1" t="inlineStr"/>
       <c r="Q245" s="1" t="inlineStr">
         <is>
-          <t>L542: punctuation artifact: repeated periods :: NoÃ«l Ouellette, Sainte-Lina .......................</t>
+          <t>L542: punctuation artifact: repeated periods :: Noël Ouellette, Sainte-Lina .......................</t>
         </is>
       </c>
       <c r="R245" s="1" t="inlineStr"/>
@@ -12463,16 +10567,8 @@
       <c r="G246" s="1" t="inlineStr"/>
       <c r="H246" s="1" t="inlineStr"/>
       <c r="I246" s="1" t="inlineStr"/>
-      <c r="J246" s="1" t="inlineStr">
-        <is>
-          <t>L1546: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: MinistÃ¨re</t>
-        </is>
-      </c>
-      <c r="K246" s="1" t="inlineStr">
-        <is>
-          <t>L1386: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ernest Aquin, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J246" s="1" t="inlineStr"/>
+      <c r="K246" s="1" t="inlineStr"/>
       <c r="L246" s="1" t="inlineStr"/>
       <c r="M246" s="1" t="inlineStr"/>
       <c r="N246" s="1" t="inlineStr">
@@ -12488,7 +10584,7 @@
       <c r="P246" s="1" t="inlineStr"/>
       <c r="Q246" s="1" t="inlineStr">
         <is>
-          <t>L546: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Paquette, Bonnyville ......................</t>
+          <t>L546: punctuation artifact: repeated periods :: Thérèse Paquette, Bonnyville ......................</t>
         </is>
       </c>
       <c r="R246" s="1" t="inlineStr"/>
@@ -12511,11 +10607,7 @@
       <c r="H247" s="1" t="inlineStr"/>
       <c r="I247" s="1" t="inlineStr"/>
       <c r="J247" s="1" t="inlineStr"/>
-      <c r="K247" s="1" t="inlineStr">
-        <is>
-          <t>L1394: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: : HÃ©lÃ¨ne Normand, ThÃ©rien Village ...............</t>
-        </is>
-      </c>
+      <c r="K247" s="1" t="inlineStr"/>
       <c r="L247" s="1" t="inlineStr"/>
       <c r="M247" s="1" t="inlineStr"/>
       <c r="N247" s="1" t="inlineStr">
@@ -12554,11 +10646,7 @@
       <c r="H248" s="1" t="inlineStr"/>
       <c r="I248" s="1" t="inlineStr"/>
       <c r="J248" s="1" t="inlineStr"/>
-      <c r="K248" s="1" t="inlineStr">
-        <is>
-          <t>L1396: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Robert BÃ©rubÃ©. Beaumont</t>
-        </is>
-      </c>
+      <c r="K248" s="1" t="inlineStr"/>
       <c r="L248" s="1" t="inlineStr"/>
       <c r="M248" s="1" t="inlineStr"/>
       <c r="N248" s="1" t="inlineStr">
@@ -12597,11 +10685,7 @@
       <c r="H249" s="1" t="inlineStr"/>
       <c r="I249" s="1" t="inlineStr"/>
       <c r="J249" s="1" t="inlineStr"/>
-      <c r="K249" s="1" t="inlineStr">
-        <is>
-          <t>L1398: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pierrette Lauzon, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="K249" s="1" t="inlineStr"/>
       <c r="L249" s="1" t="inlineStr"/>
       <c r="M249" s="1" t="inlineStr"/>
       <c r="N249" s="1" t="inlineStr">
@@ -12617,7 +10701,7 @@
       <c r="P249" s="1" t="inlineStr"/>
       <c r="Q249" s="1" t="inlineStr">
         <is>
-          <t>L552: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: PhilomÃ¨ne Frigon, Saint-Vincent ...................</t>
+          <t>L552: punctuation artifact: repeated periods :: Philomène Frigon, Saint-Vincent ...................</t>
         </is>
       </c>
       <c r="R249" s="1" t="inlineStr"/>
@@ -12640,11 +10724,7 @@
       <c r="H250" s="1" t="inlineStr"/>
       <c r="I250" s="1" t="inlineStr"/>
       <c r="J250" s="1" t="inlineStr"/>
-      <c r="K250" s="1" t="inlineStr">
-        <is>
-          <t>L1400: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: IrÃ¨ne Paul, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="K250" s="1" t="inlineStr"/>
       <c r="L250" s="1" t="inlineStr"/>
       <c r="M250" s="1" t="inlineStr"/>
       <c r="N250" s="1" t="inlineStr">
@@ -12660,7 +10740,7 @@
       <c r="P250" s="1" t="inlineStr"/>
       <c r="Q250" s="1" t="inlineStr">
         <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Alice Dame, Ã©cole Grandin .........................</t>
+          <t>L554: punctuation artifact: repeated periods :: Alice Dame, école Grandin .........................</t>
         </is>
       </c>
       <c r="R250" s="1" t="inlineStr"/>
@@ -12683,11 +10763,7 @@
       <c r="H251" s="1" t="inlineStr"/>
       <c r="I251" s="1" t="inlineStr"/>
       <c r="J251" s="1" t="inlineStr"/>
-      <c r="K251" s="1" t="inlineStr">
-        <is>
-          <t>L1404: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: GÃ©rald Lapointe, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="K251" s="1" t="inlineStr"/>
       <c r="L251" s="1" t="inlineStr"/>
       <c r="M251" s="1" t="inlineStr"/>
       <c r="N251" s="1" t="inlineStr">
@@ -12726,11 +10802,7 @@
       <c r="H252" s="1" t="inlineStr"/>
       <c r="I252" s="1" t="inlineStr"/>
       <c r="J252" s="1" t="inlineStr"/>
-      <c r="K252" s="1" t="inlineStr">
-        <is>
-          <t>L1410: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Maurier, Legal ...........................</t>
-        </is>
-      </c>
+      <c r="K252" s="1" t="inlineStr"/>
       <c r="L252" s="1" t="inlineStr"/>
       <c r="M252" s="1" t="inlineStr"/>
       <c r="N252" s="1" t="inlineStr">
@@ -12769,11 +10841,7 @@
       <c r="H253" s="1" t="inlineStr"/>
       <c r="I253" s="1" t="inlineStr"/>
       <c r="J253" s="1" t="inlineStr"/>
-      <c r="K253" s="1" t="inlineStr">
-        <is>
-          <t>L1412: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Rita TieuliÃ©, Legal</t>
-        </is>
-      </c>
+      <c r="K253" s="1" t="inlineStr"/>
       <c r="L253" s="1" t="inlineStr"/>
       <c r="M253" s="1" t="inlineStr"/>
       <c r="N253" s="1" t="inlineStr">
@@ -12812,11 +10880,7 @@
       <c r="H254" s="1" t="inlineStr"/>
       <c r="I254" s="1" t="inlineStr"/>
       <c r="J254" s="1" t="inlineStr"/>
-      <c r="K254" s="1" t="inlineStr">
-        <is>
-          <t>L1414: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: LÃ©on Schayes, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="K254" s="1" t="inlineStr"/>
       <c r="L254" s="1" t="inlineStr"/>
       <c r="M254" s="1" t="inlineStr"/>
       <c r="N254" s="1" t="inlineStr">
@@ -12832,7 +10896,7 @@
       <c r="P254" s="1" t="inlineStr"/>
       <c r="Q254" s="1" t="inlineStr">
         <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Alfred ThÃ©berge, Legal ............................</t>
+          <t>L564: punctuation artifact: repeated periods :: Alfred Théberge, Legal ............................</t>
         </is>
       </c>
       <c r="R254" s="1" t="inlineStr"/>
@@ -12855,11 +10919,7 @@
       <c r="H255" s="1" t="inlineStr"/>
       <c r="I255" s="1" t="inlineStr"/>
       <c r="J255" s="1" t="inlineStr"/>
-      <c r="K255" s="1" t="inlineStr">
-        <is>
-          <t>L1416: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© La Brie, Fort Kent .................</t>
-        </is>
-      </c>
+      <c r="K255" s="1" t="inlineStr"/>
       <c r="L255" s="1" t="inlineStr"/>
       <c r="M255" s="1" t="inlineStr"/>
       <c r="N255" s="1" t="inlineStr">
@@ -12875,7 +10935,7 @@
       <c r="P255" s="1" t="inlineStr"/>
       <c r="Q255" s="1" t="inlineStr">
         <is>
-          <t>L566: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Bonin, La Corey ............................</t>
+          <t>L566: punctuation artifact: repeated periods :: Cécile Bonin, La Corey ............................</t>
         </is>
       </c>
       <c r="R255" s="1" t="inlineStr"/>
@@ -12898,11 +10958,7 @@
       <c r="H256" s="1" t="inlineStr"/>
       <c r="I256" s="1" t="inlineStr"/>
       <c r="J256" s="1" t="inlineStr"/>
-      <c r="K256" s="1" t="inlineStr">
-        <is>
-          <t>L1418: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 86 : Pierre Despins, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="K256" s="1" t="inlineStr"/>
       <c r="L256" s="1" t="inlineStr"/>
       <c r="M256" s="1" t="inlineStr"/>
       <c r="N256" s="1" t="inlineStr">
@@ -12918,7 +10974,7 @@
       <c r="P256" s="1" t="inlineStr"/>
       <c r="Q256" s="1" t="inlineStr">
         <is>
-          <t>L568: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: I NoÃ«l ChÃ©nard, Tangente ........................</t>
+          <t>L568: punctuation artifact: repeated periods :: I Noël Chénard, Tangente ........................</t>
         </is>
       </c>
       <c r="R256" s="1" t="inlineStr"/>
@@ -12941,11 +10997,7 @@
       <c r="H257" s="1" t="inlineStr"/>
       <c r="I257" s="1" t="inlineStr"/>
       <c r="J257" s="1" t="inlineStr"/>
-      <c r="K257" s="1" t="inlineStr">
-        <is>
-          <t>L1442: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Claire Petersen, Ã©cole Grandin ................</t>
-        </is>
-      </c>
+      <c r="K257" s="1" t="inlineStr"/>
       <c r="L257" s="1" t="inlineStr"/>
       <c r="M257" s="1" t="inlineStr"/>
       <c r="N257" s="1" t="inlineStr">
@@ -12961,7 +11013,7 @@
       <c r="P257" s="1" t="inlineStr"/>
       <c r="Q257" s="1" t="inlineStr">
         <is>
-          <t>L570: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Anita St-Arneault, Ã©cole Grandin ................</t>
+          <t>L570: punctuation artifact: repeated periods :: Anita St-Arneault, école Grandin ................</t>
         </is>
       </c>
       <c r="R257" s="1" t="inlineStr"/>
@@ -12984,11 +11036,7 @@
       <c r="H258" s="1" t="inlineStr"/>
       <c r="I258" s="1" t="inlineStr"/>
       <c r="J258" s="1" t="inlineStr"/>
-      <c r="K258" s="1" t="inlineStr">
-        <is>
-          <t>L1446: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: CÃ©cile Isabel, Ã©cole consolidÃ©e, Falher ...........86</t>
-        </is>
-      </c>
+      <c r="K258" s="1" t="inlineStr"/>
       <c r="L258" s="1" t="inlineStr"/>
       <c r="M258" s="1" t="inlineStr"/>
       <c r="N258" s="1" t="inlineStr">
@@ -13004,7 +11052,7 @@
       <c r="P258" s="1" t="inlineStr"/>
       <c r="Q258" s="1" t="inlineStr">
         <is>
-          <t>L574: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lorette Tellier, Ã©cole Thibeault ................</t>
+          <t>L574: punctuation artifact: repeated periods :: Lorette Tellier, école Thibeault ................</t>
         </is>
       </c>
       <c r="R258" s="1" t="inlineStr"/>
@@ -13027,11 +11075,7 @@
       <c r="H259" s="1" t="inlineStr"/>
       <c r="I259" s="1" t="inlineStr"/>
       <c r="J259" s="1" t="inlineStr"/>
-      <c r="K259" s="1" t="inlineStr">
-        <is>
-          <t>L1448: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: CÃ©line Coulombe, Ã©cole Dunrobin 86</t>
-        </is>
-      </c>
+      <c r="K259" s="1" t="inlineStr"/>
       <c r="L259" s="1" t="inlineStr"/>
       <c r="M259" s="1" t="inlineStr"/>
       <c r="N259" s="1" t="inlineStr">
@@ -13070,11 +11114,7 @@
       <c r="H260" s="1" t="inlineStr"/>
       <c r="I260" s="1" t="inlineStr"/>
       <c r="J260" s="1" t="inlineStr"/>
-      <c r="K260" s="1" t="inlineStr">
-        <is>
-          <t>L1452: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Billy Dubois, Ã©cole Dunrobin ..............</t>
-        </is>
-      </c>
+      <c r="K260" s="1" t="inlineStr"/>
       <c r="L260" s="1" t="inlineStr"/>
       <c r="M260" s="1" t="inlineStr"/>
       <c r="N260" s="1" t="inlineStr">
@@ -13090,7 +11130,7 @@
       <c r="P260" s="1" t="inlineStr"/>
       <c r="Q260" s="1" t="inlineStr">
         <is>
-          <t>L580: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© BeauprÃ©, Bonnyville .......................</t>
+          <t>L580: punctuation artifact: repeated periods :: André Beaupré, Bonnyville .......................</t>
         </is>
       </c>
       <c r="R260" s="1" t="inlineStr"/>
@@ -13113,11 +11153,7 @@
       <c r="H261" s="1" t="inlineStr"/>
       <c r="I261" s="1" t="inlineStr"/>
       <c r="J261" s="1" t="inlineStr"/>
-      <c r="K261" s="1" t="inlineStr">
-        <is>
-          <t>L1453: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Jacques Johnson, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="K261" s="1" t="inlineStr"/>
       <c r="L261" s="1" t="inlineStr"/>
       <c r="M261" s="1" t="inlineStr"/>
       <c r="N261" s="1" t="inlineStr">
@@ -13156,11 +11192,7 @@
       <c r="H262" s="1" t="inlineStr"/>
       <c r="I262" s="1" t="inlineStr"/>
       <c r="J262" s="1" t="inlineStr"/>
-      <c r="K262" s="1" t="inlineStr">
-        <is>
-          <t>L1482: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©onard Rousseau, Ã©cole Thibeault ...........</t>
-        </is>
-      </c>
+      <c r="K262" s="1" t="inlineStr"/>
       <c r="L262" s="1" t="inlineStr"/>
       <c r="M262" s="1" t="inlineStr"/>
       <c r="N262" s="1" t="inlineStr">
@@ -13176,7 +11208,7 @@
       <c r="P262" s="1" t="inlineStr"/>
       <c r="Q262" s="1" t="inlineStr">
         <is>
-          <t>L586: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roland Carriere, Ã©cole Dunrobin .................</t>
+          <t>L586: punctuation artifact: repeated periods :: Roland Carriere, école Dunrobin .................</t>
         </is>
       </c>
       <c r="R262" s="1" t="inlineStr"/>
@@ -13199,11 +11231,7 @@
       <c r="H263" s="1" t="inlineStr"/>
       <c r="I263" s="1" t="inlineStr"/>
       <c r="J263" s="1" t="inlineStr"/>
-      <c r="K263" s="1" t="inlineStr">
-        <is>
-          <t>L1484: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Charles Ouellette, ThÃ©rien Village ..........</t>
-        </is>
-      </c>
+      <c r="K263" s="1" t="inlineStr"/>
       <c r="L263" s="1" t="inlineStr"/>
       <c r="M263" s="1" t="inlineStr"/>
       <c r="N263" s="1" t="inlineStr">
@@ -13219,7 +11247,7 @@
       <c r="P263" s="1" t="inlineStr"/>
       <c r="Q263" s="1" t="inlineStr">
         <is>
-          <t>L590: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: HervÃ© Ouellette, Sainte-Lina ....................</t>
+          <t>L590: punctuation artifact: repeated periods :: Hervé Ouellette, Sainte-Lina ....................</t>
         </is>
       </c>
       <c r="R263" s="1" t="inlineStr"/>
@@ -13242,11 +11270,7 @@
       <c r="H264" s="1" t="inlineStr"/>
       <c r="I264" s="1" t="inlineStr"/>
       <c r="J264" s="1" t="inlineStr"/>
-      <c r="K264" s="1" t="inlineStr">
-        <is>
-          <t>L1486: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Adonis Emard, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="K264" s="1" t="inlineStr"/>
       <c r="L264" s="1" t="inlineStr"/>
       <c r="M264" s="1" t="inlineStr"/>
       <c r="N264" s="1" t="inlineStr">
@@ -13285,11 +11309,7 @@
       <c r="H265" s="1" t="inlineStr"/>
       <c r="I265" s="1" t="inlineStr"/>
       <c r="J265" s="1" t="inlineStr"/>
-      <c r="K265" s="1" t="inlineStr">
-        <is>
-          <t>L1488: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lucien Gagnon, Ã©cole consolidÃ©e, Falher .....</t>
-        </is>
-      </c>
+      <c r="K265" s="1" t="inlineStr"/>
       <c r="L265" s="1" t="inlineStr"/>
       <c r="M265" s="1" t="inlineStr"/>
       <c r="N265" s="1" t="inlineStr">
@@ -13328,11 +11348,7 @@
       <c r="H266" s="1" t="inlineStr"/>
       <c r="I266" s="1" t="inlineStr"/>
       <c r="J266" s="1" t="inlineStr"/>
-      <c r="K266" s="1" t="inlineStr">
-        <is>
-          <t>L1490: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Annette Lessard, Ã©cole consolidÃ©e, Falher ...</t>
-        </is>
-      </c>
+      <c r="K266" s="1" t="inlineStr"/>
       <c r="L266" s="1" t="inlineStr"/>
       <c r="M266" s="1" t="inlineStr"/>
       <c r="N266" s="1" t="inlineStr">
@@ -13348,7 +11364,7 @@
       <c r="P266" s="1" t="inlineStr"/>
       <c r="Q266" s="1" t="inlineStr">
         <is>
-          <t>L604: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Philippe HÃ©bert, Saint-Vincent ..................</t>
+          <t>L604: punctuation artifact: repeated periods :: Philippe Hébert, Saint-Vincent ..................</t>
         </is>
       </c>
       <c r="R266" s="1" t="inlineStr"/>
@@ -13371,11 +11387,7 @@
       <c r="H267" s="1" t="inlineStr"/>
       <c r="I267" s="1" t="inlineStr"/>
       <c r="J267" s="1" t="inlineStr"/>
-      <c r="K267" s="1" t="inlineStr">
-        <is>
-          <t>L1498: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lilianne Doran, Ã©cole consolidÃ©e, Falher ....</t>
-        </is>
-      </c>
+      <c r="K267" s="1" t="inlineStr"/>
       <c r="L267" s="1" t="inlineStr"/>
       <c r="M267" s="1" t="inlineStr"/>
       <c r="N267" s="1" t="inlineStr">
@@ -13391,7 +11403,7 @@
       <c r="P267" s="1" t="inlineStr"/>
       <c r="Q267" s="1" t="inlineStr">
         <is>
-          <t>L606: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GisÃ¨le SÃ©guin, Bonnyville........................</t>
+          <t>L606: punctuation artifact: repeated periods :: Gisèle Séguin, Bonnyville........................</t>
         </is>
       </c>
       <c r="R267" s="1" t="inlineStr"/>
@@ -13414,11 +11426,7 @@
       <c r="H268" s="1" t="inlineStr"/>
       <c r="I268" s="1" t="inlineStr"/>
       <c r="J268" s="1" t="inlineStr"/>
-      <c r="K268" s="1" t="inlineStr">
-        <is>
-          <t>L1502: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se ChÃ©nard. Tangente ...................</t>
-        </is>
-      </c>
+      <c r="K268" s="1" t="inlineStr"/>
       <c r="L268" s="1" t="inlineStr"/>
       <c r="M268" s="1" t="inlineStr"/>
       <c r="N268" s="1" t="inlineStr">
@@ -13457,11 +11465,7 @@
       <c r="H269" s="1" t="inlineStr"/>
       <c r="I269" s="1" t="inlineStr"/>
       <c r="J269" s="1" t="inlineStr"/>
-      <c r="K269" s="1" t="inlineStr">
-        <is>
-          <t>L1505: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Fortin, Tangente..................</t>
-        </is>
-      </c>
+      <c r="K269" s="1" t="inlineStr"/>
       <c r="L269" s="1" t="inlineStr"/>
       <c r="M269" s="1" t="inlineStr"/>
       <c r="N269" s="1" t="inlineStr">
@@ -13477,7 +11481,7 @@
       <c r="P269" s="1" t="inlineStr"/>
       <c r="Q269" s="1" t="inlineStr">
         <is>
-          <t>L610: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: AdÃ¨le Couture, Bonnyville .......................</t>
+          <t>L610: punctuation artifact: repeated periods :: Adèle Couture, Bonnyville .......................</t>
         </is>
       </c>
       <c r="R269" s="1" t="inlineStr"/>
@@ -13500,11 +11504,7 @@
       <c r="H270" s="1" t="inlineStr"/>
       <c r="I270" s="1" t="inlineStr"/>
       <c r="J270" s="1" t="inlineStr"/>
-      <c r="K270" s="1" t="inlineStr">
-        <is>
-          <t>L1509: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roger BÃ©land, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="K270" s="1" t="inlineStr"/>
       <c r="L270" s="1" t="inlineStr"/>
       <c r="M270" s="1" t="inlineStr"/>
       <c r="N270" s="1" t="inlineStr">
@@ -13543,11 +11543,7 @@
       <c r="H271" s="1" t="inlineStr"/>
       <c r="I271" s="1" t="inlineStr"/>
       <c r="J271" s="1" t="inlineStr"/>
-      <c r="K271" s="1" t="inlineStr">
-        <is>
-          <t>L1513: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Michel Voyer, Ã©cole Grandin ................</t>
-        </is>
-      </c>
+      <c r="K271" s="1" t="inlineStr"/>
       <c r="L271" s="1" t="inlineStr"/>
       <c r="M271" s="1" t="inlineStr"/>
       <c r="N271" s="1" t="inlineStr">
@@ -13586,11 +11582,7 @@
       <c r="H272" s="1" t="inlineStr"/>
       <c r="I272" s="1" t="inlineStr"/>
       <c r="J272" s="1" t="inlineStr"/>
-      <c r="K272" s="1" t="inlineStr">
-        <is>
-          <t>L1515: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RomÃ©o BÃ©dard, Tangente .....................</t>
-        </is>
-      </c>
+      <c r="K272" s="1" t="inlineStr"/>
       <c r="L272" s="1" t="inlineStr"/>
       <c r="M272" s="1" t="inlineStr"/>
       <c r="N272" s="1" t="inlineStr">
@@ -13606,7 +11598,7 @@
       <c r="P272" s="1" t="inlineStr"/>
       <c r="Q272" s="1" t="inlineStr">
         <is>
-          <t>L621: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: â€¢ IrÃ¨ne Lambert, Bonnyville .....................</t>
+          <t>L621: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods | line starts with punctuation glued to text :: • Irène Lambert, Bonnyville .....................</t>
         </is>
       </c>
       <c r="R272" s="1" t="inlineStr"/>
@@ -13629,11 +11621,7 @@
       <c r="H273" s="1" t="inlineStr"/>
       <c r="I273" s="1" t="inlineStr"/>
       <c r="J273" s="1" t="inlineStr"/>
-      <c r="K273" s="1" t="inlineStr">
-        <is>
-          <t>L1520: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paul Boulet, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="K273" s="1" t="inlineStr"/>
       <c r="L273" s="1" t="inlineStr"/>
       <c r="M273" s="1" t="inlineStr"/>
       <c r="N273" s="1" t="inlineStr">
@@ -13649,7 +11637,7 @@
       <c r="P273" s="1" t="inlineStr"/>
       <c r="Q273" s="1" t="inlineStr">
         <is>
-          <t>L623: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 1C (letter/digit mix) :: 1CÃ©cile Lacombe, Bonnyville.................</t>
+          <t>L623: punctuation artifact: repeated periods | suspicious token(s): 1C (letter/digit mix) :: 1Cécile Lacombe, Bonnyville.................</t>
         </is>
       </c>
       <c r="R273" s="1" t="inlineStr"/>
@@ -13672,11 +11660,7 @@
       <c r="H274" s="1" t="inlineStr"/>
       <c r="I274" s="1" t="inlineStr"/>
       <c r="J274" s="1" t="inlineStr"/>
-      <c r="K274" s="1" t="inlineStr">
-        <is>
-          <t>L1565: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Madeleine GÃ©linas, pensionnat de l'Assomption</t>
-        </is>
-      </c>
+      <c r="K274" s="1" t="inlineStr"/>
       <c r="L274" s="1" t="inlineStr"/>
       <c r="M274" s="1" t="inlineStr"/>
       <c r="N274" s="1" t="inlineStr">
@@ -13715,11 +11699,7 @@
       <c r="H275" s="1" t="inlineStr"/>
       <c r="I275" s="1" t="inlineStr"/>
       <c r="J275" s="1" t="inlineStr"/>
-      <c r="K275" s="1" t="inlineStr">
-        <is>
-          <t>L1569: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lorraine BÃ©rubÃ©. Beaumont .......................</t>
-        </is>
-      </c>
+      <c r="K275" s="1" t="inlineStr"/>
       <c r="L275" s="1" t="inlineStr"/>
       <c r="M275" s="1" t="inlineStr"/>
       <c r="N275" s="1" t="inlineStr">
@@ -13758,11 +11738,7 @@
       <c r="H276" s="1" t="inlineStr"/>
       <c r="I276" s="1" t="inlineStr"/>
       <c r="J276" s="1" t="inlineStr"/>
-      <c r="K276" s="1" t="inlineStr">
-        <is>
-          <t>L1571: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Alberta LabontÃ©, Ã©cole Thibeault ................</t>
-        </is>
-      </c>
+      <c r="K276" s="1" t="inlineStr"/>
       <c r="L276" s="1" t="inlineStr"/>
       <c r="M276" s="1" t="inlineStr"/>
       <c r="N276" s="1" t="inlineStr">
@@ -13801,11 +11777,7 @@
       <c r="H277" s="1" t="inlineStr"/>
       <c r="I277" s="1" t="inlineStr"/>
       <c r="J277" s="1" t="inlineStr"/>
-      <c r="K277" s="1" t="inlineStr">
-        <is>
-          <t>L1573: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Fleurette Rousseau, Ã©cole Thibeault .............</t>
-        </is>
-      </c>
+      <c r="K277" s="1" t="inlineStr"/>
       <c r="L277" s="1" t="inlineStr"/>
       <c r="M277" s="1" t="inlineStr"/>
       <c r="N277" s="1" t="inlineStr">
@@ -13844,11 +11816,7 @@
       <c r="H278" s="1" t="inlineStr"/>
       <c r="I278" s="1" t="inlineStr"/>
       <c r="J278" s="1" t="inlineStr"/>
-      <c r="K278" s="1" t="inlineStr">
-        <is>
-          <t>L1577: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©ontine Aubin, Ã©cole consolidÃ©e, Falher ........</t>
-        </is>
-      </c>
+      <c r="K278" s="1" t="inlineStr"/>
       <c r="L278" s="1" t="inlineStr"/>
       <c r="M278" s="1" t="inlineStr"/>
       <c r="N278" s="1" t="inlineStr">
@@ -13864,7 +11832,7 @@
       <c r="P278" s="1" t="inlineStr"/>
       <c r="Q278" s="1" t="inlineStr">
         <is>
-          <t>L635: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ..61 i Vivianne Nobert, Ã©cole Dunrobin</t>
+          <t>L635: punctuation artifact: repeated periods :: ..61 i Vivianne Nobert, école Dunrobin</t>
         </is>
       </c>
       <c r="R278" s="1" t="inlineStr"/>
@@ -13887,11 +11855,7 @@
       <c r="H279" s="1" t="inlineStr"/>
       <c r="I279" s="1" t="inlineStr"/>
       <c r="J279" s="1" t="inlineStr"/>
-      <c r="K279" s="1" t="inlineStr">
-        <is>
-          <t>L1585: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: OrigÃ¨ne Caouette, Bonnyville ....................</t>
-        </is>
-      </c>
+      <c r="K279" s="1" t="inlineStr"/>
       <c r="L279" s="1" t="inlineStr"/>
       <c r="M279" s="1" t="inlineStr"/>
       <c r="N279" s="1" t="inlineStr">
@@ -13930,11 +11894,7 @@
       <c r="H280" s="1" t="inlineStr"/>
       <c r="I280" s="1" t="inlineStr"/>
       <c r="J280" s="1" t="inlineStr"/>
-      <c r="K280" s="1" t="inlineStr">
-        <is>
-          <t>L1587: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Etiennette SÃ©guin, Bonnyville ...................</t>
-        </is>
-      </c>
+      <c r="K280" s="1" t="inlineStr"/>
       <c r="L280" s="1" t="inlineStr"/>
       <c r="M280" s="1" t="inlineStr"/>
       <c r="N280" s="1" t="inlineStr">
@@ -13950,7 +11910,7 @@
       <c r="P280" s="1" t="inlineStr"/>
       <c r="Q280" s="1" t="inlineStr">
         <is>
-          <t>L645: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 581 AndrÃ© Bouchard, Tangente ..........</t>
+          <t>L645: punctuation artifact: repeated periods :: 581 André Bouchard, Tangente ..........</t>
         </is>
       </c>
       <c r="R280" s="1" t="inlineStr"/>
@@ -13973,11 +11933,7 @@
       <c r="H281" s="1" t="inlineStr"/>
       <c r="I281" s="1" t="inlineStr"/>
       <c r="J281" s="1" t="inlineStr"/>
-      <c r="K281" s="1" t="inlineStr">
-        <is>
-          <t>L1591: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ©e Meunier Ã©cole Thibeault ...................</t>
-        </is>
-      </c>
+      <c r="K281" s="1" t="inlineStr"/>
       <c r="L281" s="1" t="inlineStr"/>
       <c r="M281" s="1" t="inlineStr"/>
       <c r="N281" s="1" t="inlineStr">
@@ -14016,11 +11972,7 @@
       <c r="H282" s="1" t="inlineStr"/>
       <c r="I282" s="1" t="inlineStr"/>
       <c r="J282" s="1" t="inlineStr"/>
-      <c r="K282" s="1" t="inlineStr">
-        <is>
-          <t>L1593: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©vis Chiasson, Sainte-Lina .....................</t>
-        </is>
-      </c>
+      <c r="K282" s="1" t="inlineStr"/>
       <c r="L282" s="1" t="inlineStr"/>
       <c r="M282" s="1" t="inlineStr"/>
       <c r="N282" s="1" t="inlineStr">
@@ -14059,11 +12011,7 @@
       <c r="H283" s="1" t="inlineStr"/>
       <c r="I283" s="1" t="inlineStr"/>
       <c r="J283" s="1" t="inlineStr"/>
-      <c r="K283" s="1" t="inlineStr">
-        <is>
-          <t>L1595: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marcel Legris, Ã©cole Grandin ....................</t>
-        </is>
-      </c>
+      <c r="K283" s="1" t="inlineStr"/>
       <c r="L283" s="1" t="inlineStr"/>
       <c r="M283" s="1" t="inlineStr"/>
       <c r="N283" s="1" t="inlineStr">
@@ -14102,11 +12050,7 @@
       <c r="H284" s="1" t="inlineStr"/>
       <c r="I284" s="1" t="inlineStr"/>
       <c r="J284" s="1" t="inlineStr"/>
-      <c r="K284" s="1" t="inlineStr">
-        <is>
-          <t>L1601: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 64 Rose-Marie Aubert, ThÃ©rien ...................</t>
-        </is>
-      </c>
+      <c r="K284" s="1" t="inlineStr"/>
       <c r="L284" s="1" t="inlineStr"/>
       <c r="M284" s="1" t="inlineStr"/>
       <c r="N284" s="1" t="inlineStr">
@@ -14145,11 +12089,7 @@
       <c r="H285" s="1" t="inlineStr"/>
       <c r="I285" s="1" t="inlineStr"/>
       <c r="J285" s="1" t="inlineStr"/>
-      <c r="K285" s="1" t="inlineStr">
-        <is>
-          <t>L1603: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ,ThÃ©rÃ¨se Rochette. Tangente.................</t>
-        </is>
-      </c>
+      <c r="K285" s="1" t="inlineStr"/>
       <c r="L285" s="1" t="inlineStr"/>
       <c r="M285" s="1" t="inlineStr"/>
       <c r="N285" s="1" t="inlineStr">
@@ -14188,11 +12128,7 @@
       <c r="H286" s="1" t="inlineStr"/>
       <c r="I286" s="1" t="inlineStr"/>
       <c r="J286" s="1" t="inlineStr"/>
-      <c r="K286" s="1" t="inlineStr">
-        <is>
-          <t>L1605: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Lussier, Tangente......................</t>
-        </is>
-      </c>
+      <c r="K286" s="1" t="inlineStr"/>
       <c r="L286" s="1" t="inlineStr"/>
       <c r="M286" s="1" t="inlineStr"/>
       <c r="N286" s="1" t="inlineStr">
@@ -14231,11 +12167,7 @@
       <c r="H287" s="1" t="inlineStr"/>
       <c r="I287" s="1" t="inlineStr"/>
       <c r="J287" s="1" t="inlineStr"/>
-      <c r="K287" s="1" t="inlineStr">
-        <is>
-          <t>L1609: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ;ThÃ©rÃ¨se Gauthier, Plamondon................</t>
-        </is>
-      </c>
+      <c r="K287" s="1" t="inlineStr"/>
       <c r="L287" s="1" t="inlineStr"/>
       <c r="M287" s="1" t="inlineStr"/>
       <c r="N287" s="1" t="inlineStr">
@@ -14274,11 +12206,7 @@
       <c r="H288" s="1" t="inlineStr"/>
       <c r="I288" s="1" t="inlineStr"/>
       <c r="J288" s="1" t="inlineStr"/>
-      <c r="K288" s="1" t="inlineStr">
-        <is>
-          <t>L1613: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Elise Chartrand, Ã©cole Grandin .............</t>
-        </is>
-      </c>
+      <c r="K288" s="1" t="inlineStr"/>
       <c r="L288" s="1" t="inlineStr"/>
       <c r="M288" s="1" t="inlineStr"/>
       <c r="N288" s="1" t="inlineStr">
@@ -14317,11 +12245,7 @@
       <c r="H289" s="1" t="inlineStr"/>
       <c r="I289" s="1" t="inlineStr"/>
       <c r="J289" s="1" t="inlineStr"/>
-      <c r="K289" s="1" t="inlineStr">
-        <is>
-          <t>L1615: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RomÃ©o Dechaine, Sainte-Lina ................</t>
-        </is>
-      </c>
+      <c r="K289" s="1" t="inlineStr"/>
       <c r="L289" s="1" t="inlineStr"/>
       <c r="M289" s="1" t="inlineStr"/>
       <c r="N289" s="1" t="inlineStr">
@@ -14360,11 +12284,7 @@
       <c r="H290" s="1" t="inlineStr"/>
       <c r="I290" s="1" t="inlineStr"/>
       <c r="J290" s="1" t="inlineStr"/>
-      <c r="K290" s="1" t="inlineStr">
-        <is>
-          <t>L1617: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Bouchard, Tangente .................</t>
-        </is>
-      </c>
+      <c r="K290" s="1" t="inlineStr"/>
       <c r="L290" s="1" t="inlineStr"/>
       <c r="M290" s="1" t="inlineStr"/>
       <c r="N290" s="1" t="inlineStr">
@@ -14403,11 +12323,7 @@
       <c r="H291" s="1" t="inlineStr"/>
       <c r="I291" s="1" t="inlineStr"/>
       <c r="J291" s="1" t="inlineStr"/>
-      <c r="K291" s="1" t="inlineStr">
-        <is>
-          <t>L1623: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: Laurier CarriÃ¨re, Legal ....................</t>
-        </is>
-      </c>
+      <c r="K291" s="1" t="inlineStr"/>
       <c r="L291" s="1" t="inlineStr"/>
       <c r="M291" s="1" t="inlineStr"/>
       <c r="N291" s="1" t="inlineStr">
@@ -14446,11 +12362,7 @@
       <c r="H292" s="1" t="inlineStr"/>
       <c r="I292" s="1" t="inlineStr"/>
       <c r="J292" s="1" t="inlineStr"/>
-      <c r="K292" s="1" t="inlineStr">
-        <is>
-          <t>L1629: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Laurette Lafond, Ã©cole Thibeault ...........</t>
-        </is>
-      </c>
+      <c r="K292" s="1" t="inlineStr"/>
       <c r="L292" s="1" t="inlineStr"/>
       <c r="M292" s="1" t="inlineStr"/>
       <c r="N292" s="1" t="inlineStr">
@@ -14489,11 +12401,7 @@
       <c r="H293" s="1" t="inlineStr"/>
       <c r="I293" s="1" t="inlineStr"/>
       <c r="J293" s="1" t="inlineStr"/>
-      <c r="K293" s="1" t="inlineStr">
-        <is>
-          <t>L1631: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Doreen Stelte, Ã©cole Thibeault .............</t>
-        </is>
-      </c>
+      <c r="K293" s="1" t="inlineStr"/>
       <c r="L293" s="1" t="inlineStr"/>
       <c r="M293" s="1" t="inlineStr"/>
       <c r="N293" s="1" t="inlineStr">
@@ -14532,11 +12440,7 @@
       <c r="H294" s="1" t="inlineStr"/>
       <c r="I294" s="1" t="inlineStr"/>
       <c r="J294" s="1" t="inlineStr"/>
-      <c r="K294" s="1" t="inlineStr">
-        <is>
-          <t>L1635: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Magant, Sainte-Lina ......-</t>
-        </is>
-      </c>
+      <c r="K294" s="1" t="inlineStr"/>
       <c r="L294" s="1" t="inlineStr"/>
       <c r="M294" s="1" t="inlineStr"/>
       <c r="N294" s="1" t="inlineStr">
@@ -14575,11 +12479,7 @@
       <c r="H295" s="1" t="inlineStr"/>
       <c r="I295" s="1" t="inlineStr"/>
       <c r="J295" s="1" t="inlineStr"/>
-      <c r="K295" s="1" t="inlineStr">
-        <is>
-          <t>L1643: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RÃ©jeanne Rochette, Tangente ................</t>
-        </is>
-      </c>
+      <c r="K295" s="1" t="inlineStr"/>
       <c r="L295" s="1" t="inlineStr"/>
       <c r="M295" s="1" t="inlineStr"/>
       <c r="N295" s="1" t="inlineStr">
@@ -14618,11 +12518,7 @@
       <c r="H296" s="1" t="inlineStr"/>
       <c r="I296" s="1" t="inlineStr"/>
       <c r="J296" s="1" t="inlineStr"/>
-      <c r="K296" s="1" t="inlineStr">
-        <is>
-          <t>L1645: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: Rachel Ouellette, Tangente .............â€”...</t>
-        </is>
-      </c>
+      <c r="K296" s="1" t="inlineStr"/>
       <c r="L296" s="1" t="inlineStr"/>
       <c r="M296" s="1" t="inlineStr"/>
       <c r="N296" s="1" t="inlineStr">
@@ -14661,11 +12557,7 @@
       <c r="H297" s="1" t="inlineStr"/>
       <c r="I297" s="1" t="inlineStr"/>
       <c r="J297" s="1" t="inlineStr"/>
-      <c r="K297" s="1" t="inlineStr">
-        <is>
-          <t>L1647: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Albert Benoit, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="K297" s="1" t="inlineStr"/>
       <c r="L297" s="1" t="inlineStr"/>
       <c r="M297" s="1" t="inlineStr"/>
       <c r="N297" s="1" t="inlineStr">
@@ -14704,11 +12596,7 @@
       <c r="H298" s="1" t="inlineStr"/>
       <c r="I298" s="1" t="inlineStr"/>
       <c r="J298" s="1" t="inlineStr"/>
-      <c r="K298" s="1" t="inlineStr">
-        <is>
-          <t>L1649: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: Lucille LaverdiÃ¨re, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="K298" s="1" t="inlineStr"/>
       <c r="L298" s="1" t="inlineStr"/>
       <c r="M298" s="1" t="inlineStr"/>
       <c r="N298" s="1" t="inlineStr">
@@ -14747,11 +12635,7 @@
       <c r="H299" s="1" t="inlineStr"/>
       <c r="I299" s="1" t="inlineStr"/>
       <c r="J299" s="1" t="inlineStr"/>
-      <c r="K299" s="1" t="inlineStr">
-        <is>
-          <t>L1651: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marc Voyer, Ã©cole Grandin ..................</t>
-        </is>
-      </c>
+      <c r="K299" s="1" t="inlineStr"/>
       <c r="L299" s="1" t="inlineStr"/>
       <c r="M299" s="1" t="inlineStr"/>
       <c r="N299" s="1" t="inlineStr">
@@ -14790,11 +12674,7 @@
       <c r="H300" s="1" t="inlineStr"/>
       <c r="I300" s="1" t="inlineStr"/>
       <c r="J300" s="1" t="inlineStr"/>
-      <c r="K300" s="1" t="inlineStr">
-        <is>
-          <t>L1661: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Denise Despins, Ã©cole Dunrobin ..........................</t>
-        </is>
-      </c>
+      <c r="K300" s="1" t="inlineStr"/>
       <c r="L300" s="1" t="inlineStr"/>
       <c r="M300" s="1" t="inlineStr"/>
       <c r="N300" s="1" t="inlineStr">
@@ -14833,11 +12713,7 @@
       <c r="H301" s="1" t="inlineStr"/>
       <c r="I301" s="1" t="inlineStr"/>
       <c r="J301" s="1" t="inlineStr"/>
-      <c r="K301" s="1" t="inlineStr">
-        <is>
-          <t>L1663: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 82 Antonia Villeneuve, Ã©cole consolidÃ©e, Falher ........</t>
-        </is>
-      </c>
+      <c r="K301" s="1" t="inlineStr"/>
       <c r="L301" s="1" t="inlineStr"/>
       <c r="M301" s="1" t="inlineStr"/>
       <c r="N301" s="1" t="inlineStr">
@@ -14853,7 +12729,7 @@
       <c r="P301" s="1" t="inlineStr"/>
       <c r="Q301" s="1" t="inlineStr">
         <is>
-          <t>L696: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: EvangÃ©line Gillon, Tangente .................</t>
+          <t>L696: punctuation artifact: repeated periods :: Evangéline Gillon, Tangente .................</t>
         </is>
       </c>
       <c r="R301" s="1" t="inlineStr"/>
@@ -14876,11 +12752,7 @@
       <c r="H302" s="1" t="inlineStr"/>
       <c r="I302" s="1" t="inlineStr"/>
       <c r="J302" s="1" t="inlineStr"/>
-      <c r="K302" s="1" t="inlineStr">
-        <is>
-          <t>L1669: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: LÃ©o Cloutier, Tangente</t>
-        </is>
-      </c>
+      <c r="K302" s="1" t="inlineStr"/>
       <c r="L302" s="1" t="inlineStr"/>
       <c r="M302" s="1" t="inlineStr"/>
       <c r="N302" s="1" t="inlineStr">
@@ -14896,7 +12768,7 @@
       <c r="P302" s="1" t="inlineStr"/>
       <c r="Q302" s="1" t="inlineStr">
         <is>
-          <t>L698: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Euclide BÃ©rubÃ©, Beaumont .........</t>
+          <t>L698: punctuation artifact: repeated periods :: Euclide Bérubé, Beaumont .........</t>
         </is>
       </c>
       <c r="R302" s="1" t="inlineStr"/>
@@ -14919,11 +12791,7 @@
       <c r="H303" s="1" t="inlineStr"/>
       <c r="I303" s="1" t="inlineStr"/>
       <c r="J303" s="1" t="inlineStr"/>
-      <c r="K303" s="1" t="inlineStr">
-        <is>
-          <t>L1671: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Diane Ouellette, Ã©cole consolidÃ©e, Donnelly .............</t>
-        </is>
-      </c>
+      <c r="K303" s="1" t="inlineStr"/>
       <c r="L303" s="1" t="inlineStr"/>
       <c r="M303" s="1" t="inlineStr"/>
       <c r="N303" s="1" t="inlineStr">
@@ -14962,11 +12830,7 @@
       <c r="H304" s="1" t="inlineStr"/>
       <c r="I304" s="1" t="inlineStr"/>
       <c r="J304" s="1" t="inlineStr"/>
-      <c r="K304" s="1" t="inlineStr">
-        <is>
-          <t>L1678: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ....85 Denise Plaquin, ThÃ©rien:</t>
-        </is>
-      </c>
+      <c r="K304" s="1" t="inlineStr"/>
       <c r="L304" s="1" t="inlineStr"/>
       <c r="M304" s="1" t="inlineStr"/>
       <c r="N304" s="1" t="inlineStr">
@@ -14982,7 +12846,7 @@
       <c r="P304" s="1" t="inlineStr"/>
       <c r="Q304" s="1" t="inlineStr">
         <is>
-          <t>L704: punctuation artifact: repeated periods :: NoÃ«l Martel, La Corey........................</t>
+          <t>L704: punctuation artifact: repeated periods :: Noël Martel, La Corey........................</t>
         </is>
       </c>
       <c r="R304" s="1" t="inlineStr"/>
@@ -15005,11 +12869,7 @@
       <c r="H305" s="1" t="inlineStr"/>
       <c r="I305" s="1" t="inlineStr"/>
       <c r="J305" s="1" t="inlineStr"/>
-      <c r="K305" s="1" t="inlineStr">
-        <is>
-          <t>L1680: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 851 Lorraine Bachoffer, ThÃ©rien</t>
-        </is>
-      </c>
+      <c r="K305" s="1" t="inlineStr"/>
       <c r="L305" s="1" t="inlineStr"/>
       <c r="M305" s="1" t="inlineStr"/>
       <c r="N305" s="1" t="inlineStr">
@@ -15048,11 +12908,7 @@
       <c r="H306" s="1" t="inlineStr"/>
       <c r="I306" s="1" t="inlineStr"/>
       <c r="J306" s="1" t="inlineStr"/>
-      <c r="K306" s="1" t="inlineStr">
-        <is>
-          <t>L1686: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Claude BÃ©rubÃ©, Beaumont</t>
-        </is>
-      </c>
+      <c r="K306" s="1" t="inlineStr"/>
       <c r="L306" s="1" t="inlineStr"/>
       <c r="M306" s="1" t="inlineStr"/>
       <c r="N306" s="1" t="inlineStr">
@@ -15091,11 +12947,7 @@
       <c r="H307" s="1" t="inlineStr"/>
       <c r="I307" s="1" t="inlineStr"/>
       <c r="J307" s="1" t="inlineStr"/>
-      <c r="K307" s="1" t="inlineStr">
-        <is>
-          <t>L1687: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: HÃ©lÃ¨ne Chouinard, La Corey</t>
-        </is>
-      </c>
+      <c r="K307" s="1" t="inlineStr"/>
       <c r="L307" s="1" t="inlineStr"/>
       <c r="M307" s="1" t="inlineStr"/>
       <c r="N307" s="1" t="inlineStr">
@@ -15134,11 +12986,7 @@
       <c r="H308" s="1" t="inlineStr"/>
       <c r="I308" s="1" t="inlineStr"/>
       <c r="J308" s="1" t="inlineStr"/>
-      <c r="K308" s="1" t="inlineStr">
-        <is>
-          <t>L1694: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ©a Trudel, Saint-Paul ................</t>
-        </is>
-      </c>
+      <c r="K308" s="1" t="inlineStr"/>
       <c r="L308" s="1" t="inlineStr"/>
       <c r="M308" s="1" t="inlineStr"/>
       <c r="N308" s="1" t="inlineStr">
@@ -15177,11 +13025,7 @@
       <c r="H309" s="1" t="inlineStr"/>
       <c r="I309" s="1" t="inlineStr"/>
       <c r="J309" s="1" t="inlineStr"/>
-      <c r="K309" s="1" t="inlineStr">
-        <is>
-          <t>L1698: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Emile Isabel, Ã©cole consolidÃ©e, Falher ..</t>
-        </is>
-      </c>
+      <c r="K309" s="1" t="inlineStr"/>
       <c r="L309" s="1" t="inlineStr"/>
       <c r="M309" s="1" t="inlineStr"/>
       <c r="N309" s="1" t="inlineStr">
@@ -15220,11 +13064,7 @@
       <c r="H310" s="1" t="inlineStr"/>
       <c r="I310" s="1" t="inlineStr"/>
       <c r="J310" s="1" t="inlineStr"/>
-      <c r="K310" s="1" t="inlineStr">
-        <is>
-          <t>L1702: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lucien Gratton, ThÃ©rien Village .........</t>
-        </is>
-      </c>
+      <c r="K310" s="1" t="inlineStr"/>
       <c r="L310" s="1" t="inlineStr"/>
       <c r="M310" s="1" t="inlineStr"/>
       <c r="N310" s="1" t="inlineStr">
@@ -15240,7 +13080,7 @@
       <c r="P310" s="1" t="inlineStr"/>
       <c r="Q310" s="1" t="inlineStr">
         <is>
-          <t>L732: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Dolores Comeau, Ã©cole consolidÃ©e, Falher ....</t>
+          <t>L732: punctuation artifact: repeated periods :: Dolores Comeau, école consolidée, Falher ....</t>
         </is>
       </c>
       <c r="R310" s="1" t="inlineStr"/>
@@ -15263,11 +13103,7 @@
       <c r="H311" s="1" t="inlineStr"/>
       <c r="I311" s="1" t="inlineStr"/>
       <c r="J311" s="1" t="inlineStr"/>
-      <c r="K311" s="1" t="inlineStr">
-        <is>
-          <t>L1704: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lucien Fortier, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="K311" s="1" t="inlineStr"/>
       <c r="L311" s="1" t="inlineStr"/>
       <c r="M311" s="1" t="inlineStr"/>
       <c r="N311" s="1" t="inlineStr">
@@ -15306,11 +13142,7 @@
       <c r="H312" s="1" t="inlineStr"/>
       <c r="I312" s="1" t="inlineStr"/>
       <c r="J312" s="1" t="inlineStr"/>
-      <c r="K312" s="1" t="inlineStr">
-        <is>
-          <t>L1710: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lucille Fortier, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="K312" s="1" t="inlineStr"/>
       <c r="L312" s="1" t="inlineStr"/>
       <c r="M312" s="1" t="inlineStr"/>
       <c r="N312" s="1" t="inlineStr">
@@ -15326,7 +13158,7 @@
       <c r="P312" s="1" t="inlineStr"/>
       <c r="Q312" s="1" t="inlineStr">
         <is>
-          <t>L738: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Yolande Robert, Ã©cole Thibeault .............</t>
+          <t>L738: punctuation artifact: repeated periods :: Yolande Robert, école Thibeault .............</t>
         </is>
       </c>
       <c r="R312" s="1" t="inlineStr"/>
@@ -15349,11 +13181,7 @@
       <c r="H313" s="1" t="inlineStr"/>
       <c r="I313" s="1" t="inlineStr"/>
       <c r="J313" s="1" t="inlineStr"/>
-      <c r="K313" s="1" t="inlineStr">
-        <is>
-          <t>L1712: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lucien Roy, Ã©cole consolidÃ©e, Falher .....</t>
-        </is>
-      </c>
+      <c r="K313" s="1" t="inlineStr"/>
       <c r="L313" s="1" t="inlineStr"/>
       <c r="M313" s="1" t="inlineStr"/>
       <c r="N313" s="1" t="inlineStr">
@@ -15392,11 +13220,7 @@
       <c r="H314" s="1" t="inlineStr"/>
       <c r="I314" s="1" t="inlineStr"/>
       <c r="J314" s="1" t="inlineStr"/>
-      <c r="K314" s="1" t="inlineStr">
-        <is>
-          <t>L1784: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Claire HÃ©bert, Saint-Vincent ................,....99</t>
-        </is>
-      </c>
+      <c r="K314" s="1" t="inlineStr"/>
       <c r="L314" s="1" t="inlineStr"/>
       <c r="M314" s="1" t="inlineStr"/>
       <c r="N314" s="1" t="inlineStr">
@@ -15435,11 +13259,7 @@
       <c r="H315" s="1" t="inlineStr"/>
       <c r="I315" s="1" t="inlineStr"/>
       <c r="J315" s="1" t="inlineStr"/>
-      <c r="K315" s="1" t="inlineStr">
-        <is>
-          <t>L1786: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Bernard LavallÃ©e, Ã©cole Thibeault ................98</t>
-        </is>
-      </c>
+      <c r="K315" s="1" t="inlineStr"/>
       <c r="L315" s="1" t="inlineStr"/>
       <c r="M315" s="1" t="inlineStr"/>
       <c r="N315" s="1" t="inlineStr">
@@ -15455,7 +13275,7 @@
       <c r="P315" s="1" t="inlineStr"/>
       <c r="Q315" s="1" t="inlineStr">
         <is>
-          <t>L748: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Ronald Patry, Ã©cole Thibeault .....</t>
+          <t>L748: punctuation artifact: repeated periods :: Ronald Patry, école Thibeault .....</t>
         </is>
       </c>
       <c r="R315" s="1" t="inlineStr"/>
@@ -15478,11 +13298,7 @@
       <c r="H316" s="1" t="inlineStr"/>
       <c r="I316" s="1" t="inlineStr"/>
       <c r="J316" s="1" t="inlineStr"/>
-      <c r="K316" s="1" t="inlineStr">
-        <is>
-          <t>L1788: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Carole Lefebvre, Ã©cole Grandin ...................98</t>
-        </is>
-      </c>
+      <c r="K316" s="1" t="inlineStr"/>
       <c r="L316" s="1" t="inlineStr"/>
       <c r="M316" s="1" t="inlineStr"/>
       <c r="N316" s="1" t="inlineStr">
@@ -15521,11 +13337,7 @@
       <c r="H317" s="1" t="inlineStr"/>
       <c r="I317" s="1" t="inlineStr"/>
       <c r="J317" s="1" t="inlineStr"/>
-      <c r="K317" s="1" t="inlineStr">
-        <is>
-          <t>L1790: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Simonne LavallÃ©e, pensionnat de l'Assomption .....97</t>
-        </is>
-      </c>
+      <c r="K317" s="1" t="inlineStr"/>
       <c r="L317" s="1" t="inlineStr"/>
       <c r="M317" s="1" t="inlineStr"/>
       <c r="N317" s="1" t="inlineStr">
@@ -15564,11 +13376,7 @@
       <c r="H318" s="1" t="inlineStr"/>
       <c r="I318" s="1" t="inlineStr"/>
       <c r="J318" s="1" t="inlineStr"/>
-      <c r="K318" s="1" t="inlineStr">
-        <is>
-          <t>L1792: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Marie St-Arnaud, Ã©cole Dunrobin, Vimy 97</t>
-        </is>
-      </c>
+      <c r="K318" s="1" t="inlineStr"/>
       <c r="L318" s="1" t="inlineStr"/>
       <c r="M318" s="1" t="inlineStr"/>
       <c r="N318" s="1" t="inlineStr">
@@ -15584,7 +13392,7 @@
       <c r="P318" s="1" t="inlineStr"/>
       <c r="Q318" s="1" t="inlineStr">
         <is>
-          <t>L757: punctuation artifact: repeated periods :: Jean-Paul NoÃ«l. Saint-Paul .............</t>
+          <t>L757: punctuation artifact: repeated periods :: Jean-Paul Noël. Saint-Paul .............</t>
         </is>
       </c>
       <c r="R318" s="1" t="inlineStr"/>
@@ -15607,11 +13415,7 @@
       <c r="H319" s="1" t="inlineStr"/>
       <c r="I319" s="1" t="inlineStr"/>
       <c r="J319" s="1" t="inlineStr"/>
-      <c r="K319" s="1" t="inlineStr">
-        <is>
-          <t>L1798: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Une leÃ§on de rÃ©alisme</t>
-        </is>
-      </c>
+      <c r="K319" s="1" t="inlineStr"/>
       <c r="L319" s="1" t="inlineStr"/>
       <c r="M319" s="1" t="inlineStr"/>
       <c r="N319" s="1" t="inlineStr">
@@ -15650,11 +13454,7 @@
       <c r="H320" s="1" t="inlineStr"/>
       <c r="I320" s="1" t="inlineStr"/>
       <c r="J320" s="1" t="inlineStr"/>
-      <c r="K320" s="1" t="inlineStr">
-        <is>
-          <t>L1800: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Gentile Bellini, peintre vÃ©nitien, fut :</t>
-        </is>
-      </c>
+      <c r="K320" s="1" t="inlineStr"/>
       <c r="L320" s="1" t="inlineStr"/>
       <c r="M320" s="1" t="inlineStr"/>
       <c r="N320" s="1" t="inlineStr">
@@ -15693,11 +13493,7 @@
       <c r="H321" s="1" t="inlineStr"/>
       <c r="I321" s="1" t="inlineStr"/>
       <c r="J321" s="1" t="inlineStr"/>
-      <c r="K321" s="1" t="inlineStr">
-        <is>
-          <t>L1801: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: appelÃ© Ã Constantinople par Mahomet :</t>
-        </is>
-      </c>
+      <c r="K321" s="1" t="inlineStr"/>
       <c r="L321" s="1" t="inlineStr"/>
       <c r="M321" s="1" t="inlineStr"/>
       <c r="N321" s="1" t="inlineStr">
@@ -15736,11 +13532,7 @@
       <c r="H322" s="1" t="inlineStr"/>
       <c r="I322" s="1" t="inlineStr"/>
       <c r="J322" s="1" t="inlineStr"/>
-      <c r="K322" s="1" t="inlineStr">
-        <is>
-          <t>L1803: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: double/multiple hyphen :: tableau qui comportait un homme dÃ©ca--</t>
-        </is>
-      </c>
+      <c r="K322" s="1" t="inlineStr"/>
       <c r="L322" s="1" t="inlineStr"/>
       <c r="M322" s="1" t="inlineStr"/>
       <c r="N322" s="1" t="inlineStr">
@@ -15779,11 +13571,7 @@
       <c r="H323" s="1" t="inlineStr"/>
       <c r="I323" s="1" t="inlineStr"/>
       <c r="J323" s="1" t="inlineStr"/>
-      <c r="K323" s="1" t="inlineStr">
-        <is>
-          <t>L1804: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: pitÃ©. Le grand seigneur apprÃ©cia l'art</t>
-        </is>
-      </c>
+      <c r="K323" s="1" t="inlineStr"/>
       <c r="L323" s="1" t="inlineStr"/>
       <c r="M323" s="1" t="inlineStr"/>
       <c r="N323" s="1" t="inlineStr">
@@ -15799,7 +13587,7 @@
       <c r="P323" s="1" t="inlineStr"/>
       <c r="Q323" s="1" t="inlineStr">
         <is>
-          <t>L780: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Albert Anctil, Ã©cole Thibeault ...........</t>
+          <t>L780: punctuation artifact: repeated periods :: Albert Anctil, école Thibeault ...........</t>
         </is>
       </c>
       <c r="R323" s="1" t="inlineStr"/>
@@ -15822,11 +13610,7 @@
       <c r="H324" s="1" t="inlineStr"/>
       <c r="I324" s="1" t="inlineStr"/>
       <c r="J324" s="1" t="inlineStr"/>
-      <c r="K324" s="1" t="inlineStr">
-        <is>
-          <t>L1805: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de l'Italien; nÃ©anmoins, il releva un</t>
-        </is>
-      </c>
+      <c r="K324" s="1" t="inlineStr"/>
       <c r="L324" s="1" t="inlineStr"/>
       <c r="M324" s="1" t="inlineStr"/>
       <c r="N324" s="1" t="inlineStr">
@@ -15842,7 +13626,7 @@
       <c r="P324" s="1" t="inlineStr"/>
       <c r="Q324" s="1" t="inlineStr">
         <is>
-          <t>L783: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Alice Aquin, Ã©cole Thibeault ................</t>
+          <t>L783: punctuation artifact: repeated periods :: Alice Aquin, école Thibeault ................</t>
         </is>
       </c>
       <c r="R324" s="1" t="inlineStr"/>
@@ -15865,11 +13649,7 @@
       <c r="H325" s="1" t="inlineStr"/>
       <c r="I325" s="1" t="inlineStr"/>
       <c r="J325" s="1" t="inlineStr"/>
-      <c r="K325" s="1" t="inlineStr">
-        <is>
-          <t>L1806: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dÃ©faut qui le choquait: la tÃªte sanglan-</t>
-        </is>
-      </c>
+      <c r="K325" s="1" t="inlineStr"/>
       <c r="L325" s="1" t="inlineStr"/>
       <c r="M325" s="1" t="inlineStr"/>
       <c r="N325" s="1" t="inlineStr">
@@ -15908,11 +13688,7 @@
       <c r="H326" s="1" t="inlineStr"/>
       <c r="I326" s="1" t="inlineStr"/>
       <c r="J326" s="1" t="inlineStr"/>
-      <c r="K326" s="1" t="inlineStr">
-        <is>
-          <t>L1807: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: te n'Ã©tait pas telle qu'il fallait.</t>
-        </is>
-      </c>
+      <c r="K326" s="1" t="inlineStr"/>
       <c r="L326" s="1" t="inlineStr"/>
       <c r="M326" s="1" t="inlineStr"/>
       <c r="N326" s="1" t="inlineStr">
@@ -15951,11 +13727,7 @@
       <c r="H327" s="1" t="inlineStr"/>
       <c r="I327" s="1" t="inlineStr"/>
       <c r="J327" s="1" t="inlineStr"/>
-      <c r="K327" s="1" t="inlineStr">
-        <is>
-          <t>L1809: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A9 COPYRIGHT SIGN :: â€”Quand un homme est dÃ©capitÃ©, dit-1</t>
-        </is>
-      </c>
+      <c r="K327" s="1" t="inlineStr"/>
       <c r="L327" s="1" t="inlineStr"/>
       <c r="M327" s="1" t="inlineStr"/>
       <c r="N327" s="1" t="inlineStr">
@@ -15994,11 +13766,7 @@
       <c r="H328" s="1" t="inlineStr"/>
       <c r="I328" s="1" t="inlineStr"/>
       <c r="J328" s="1" t="inlineStr"/>
-      <c r="K328" s="1" t="inlineStr">
-        <is>
-          <t>L1814: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): l'artiste1 (letter/digit mix) :: clave tomba et fut prÃ©sentÃ©e Ã l'artiste1</t>
-        </is>
-      </c>
+      <c r="K328" s="1" t="inlineStr"/>
       <c r="L328" s="1" t="inlineStr"/>
       <c r="M328" s="1" t="inlineStr"/>
       <c r="N328" s="1" t="inlineStr">
@@ -16037,11 +13805,7 @@
       <c r="H329" s="1" t="inlineStr"/>
       <c r="I329" s="1" t="inlineStr"/>
       <c r="J329" s="1" t="inlineStr"/>
-      <c r="K329" s="1" t="inlineStr">
-        <is>
-          <t>L1815: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN :: pour qu'il l'examinÃ¢t.1</t>
-        </is>
-      </c>
+      <c r="K329" s="1" t="inlineStr"/>
       <c r="L329" s="1" t="inlineStr"/>
       <c r="M329" s="1" t="inlineStr"/>
       <c r="N329" s="1" t="inlineStr">
@@ -16080,11 +13844,7 @@
       <c r="H330" s="1" t="inlineStr"/>
       <c r="I330" s="1" t="inlineStr"/>
       <c r="J330" s="1" t="inlineStr"/>
-      <c r="K330" s="1" t="inlineStr">
-        <is>
-          <t>L1817: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Bellini fut tellement Ã©pouvantÃ©, qu'il!</t>
-        </is>
-      </c>
+      <c r="K330" s="1" t="inlineStr"/>
       <c r="L330" s="1" t="inlineStr"/>
       <c r="M330" s="1" t="inlineStr"/>
       <c r="N330" s="1" t="inlineStr">
@@ -16123,11 +13883,7 @@
       <c r="H331" s="1" t="inlineStr"/>
       <c r="I331" s="1" t="inlineStr"/>
       <c r="J331" s="1" t="inlineStr"/>
-      <c r="K331" s="1" t="inlineStr">
-        <is>
-          <t>L1819: stray/suspicious non-ASCII glyph(s): U+00AE REGISTERED SIGN :: promptement un tel maÃ®tre.</t>
-        </is>
-      </c>
+      <c r="K331" s="1" t="inlineStr"/>
       <c r="L331" s="1" t="inlineStr"/>
       <c r="M331" s="1" t="inlineStr"/>
       <c r="N331" s="1" t="inlineStr">
@@ -16166,11 +13922,7 @@
       <c r="H332" s="1" t="inlineStr"/>
       <c r="I332" s="1" t="inlineStr"/>
       <c r="J332" s="1" t="inlineStr"/>
-      <c r="K332" s="1" t="inlineStr">
-        <is>
-          <t>L1821: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: on classe l'historien amÃ©ricain School-</t>
-        </is>
-      </c>
+      <c r="K332" s="1" t="inlineStr"/>
       <c r="L332" s="1" t="inlineStr"/>
       <c r="M332" s="1" t="inlineStr"/>
       <c r="N332" s="1" t="inlineStr">
@@ -16186,7 +13938,7 @@
       <c r="P332" s="1" t="inlineStr"/>
       <c r="Q332" s="1" t="inlineStr">
         <is>
-          <t>L954: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Laurette PrÃ©fentaine, Legal ........</t>
+          <t>L954: punctuation artifact: repeated periods :: Laurette Préfentaine, Legal ........</t>
         </is>
       </c>
       <c r="R332" s="1" t="inlineStr"/>
@@ -16209,11 +13961,7 @@
       <c r="H333" s="1" t="inlineStr"/>
       <c r="I333" s="1" t="inlineStr"/>
       <c r="J333" s="1" t="inlineStr"/>
-      <c r="K333" s="1" t="inlineStr">
-        <is>
-          <t>L1822: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: craft, qui s'en servit pour pÃ©nÃ©trer au</t>
-        </is>
-      </c>
+      <c r="K333" s="1" t="inlineStr"/>
       <c r="L333" s="1" t="inlineStr"/>
       <c r="M333" s="1" t="inlineStr"/>
       <c r="N333" s="1" t="inlineStr">
@@ -16252,11 +14000,7 @@
       <c r="H334" s="1" t="inlineStr"/>
       <c r="I334" s="1" t="inlineStr"/>
       <c r="J334" s="1" t="inlineStr"/>
-      <c r="K334" s="1" t="inlineStr">
-        <is>
-          <t>L1823: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: coeur des tribus indiennes et les Ã©tudier</t>
-        </is>
-      </c>
+      <c r="K334" s="1" t="inlineStr"/>
       <c r="L334" s="1" t="inlineStr"/>
       <c r="M334" s="1" t="inlineStr"/>
       <c r="N334" s="1" t="inlineStr">
@@ -16295,11 +14039,7 @@
       <c r="H335" s="1" t="inlineStr"/>
       <c r="I335" s="1" t="inlineStr"/>
       <c r="J335" s="1" t="inlineStr"/>
-      <c r="K335" s="1" t="inlineStr">
-        <is>
-          <t>L1825: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN :: d'aventures, dont il ne se tira que grÃ¢ce</t>
-        </is>
-      </c>
+      <c r="K335" s="1" t="inlineStr"/>
       <c r="L335" s="1" t="inlineStr"/>
       <c r="M335" s="1" t="inlineStr"/>
       <c r="N335" s="1" t="inlineStr">
@@ -16338,11 +14078,7 @@
       <c r="H336" s="1" t="inlineStr"/>
       <c r="I336" s="1" t="inlineStr"/>
       <c r="J336" s="1" t="inlineStr"/>
-      <c r="K336" s="1" t="inlineStr">
-        <is>
-          <t>L1826: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ã son extrÃªme habiletÃ©. Il mourut Ã</t>
-        </is>
-      </c>
+      <c r="K336" s="1" t="inlineStr"/>
       <c r="L336" s="1" t="inlineStr"/>
       <c r="M336" s="1" t="inlineStr"/>
       <c r="N336" s="1" t="inlineStr">
@@ -16381,11 +14117,7 @@
       <c r="H337" s="1" t="inlineStr"/>
       <c r="I337" s="1" t="inlineStr"/>
       <c r="J337" s="1" t="inlineStr"/>
-      <c r="K337" s="1" t="inlineStr">
-        <is>
-          <t>L1831: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pierre MÃ©nard</t>
-        </is>
-      </c>
+      <c r="K337" s="1" t="inlineStr"/>
       <c r="L337" s="1" t="inlineStr"/>
       <c r="M337" s="1" t="inlineStr"/>
       <c r="N337" s="1" t="inlineStr">
@@ -16401,7 +14133,7 @@
       <c r="P337" s="1" t="inlineStr"/>
       <c r="Q337" s="1" t="inlineStr">
         <is>
-          <t>L966: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Robert Despins, Ã©cole Dunrobin .......</t>
+          <t>L966: punctuation artifact: repeated periods :: Robert Despins, école Dunrobin .......</t>
         </is>
       </c>
       <c r="R337" s="1" t="inlineStr"/>
@@ -16424,11 +14156,7 @@
       <c r="H338" s="1" t="inlineStr"/>
       <c r="I338" s="1" t="inlineStr"/>
       <c r="J338" s="1" t="inlineStr"/>
-      <c r="K338" s="1" t="inlineStr">
-        <is>
-          <t>L1839: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: des Canadiens franÃ§ais de lâ€™Alberta.</t>
-        </is>
-      </c>
+      <c r="K338" s="1" t="inlineStr"/>
       <c r="L338" s="1" t="inlineStr"/>
       <c r="M338" s="1" t="inlineStr"/>
       <c r="N338" s="1" t="inlineStr">
@@ -16467,11 +14195,7 @@
       <c r="H339" s="1" t="inlineStr"/>
       <c r="I339" s="1" t="inlineStr"/>
       <c r="J339" s="1" t="inlineStr"/>
-      <c r="K339" s="1" t="inlineStr">
-        <is>
-          <t>L1844: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Autre fondateur de ville amÃ©ricaine,</t>
-        </is>
-      </c>
+      <c r="K339" s="1" t="inlineStr"/>
       <c r="L339" s="1" t="inlineStr"/>
       <c r="M339" s="1" t="inlineStr"/>
       <c r="N339" s="1" t="inlineStr">
@@ -16510,11 +14234,7 @@
       <c r="H340" s="1" t="inlineStr"/>
       <c r="I340" s="1" t="inlineStr"/>
       <c r="J340" s="1" t="inlineStr"/>
-      <c r="K340" s="1" t="inlineStr">
-        <is>
-          <t>L1851: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: , 1 ents qui se rendaient a washing- te et finit par s'Ã©tablir, en 1853, Ã Supe-</t>
-        </is>
-      </c>
+      <c r="K340" s="1" t="inlineStr"/>
       <c r="L340" s="1" t="inlineStr"/>
       <c r="M340" s="1" t="inlineStr"/>
       <c r="N340" s="1" t="inlineStr">
@@ -16530,7 +14250,7 @@
       <c r="P340" s="1" t="inlineStr"/>
       <c r="Q340" s="1" t="inlineStr">
         <is>
-          <t>L972: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Huguette HÃ©tu. Bonnyville .....................</t>
+          <t>L972: punctuation artifact: repeated periods :: Huguette Hétu. Bonnyville .....................</t>
         </is>
       </c>
       <c r="R340" s="1" t="inlineStr"/>
@@ -16553,11 +14273,7 @@
       <c r="H341" s="1" t="inlineStr"/>
       <c r="I341" s="1" t="inlineStr"/>
       <c r="J341" s="1" t="inlineStr"/>
-      <c r="K341" s="1" t="inlineStr">
-        <is>
-          <t>L1852: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN :: ese comporta dans cette tÃ¢che en rior-City en compagnie de trois Cana-</t>
-        </is>
-      </c>
+      <c r="K341" s="1" t="inlineStr"/>
       <c r="L341" s="1" t="inlineStr"/>
       <c r="M341" s="1" t="inlineStr"/>
       <c r="N341" s="1" t="inlineStr">
@@ -16573,7 +14289,7 @@
       <c r="P341" s="1" t="inlineStr"/>
       <c r="Q341" s="1" t="inlineStr">
         <is>
-          <t>L974: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Doris Aubin, Ã©cole consolidÃ©e, Falher .........</t>
+          <t>L974: punctuation artifact: repeated periods :: Doris Aubin, école consolidée, Falher .........</t>
         </is>
       </c>
       <c r="R341" s="1" t="inlineStr"/>
@@ -16596,11 +14312,7 @@
       <c r="H342" s="1" t="inlineStr"/>
       <c r="I342" s="1" t="inlineStr"/>
       <c r="J342" s="1" t="inlineStr"/>
-      <c r="K342" s="1" t="inlineStr">
-        <is>
-          <t>L1853: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: vrai patriote et en serviteur fidÃ¨le de la diens: Basile Saint-Denis, FranÃ§ois Roy</t>
-        </is>
-      </c>
+      <c r="K342" s="1" t="inlineStr"/>
       <c r="L342" s="1" t="inlineStr"/>
       <c r="M342" s="1" t="inlineStr"/>
       <c r="N342" s="1" t="inlineStr">
@@ -16639,11 +14351,7 @@
       <c r="H343" s="1" t="inlineStr"/>
       <c r="I343" s="1" t="inlineStr"/>
       <c r="J343" s="1" t="inlineStr"/>
-      <c r="K343" s="1" t="inlineStr">
-        <is>
-          <t>L1854: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: patrie. On affirme, en effet, quâ€™il ne et Jean-Baptiste Samt-Jean.</t>
-        </is>
-      </c>
+      <c r="K343" s="1" t="inlineStr"/>
       <c r="L343" s="1" t="inlineStr"/>
       <c r="M343" s="1" t="inlineStr"/>
       <c r="N343" s="1" t="inlineStr">
@@ -16659,7 +14367,7 @@
       <c r="P343" s="1" t="inlineStr"/>
       <c r="Q343" s="1" t="inlineStr">
         <is>
-          <t>L978: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rosemary Heppeler, Ã©cole Thibeault ............</t>
+          <t>L978: punctuation artifact: repeated periods :: Rosemary Heppeler, école Thibeault ............</t>
         </is>
       </c>
       <c r="R343" s="1" t="inlineStr"/>
@@ -16682,11 +14390,7 @@
       <c r="H344" s="1" t="inlineStr"/>
       <c r="I344" s="1" t="inlineStr"/>
       <c r="J344" s="1" t="inlineStr"/>
-      <c r="K344" s="1" t="inlineStr">
-        <is>
-          <t>L1856: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: vres avec l'Etat. Il est vrai que ce n'Ã©tait</t>
-        </is>
-      </c>
+      <c r="K344" s="1" t="inlineStr"/>
       <c r="L344" s="1" t="inlineStr"/>
       <c r="M344" s="1" t="inlineStr"/>
       <c r="N344" s="1" t="inlineStr">
@@ -16725,11 +14429,7 @@
       <c r="H345" s="1" t="inlineStr"/>
       <c r="I345" s="1" t="inlineStr"/>
       <c r="J345" s="1" t="inlineStr"/>
-      <c r="K345" s="1" t="inlineStr">
-        <is>
-          <t>L1859: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Loi sur la Taxation des Surplus de bÃ©nÃ©fices</t>
-        </is>
-      </c>
+      <c r="K345" s="1" t="inlineStr"/>
       <c r="L345" s="1" t="inlineStr"/>
       <c r="M345" s="1" t="inlineStr"/>
       <c r="N345" s="1" t="inlineStr">
@@ -16745,7 +14445,7 @@
       <c r="P345" s="1" t="inlineStr"/>
       <c r="Q345" s="1" t="inlineStr">
         <is>
-          <t>L982: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roland BÃ©rubÃ©. Beaumont .......................</t>
+          <t>L982: punctuation artifact: repeated periods :: Roland Bérubé. Beaumont .......................</t>
         </is>
       </c>
       <c r="R345" s="1" t="inlineStr"/>
@@ -16768,11 +14468,7 @@
       <c r="H346" s="1" t="inlineStr"/>
       <c r="I346" s="1" t="inlineStr"/>
       <c r="J346" s="1" t="inlineStr"/>
-      <c r="K346" s="1" t="inlineStr">
-        <is>
-          <t>L1860: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Demande concernant les bÃ©nÃ©fices normaux</t>
-        </is>
-      </c>
+      <c r="K346" s="1" t="inlineStr"/>
       <c r="L346" s="1" t="inlineStr"/>
       <c r="M346" s="1" t="inlineStr"/>
       <c r="N346" s="1" t="inlineStr">
@@ -16788,7 +14484,7 @@
       <c r="P346" s="1" t="inlineStr"/>
       <c r="Q346" s="1" t="inlineStr">
         <is>
-          <t>L984: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Claudette BÃ©rubÃ©, Beaumont ....................</t>
+          <t>L984: punctuation artifact: repeated periods :: Claudette Bérubé, Beaumont ....................</t>
         </is>
       </c>
       <c r="R346" s="1" t="inlineStr"/>
@@ -16811,11 +14507,7 @@
       <c r="H347" s="1" t="inlineStr"/>
       <c r="I347" s="1" t="inlineStr"/>
       <c r="J347" s="1" t="inlineStr"/>
-      <c r="K347" s="1" t="inlineStr">
-        <is>
-          <t>L1862: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: munitionnaire des vivres pour l'armÃ©e</t>
-        </is>
-      </c>
+      <c r="K347" s="1" t="inlineStr"/>
       <c r="L347" s="1" t="inlineStr"/>
       <c r="M347" s="1" t="inlineStr"/>
       <c r="N347" s="1" t="inlineStr">
@@ -16854,11 +14546,7 @@
       <c r="H348" s="1" t="inlineStr"/>
       <c r="I348" s="1" t="inlineStr"/>
       <c r="J348" s="1" t="inlineStr"/>
-      <c r="K348" s="1" t="inlineStr">
-        <is>
-          <t>L1864: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: rÃ©guliÃ¨re. Il suivit, en cette qualitÃ©, les</t>
-        </is>
-      </c>
+      <c r="K348" s="1" t="inlineStr"/>
       <c r="L348" s="1" t="inlineStr"/>
       <c r="M348" s="1" t="inlineStr"/>
       <c r="N348" s="1" t="inlineStr">
@@ -16897,11 +14585,7 @@
       <c r="H349" s="1" t="inlineStr"/>
       <c r="I349" s="1" t="inlineStr"/>
       <c r="J349" s="1" t="inlineStr"/>
-      <c r="K349" s="1" t="inlineStr">
-        <is>
-          <t>L1867: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Nous avons donnÃ©, la semaine der-</t>
-        </is>
-      </c>
+      <c r="K349" s="1" t="inlineStr"/>
       <c r="L349" s="1" t="inlineStr"/>
       <c r="M349" s="1" t="inlineStr"/>
       <c r="N349" s="1" t="inlineStr">
@@ -16917,7 +14601,7 @@
       <c r="P349" s="1" t="inlineStr"/>
       <c r="Q349" s="1" t="inlineStr">
         <is>
-          <t>L990: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: FranÃ§oise Turcotte, Ã©cole Grandin .............</t>
+          <t>L990: punctuation artifact: repeated periods :: Françoise Turcotte, école Grandin .............</t>
         </is>
       </c>
       <c r="R349" s="1" t="inlineStr"/>
@@ -16940,11 +14624,7 @@
       <c r="H350" s="1" t="inlineStr"/>
       <c r="I350" s="1" t="inlineStr"/>
       <c r="J350" s="1" t="inlineStr"/>
-      <c r="K350" s="1" t="inlineStr">
-        <is>
-          <t>L1868: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: miÃ¨re, une courte biographie de trois</t>
-        </is>
-      </c>
+      <c r="K350" s="1" t="inlineStr"/>
       <c r="L350" s="1" t="inlineStr"/>
       <c r="M350" s="1" t="inlineStr"/>
       <c r="N350" s="1" t="inlineStr">
@@ -16983,11 +14663,7 @@
       <c r="H351" s="1" t="inlineStr"/>
       <c r="I351" s="1" t="inlineStr"/>
       <c r="J351" s="1" t="inlineStr"/>
-      <c r="K351" s="1" t="inlineStr">
-        <is>
-          <t>L1869: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT, U+00A9 COPYRIGHT SIGN :: des nÃ´tres qui ont fondÃ© des villes aux</t>
-        </is>
-      </c>
+      <c r="K351" s="1" t="inlineStr"/>
       <c r="L351" s="1" t="inlineStr"/>
       <c r="M351" s="1" t="inlineStr"/>
       <c r="N351" s="1" t="inlineStr">
@@ -17026,11 +14702,7 @@
       <c r="H352" s="1" t="inlineStr"/>
       <c r="I352" s="1" t="inlineStr"/>
       <c r="J352" s="1" t="inlineStr"/>
-      <c r="K352" s="1" t="inlineStr">
-        <is>
-          <t>L1871: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: les noms sont inscrits dans le dÃ©velop-</t>
-        </is>
-      </c>
+      <c r="K352" s="1" t="inlineStr"/>
       <c r="L352" s="1" t="inlineStr"/>
       <c r="M352" s="1" t="inlineStr"/>
       <c r="N352" s="1" t="inlineStr">
@@ -17069,11 +14741,7 @@
       <c r="H353" s="1" t="inlineStr"/>
       <c r="I353" s="1" t="inlineStr"/>
       <c r="J353" s="1" t="inlineStr"/>
-      <c r="K353" s="1" t="inlineStr">
-        <is>
-          <t>L1872: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: pement de la grande rÃ©publique amÃ©ri-</t>
-        </is>
-      </c>
+      <c r="K353" s="1" t="inlineStr"/>
       <c r="L353" s="1" t="inlineStr"/>
       <c r="M353" s="1" t="inlineStr"/>
       <c r="N353" s="1" t="inlineStr">
@@ -17112,11 +14780,7 @@
       <c r="H354" s="1" t="inlineStr"/>
       <c r="I354" s="1" t="inlineStr"/>
       <c r="J354" s="1" t="inlineStr"/>
-      <c r="K354" s="1" t="inlineStr">
-        <is>
-          <t>L1877: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Victor Beaudry</t>
-        </is>
-      </c>
+      <c r="K354" s="1" t="inlineStr"/>
       <c r="L354" s="1" t="inlineStr"/>
       <c r="M354" s="1" t="inlineStr"/>
       <c r="N354" s="1" t="inlineStr">
@@ -17132,7 +14796,7 @@
       <c r="P354" s="1" t="inlineStr"/>
       <c r="Q354" s="1" t="inlineStr">
         <is>
-          <t>L1002: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marcel Arcand, Ã©cole Grandin ..................</t>
+          <t>L1002: punctuation artifact: repeated periods :: Marcel Arcand, école Grandin ..................</t>
         </is>
       </c>
       <c r="R354" s="1" t="inlineStr"/>
@@ -17155,11 +14819,7 @@
       <c r="H355" s="1" t="inlineStr"/>
       <c r="I355" s="1" t="inlineStr"/>
       <c r="J355" s="1" t="inlineStr"/>
-      <c r="K355" s="1" t="inlineStr">
-        <is>
-          <t>L1882: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: sont illustrÃ©s aux Etats-Unis, il n'en est</t>
-        </is>
-      </c>
+      <c r="K355" s="1" t="inlineStr"/>
       <c r="L355" s="1" t="inlineStr"/>
       <c r="M355" s="1" t="inlineStr"/>
       <c r="N355" s="1" t="inlineStr">
@@ -17198,11 +14858,7 @@
       <c r="H356" s="1" t="inlineStr"/>
       <c r="I356" s="1" t="inlineStr"/>
       <c r="J356" s="1" t="inlineStr"/>
-      <c r="K356" s="1" t="inlineStr">
-        <is>
-          <t>L1889: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: nom, Ã©crit TassÃ©, mais l'annÃ©e suivante, honneur Ã leur pays d'origine que Pierre</t>
-        </is>
-      </c>
+      <c r="K356" s="1" t="inlineStr"/>
       <c r="L356" s="1" t="inlineStr"/>
       <c r="M356" s="1" t="inlineStr"/>
       <c r="N356" s="1" t="inlineStr">
@@ -17241,11 +14897,7 @@
       <c r="H357" s="1" t="inlineStr"/>
       <c r="I357" s="1" t="inlineStr"/>
       <c r="J357" s="1" t="inlineStr"/>
-      <c r="K357" s="1" t="inlineStr">
-        <is>
-          <t>L1890: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: elle voyait accourir des milliers de spÃ©-</t>
-        </is>
-      </c>
+      <c r="K357" s="1" t="inlineStr"/>
       <c r="L357" s="1" t="inlineStr"/>
       <c r="M357" s="1" t="inlineStr"/>
       <c r="N357" s="1" t="inlineStr">
@@ -17284,11 +14936,7 @@
       <c r="H358" s="1" t="inlineStr"/>
       <c r="I358" s="1" t="inlineStr"/>
       <c r="J358" s="1" t="inlineStr"/>
-      <c r="K358" s="1" t="inlineStr">
-        <is>
-          <t>L1892: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: MÃ©nard.</t>
-        </is>
-      </c>
+      <c r="K358" s="1" t="inlineStr"/>
       <c r="L358" s="1" t="inlineStr"/>
       <c r="M358" s="1" t="inlineStr"/>
       <c r="N358" s="1" t="inlineStr">
@@ -17327,11 +14975,7 @@
       <c r="H359" s="1" t="inlineStr"/>
       <c r="I359" s="1" t="inlineStr"/>
       <c r="J359" s="1" t="inlineStr"/>
-      <c r="K359" s="1" t="inlineStr">
-        <is>
-          <t>L1894: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Il naquit Ã QuÃ©bec en 1767. A dix-neuf</t>
-        </is>
-      </c>
+      <c r="K359" s="1" t="inlineStr"/>
       <c r="L359" s="1" t="inlineStr"/>
       <c r="M359" s="1" t="inlineStr"/>
       <c r="N359" s="1" t="inlineStr">
@@ -17347,7 +14991,7 @@
       <c r="P359" s="1" t="inlineStr"/>
       <c r="Q359" s="1" t="inlineStr">
         <is>
-          <t>L1012: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Bernard HÃ©bert, Saint-Vincent .................</t>
+          <t>L1012: punctuation artifact: repeated periods :: Bernard Hébert, Saint-Vincent .................</t>
         </is>
       </c>
       <c r="R359" s="1" t="inlineStr"/>
@@ -17370,11 +15014,7 @@
       <c r="H360" s="1" t="inlineStr"/>
       <c r="I360" s="1" t="inlineStr"/>
       <c r="J360" s="1" t="inlineStr"/>
-      <c r="K360" s="1" t="inlineStr">
-        <is>
-          <t>L1896: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dans la sociÃ©tÃ© commerciale Lisa &amp; Cie,</t>
-        </is>
-      </c>
+      <c r="K360" s="1" t="inlineStr"/>
       <c r="L360" s="1" t="inlineStr"/>
       <c r="M360" s="1" t="inlineStr"/>
       <c r="N360" s="1" t="inlineStr">
@@ -17390,7 +15030,7 @@
       <c r="P360" s="1" t="inlineStr"/>
       <c r="Q360" s="1" t="inlineStr">
         <is>
-          <t>L1014: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Tarcienne Meunier, Ã©cole Thibeault ............</t>
+          <t>L1014: punctuation artifact: repeated periods :: Tarcienne Meunier, école Thibeault ............</t>
         </is>
       </c>
       <c r="R360" s="1" t="inlineStr"/>
@@ -17413,11 +15053,7 @@
       <c r="H361" s="1" t="inlineStr"/>
       <c r="I361" s="1" t="inlineStr"/>
       <c r="J361" s="1" t="inlineStr"/>
-      <c r="K361" s="1" t="inlineStr">
-        <is>
-          <t>L1898: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: De rÃ©centes modifications apportÃ©es Ã la loi ci-dessus</t>
-        </is>
-      </c>
+      <c r="K361" s="1" t="inlineStr"/>
       <c r="L361" s="1" t="inlineStr"/>
       <c r="M361" s="1" t="inlineStr"/>
       <c r="N361" s="1" t="inlineStr">
@@ -17452,11 +15088,7 @@
       <c r="H362" s="1" t="inlineStr"/>
       <c r="I362" s="1" t="inlineStr"/>
       <c r="J362" s="1" t="inlineStr"/>
-      <c r="K362" s="1" t="inlineStr">
-        <is>
-          <t>L1899: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: portent que toute demande concernant les bÃ©nÃ©fices</t>
-        </is>
-      </c>
+      <c r="K362" s="1" t="inlineStr"/>
       <c r="L362" s="1" t="inlineStr"/>
       <c r="M362" s="1" t="inlineStr"/>
       <c r="N362" s="1" t="inlineStr">
@@ -17491,11 +15123,7 @@
       <c r="H363" s="1" t="inlineStr"/>
       <c r="I363" s="1" t="inlineStr"/>
       <c r="J363" s="1" t="inlineStr"/>
-      <c r="K363" s="1" t="inlineStr">
-        <is>
-          <t>L1900: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: normaux doit Ãªtre produite au MinistÃ¨re du Revenu</t>
-        </is>
-      </c>
+      <c r="K363" s="1" t="inlineStr"/>
       <c r="L363" s="1" t="inlineStr"/>
       <c r="M363" s="1" t="inlineStr"/>
       <c r="N363" s="1" t="inlineStr">
@@ -17530,11 +15158,7 @@
       <c r="H364" s="1" t="inlineStr"/>
       <c r="I364" s="1" t="inlineStr"/>
       <c r="J364" s="1" t="inlineStr"/>
-      <c r="K364" s="1" t="inlineStr">
-        <is>
-          <t>L1907: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ferme pas les renseignements exigÃ©s.</t>
-        </is>
-      </c>
+      <c r="K364" s="1" t="inlineStr"/>
       <c r="L364" s="1" t="inlineStr"/>
       <c r="M364" s="1" t="inlineStr"/>
       <c r="N364" s="1" t="inlineStr">
@@ -17569,11 +15193,7 @@
       <c r="H365" s="1" t="inlineStr"/>
       <c r="I365" s="1" t="inlineStr"/>
       <c r="J365" s="1" t="inlineStr"/>
-      <c r="K365" s="1" t="inlineStr">
-        <is>
-          <t>L1910: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT :: bureau de district de l'impÃ´t sur le revenu du gouverne-</t>
-        </is>
-      </c>
+      <c r="K365" s="1" t="inlineStr"/>
       <c r="L365" s="1" t="inlineStr"/>
       <c r="M365" s="1" t="inlineStr"/>
       <c r="N365" s="1" t="inlineStr">
@@ -17585,7 +15205,7 @@
       <c r="P365" s="1" t="inlineStr"/>
       <c r="Q365" s="1" t="inlineStr">
         <is>
-          <t>L1024: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AdÃ©lard SÃ©guin, Bonnyville ....................</t>
+          <t>L1024: punctuation artifact: repeated periods :: Adélard Séguin, Bonnyville ....................</t>
         </is>
       </c>
       <c r="R365" s="1" t="inlineStr"/>
@@ -17608,11 +15228,7 @@
       <c r="H366" s="1" t="inlineStr"/>
       <c r="I366" s="1" t="inlineStr"/>
       <c r="J366" s="1" t="inlineStr"/>
-      <c r="K366" s="1" t="inlineStr">
-        <is>
-          <t>L1911: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ment fÃ©dÃ©ral.</t>
-        </is>
-      </c>
+      <c r="K366" s="1" t="inlineStr"/>
       <c r="L366" s="1" t="inlineStr"/>
       <c r="M366" s="1" t="inlineStr"/>
       <c r="N366" s="1" t="inlineStr">
@@ -17624,7 +15240,7 @@
       <c r="P366" s="1" t="inlineStr"/>
       <c r="Q366" s="1" t="inlineStr">
         <is>
-          <t>L1028: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Carmen Tellier, Ã©cole Thibeault ...............</t>
+          <t>L1028: punctuation artifact: repeated periods :: Carmen Tellier, école Thibeault ...............</t>
         </is>
       </c>
       <c r="R366" s="1" t="inlineStr"/>
@@ -17647,11 +15263,7 @@
       <c r="H367" s="1" t="inlineStr"/>
       <c r="I367" s="1" t="inlineStr"/>
       <c r="J367" s="1" t="inlineStr"/>
-      <c r="K367" s="1" t="inlineStr">
-        <is>
-          <t>L1913: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Les renseignements pertinents exigÃ©s dans la formule</t>
-        </is>
-      </c>
+      <c r="K367" s="1" t="inlineStr"/>
       <c r="L367" s="1" t="inlineStr"/>
       <c r="M367" s="1" t="inlineStr"/>
       <c r="N367" s="1" t="inlineStr">
@@ -17663,7 +15275,7 @@
       <c r="P367" s="1" t="inlineStr"/>
       <c r="Q367" s="1" t="inlineStr">
         <is>
-          <t>L1030: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Muriel Walker, Ã©cole Thibeault ...............</t>
+          <t>L1030: punctuation artifact: repeated periods :: Muriel Walker, école Thibeault ...............</t>
         </is>
       </c>
       <c r="R367" s="1" t="inlineStr"/>
@@ -17686,11 +15298,7 @@
       <c r="H368" s="1" t="inlineStr"/>
       <c r="I368" s="1" t="inlineStr"/>
       <c r="J368" s="1" t="inlineStr"/>
-      <c r="K368" s="1" t="inlineStr">
-        <is>
-          <t>L1915: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: formules d'essai et les formulÃ©s incomplÃ¨tes, de mÃªme</t>
-        </is>
-      </c>
+      <c r="K368" s="1" t="inlineStr"/>
       <c r="L368" s="1" t="inlineStr"/>
       <c r="M368" s="1" t="inlineStr"/>
       <c r="N368" s="1" t="inlineStr">
@@ -17725,11 +15333,7 @@
       <c r="H369" s="1" t="inlineStr"/>
       <c r="I369" s="1" t="inlineStr"/>
       <c r="J369" s="1" t="inlineStr"/>
-      <c r="K369" s="1" t="inlineStr">
-        <is>
-          <t>L1916: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: que celles produites aprÃ¨s le 31 aoÃ»t 1947, ne seront pas</t>
-        </is>
-      </c>
+      <c r="K369" s="1" t="inlineStr"/>
       <c r="L369" s="1" t="inlineStr"/>
       <c r="M369" s="1" t="inlineStr"/>
       <c r="N369" s="1" t="inlineStr">
@@ -17764,11 +15368,7 @@
       <c r="H370" s="1" t="inlineStr"/>
       <c r="I370" s="1" t="inlineStr"/>
       <c r="J370" s="1" t="inlineStr"/>
-      <c r="K370" s="1" t="inlineStr">
-        <is>
-          <t>L1917: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: acceptÃ©es.</t>
-        </is>
-      </c>
+      <c r="K370" s="1" t="inlineStr"/>
       <c r="L370" s="1" t="inlineStr"/>
       <c r="M370" s="1" t="inlineStr"/>
       <c r="N370" s="1" t="inlineStr">
@@ -17803,11 +15403,7 @@
       <c r="H371" s="1" t="inlineStr"/>
       <c r="I371" s="1" t="inlineStr"/>
       <c r="J371" s="1" t="inlineStr"/>
-      <c r="K371" s="1" t="inlineStr">
-        <is>
-          <t>L1919: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: MinistÃ¨re du Revenu National</t>
-        </is>
-      </c>
+      <c r="K371" s="1" t="inlineStr"/>
       <c r="L371" s="1" t="inlineStr"/>
       <c r="M371" s="1" t="inlineStr"/>
       <c r="N371" s="1" t="inlineStr">
@@ -17819,7 +15415,7 @@
       <c r="P371" s="1" t="inlineStr"/>
       <c r="Q371" s="1" t="inlineStr">
         <is>
-          <t>L1042: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ©rard-Meunier, Ã©cole Thibeault ..</t>
+          <t>L1042: punctuation artifact: repeated periods :: Gérard-Meunier, école Thibeault ..</t>
         </is>
       </c>
       <c r="R371" s="1" t="inlineStr"/>
@@ -17842,11 +15438,7 @@
       <c r="H372" s="1" t="inlineStr"/>
       <c r="I372" s="1" t="inlineStr"/>
       <c r="J372" s="1" t="inlineStr"/>
-      <c r="K372" s="1" t="inlineStr">
-        <is>
-          <t>L1926: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00B4 ACUTE ACCENT :: geaient rien moins qu'Ã dÃ©trÃ´ner Chica-</t>
-        </is>
-      </c>
+      <c r="K372" s="1" t="inlineStr"/>
       <c r="L372" s="1" t="inlineStr"/>
       <c r="M372" s="1" t="inlineStr"/>
       <c r="N372" s="1" t="inlineStr">
@@ -17881,11 +15473,7 @@
       <c r="H373" s="1" t="inlineStr"/>
       <c r="I373" s="1" t="inlineStr"/>
       <c r="J373" s="1" t="inlineStr"/>
-      <c r="K373" s="1" t="inlineStr">
-        <is>
-          <t>L1928: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: go. Ils s'imaginaient qu'elle Ã©tait appe-</t>
-        </is>
-      </c>
+      <c r="K373" s="1" t="inlineStr"/>
       <c r="L373" s="1" t="inlineStr"/>
       <c r="M373" s="1" t="inlineStr"/>
       <c r="N373" s="1" t="inlineStr">
@@ -17920,11 +15508,7 @@
       <c r="H374" s="1" t="inlineStr"/>
       <c r="I374" s="1" t="inlineStr"/>
       <c r="J374" s="1" t="inlineStr"/>
-      <c r="K374" s="1" t="inlineStr">
-        <is>
-          <t>L1929: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00B4 ACUTE ACCENT, U+20AC EURO SIGN | punctuation artifact: repeated periods :: la fonte des mine- lÃ©e Ã devenir l'entrepÃ´t des produits du ..........__â€ž</t>
-        </is>
-      </c>
+      <c r="K374" s="1" t="inlineStr"/>
       <c r="L374" s="1" t="inlineStr"/>
       <c r="M374" s="1" t="inlineStr"/>
       <c r="N374" s="1" t="inlineStr">
@@ -17959,11 +15543,7 @@
       <c r="H375" s="1" t="inlineStr"/>
       <c r="I375" s="1" t="inlineStr"/>
       <c r="J375" s="1" t="inlineStr"/>
-      <c r="K375" s="1" t="inlineStr">
-        <is>
-          <t>L1931: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Nord-Ouest, le port le plus frÃ©quente de quâ€™aux Rocheuses. NommÃ© plus tard a-</t>
-        </is>
-      </c>
+      <c r="K375" s="1" t="inlineStr"/>
       <c r="L375" s="1" t="inlineStr"/>
       <c r="M375" s="1" t="inlineStr"/>
       <c r="N375" s="1" t="inlineStr">
@@ -17998,11 +15578,7 @@
       <c r="H376" s="1" t="inlineStr"/>
       <c r="I376" s="1" t="inlineStr"/>
       <c r="J376" s="1" t="inlineStr"/>
-      <c r="K376" s="1" t="inlineStr">
-        <is>
-          <t>L1932: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: tous les lacs. Ils n'avaient pas songÃ© que</t>
-        </is>
-      </c>
+      <c r="K376" s="1" t="inlineStr"/>
       <c r="L376" s="1" t="inlineStr"/>
       <c r="M376" s="1" t="inlineStr"/>
       <c r="N376" s="1" t="inlineStr">
@@ -18037,11 +15613,7 @@
       <c r="H377" s="1" t="inlineStr"/>
       <c r="I377" s="1" t="inlineStr"/>
       <c r="J377" s="1" t="inlineStr"/>
-      <c r="K377" s="1" t="inlineStr">
-        <is>
-          <t>L1936: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ã Independance. Il dÃ©couvrit un nou-</t>
-        </is>
-      </c>
+      <c r="K377" s="1" t="inlineStr"/>
       <c r="L377" s="1" t="inlineStr"/>
       <c r="M377" s="1" t="inlineStr"/>
       <c r="N377" s="1" t="inlineStr">
@@ -18076,11 +15648,7 @@
       <c r="H378" s="1" t="inlineStr"/>
       <c r="I378" s="1" t="inlineStr"/>
       <c r="J378" s="1" t="inlineStr"/>
-      <c r="K378" s="1" t="inlineStr">
-        <is>
-          <t>L1938: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: veau procÃ©dÃ© pour</t>
-        </is>
-      </c>
+      <c r="K378" s="1" t="inlineStr"/>
       <c r="L378" s="1" t="inlineStr"/>
       <c r="M378" s="1" t="inlineStr"/>
       <c r="N378" s="1" t="inlineStr">
@@ -18115,11 +15683,7 @@
       <c r="H379" s="1" t="inlineStr"/>
       <c r="I379" s="1" t="inlineStr"/>
       <c r="J379" s="1" t="inlineStr"/>
-      <c r="K379" s="1" t="inlineStr">
-        <is>
-          <t>L1940: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: lui assurÃ¨rent un revenu considÃ©rable.</t>
-        </is>
-      </c>
+      <c r="K379" s="1" t="inlineStr"/>
       <c r="L379" s="1" t="inlineStr"/>
       <c r="M379" s="1" t="inlineStr"/>
       <c r="N379" s="1" t="inlineStr">
@@ -18154,11 +15718,7 @@
       <c r="H380" s="1" t="inlineStr"/>
       <c r="I380" s="1" t="inlineStr"/>
       <c r="J380" s="1" t="inlineStr"/>
-      <c r="K380" s="1" t="inlineStr">
-        <is>
-          <t>L1942: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Personne n'a manifestÃ© plus d'esprit</t>
-        </is>
-      </c>
+      <c r="K380" s="1" t="inlineStr"/>
       <c r="L380" s="1" t="inlineStr"/>
       <c r="M380" s="1" t="inlineStr"/>
       <c r="N380" s="1" t="inlineStr">
@@ -18170,7 +15730,7 @@
       <c r="P380" s="1" t="inlineStr"/>
       <c r="Q380" s="1" t="inlineStr">
         <is>
-          <t>L1095: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 7C (letter/digit mix) :: 89 Monique Roy. Ã©cole consolidÃ©e, Donnelly ............7C</t>
+          <t>L1095: punctuation artifact: repeated periods | suspicious token(s): 7C (letter/digit mix) :: 89 Monique Roy. école consolidée, Donnelly ............7C</t>
         </is>
       </c>
       <c r="R380" s="1" t="inlineStr"/>
@@ -18193,11 +15753,7 @@
       <c r="H381" s="1" t="inlineStr"/>
       <c r="I381" s="1" t="inlineStr"/>
       <c r="J381" s="1" t="inlineStr"/>
-      <c r="K381" s="1" t="inlineStr">
-        <is>
-          <t>L1943: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: d'initiative dans le dÃ©veloppement de</t>
-        </is>
-      </c>
+      <c r="K381" s="1" t="inlineStr"/>
       <c r="L381" s="1" t="inlineStr"/>
       <c r="M381" s="1" t="inlineStr"/>
       <c r="N381" s="1" t="inlineStr">
@@ -18232,11 +15788,7 @@
       <c r="H382" s="1" t="inlineStr"/>
       <c r="I382" s="1" t="inlineStr"/>
       <c r="J382" s="1" t="inlineStr"/>
-      <c r="K382" s="1" t="inlineStr">
-        <is>
-          <t>L1944: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: : l'Ouest amÃ©ricain que les frÃ¨res Beau-</t>
-        </is>
-      </c>
+      <c r="K382" s="1" t="inlineStr"/>
       <c r="L382" s="1" t="inlineStr"/>
       <c r="M382" s="1" t="inlineStr"/>
       <c r="N382" s="1" t="inlineStr">
@@ -18271,11 +15823,7 @@
       <c r="H383" s="1" t="inlineStr"/>
       <c r="I383" s="1" t="inlineStr"/>
       <c r="J383" s="1" t="inlineStr"/>
-      <c r="K383" s="1" t="inlineStr">
-        <is>
-          <t>L1948: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: carriÃ¨re presque aussi Ã©tonnante. Il na-</t>
-        </is>
-      </c>
+      <c r="K383" s="1" t="inlineStr"/>
       <c r="L383" s="1" t="inlineStr"/>
       <c r="M383" s="1" t="inlineStr"/>
       <c r="N383" s="1" t="inlineStr">
@@ -18310,11 +15858,7 @@
       <c r="H384" s="1" t="inlineStr"/>
       <c r="I384" s="1" t="inlineStr"/>
       <c r="J384" s="1" t="inlineStr"/>
-      <c r="K384" s="1" t="inlineStr">
-        <is>
-          <t>L1950: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: -fÃ©vrier 1831. Il n'avait que dix-huit ans</t>
-        </is>
-      </c>
+      <c r="K384" s="1" t="inlineStr"/>
       <c r="L384" s="1" t="inlineStr"/>
       <c r="M384" s="1" t="inlineStr"/>
       <c r="N384" s="1" t="inlineStr">
@@ -18349,11 +15893,7 @@
       <c r="H385" s="1" t="inlineStr"/>
       <c r="I385" s="1" t="inlineStr"/>
       <c r="J385" s="1" t="inlineStr"/>
-      <c r="K385" s="1" t="inlineStr">
-        <is>
-          <t>L1954: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: s'Ã©tendaient jus-</t>
-        </is>
-      </c>
+      <c r="K385" s="1" t="inlineStr"/>
       <c r="L385" s="1" t="inlineStr"/>
       <c r="M385" s="1" t="inlineStr"/>
       <c r="N385" s="1" t="inlineStr">
@@ -18388,11 +15928,7 @@
       <c r="H386" s="1" t="inlineStr"/>
       <c r="I386" s="1" t="inlineStr"/>
       <c r="J386" s="1" t="inlineStr"/>
-      <c r="K386" s="1" t="inlineStr">
-        <is>
-          <t>L1956: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dont les opÃ©rations</t>
-        </is>
-      </c>
+      <c r="K386" s="1" t="inlineStr"/>
       <c r="L386" s="1" t="inlineStr"/>
       <c r="M386" s="1" t="inlineStr"/>
       <c r="N386" s="1" t="inlineStr">
@@ -18427,11 +15963,7 @@
       <c r="H387" s="1" t="inlineStr"/>
       <c r="I387" s="1" t="inlineStr"/>
       <c r="J387" s="1" t="inlineStr"/>
-      <c r="K387" s="1" t="inlineStr">
-        <is>
-          <t>L1959: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: des Etats-Unis, il rÃ©ussit Ã conclure des</t>
-        </is>
-      </c>
+      <c r="K387" s="1" t="inlineStr"/>
       <c r="L387" s="1" t="inlineStr"/>
       <c r="M387" s="1" t="inlineStr"/>
       <c r="N387" s="1" t="inlineStr">
@@ -18466,11 +15998,7 @@
       <c r="H388" s="1" t="inlineStr"/>
       <c r="I388" s="1" t="inlineStr"/>
       <c r="J388" s="1" t="inlineStr"/>
-      <c r="K388" s="1" t="inlineStr">
-        <is>
-          <t>L1960: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: traitÃ©s avec plusieurs tribus. Aux Ã©lec-</t>
-        </is>
-      </c>
+      <c r="K388" s="1" t="inlineStr"/>
       <c r="L388" s="1" t="inlineStr"/>
       <c r="M388" s="1" t="inlineStr"/>
       <c r="N388" s="1" t="inlineStr">
@@ -18505,11 +16033,7 @@
       <c r="H389" s="1" t="inlineStr"/>
       <c r="I389" s="1" t="inlineStr"/>
       <c r="J389" s="1" t="inlineStr"/>
-      <c r="K389" s="1" t="inlineStr">
-        <is>
-          <t>L1961: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: tions de 1803, il obtint un siÃ¨ge Ã la</t>
-        </is>
-      </c>
+      <c r="K389" s="1" t="inlineStr"/>
       <c r="L389" s="1" t="inlineStr"/>
       <c r="M389" s="1" t="inlineStr"/>
       <c r="N389" s="1" t="inlineStr">
@@ -18544,11 +16068,7 @@
       <c r="H390" s="1" t="inlineStr"/>
       <c r="I390" s="1" t="inlineStr"/>
       <c r="J390" s="1" t="inlineStr"/>
-      <c r="K390" s="1" t="inlineStr">
-        <is>
-          <t>L1962: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: LÃ©gislature de lâ€™Indiana. Plus tard, on le</t>
-        </is>
-      </c>
+      <c r="K390" s="1" t="inlineStr"/>
       <c r="L390" s="1" t="inlineStr"/>
       <c r="M390" s="1" t="inlineStr"/>
       <c r="N390" s="1" t="inlineStr">
@@ -18583,11 +16103,7 @@
       <c r="H391" s="1" t="inlineStr"/>
       <c r="I391" s="1" t="inlineStr"/>
       <c r="J391" s="1" t="inlineStr"/>
-      <c r="K391" s="1" t="inlineStr">
-        <is>
-          <t>L1963: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dÃ©signa unanimement comme prÃ©sident</t>
-        </is>
-      </c>
+      <c r="K391" s="1" t="inlineStr"/>
       <c r="L391" s="1" t="inlineStr"/>
       <c r="M391" s="1" t="inlineStr"/>
       <c r="N391" s="1" t="inlineStr">
@@ -18622,11 +16138,7 @@
       <c r="H392" s="1" t="inlineStr"/>
       <c r="I392" s="1" t="inlineStr"/>
       <c r="J392" s="1" t="inlineStr"/>
-      <c r="K392" s="1" t="inlineStr">
-        <is>
-          <t>L1964: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: du Conseil lÃ©gislatif. Le scrutin mÃªme</t>
-        </is>
-      </c>
+      <c r="K392" s="1" t="inlineStr"/>
       <c r="L392" s="1" t="inlineStr"/>
       <c r="M392" s="1" t="inlineStr"/>
       <c r="N392" s="1" t="inlineStr">
@@ -18661,11 +16173,7 @@
       <c r="H393" s="1" t="inlineStr"/>
       <c r="I393" s="1" t="inlineStr"/>
       <c r="J393" s="1" t="inlineStr"/>
-      <c r="K393" s="1" t="inlineStr">
-        <is>
-          <t>L1966: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: aprÃ¨s que l'on eut modifiÃ© spÃ©cialement</t>
-        </is>
-      </c>
+      <c r="K393" s="1" t="inlineStr"/>
       <c r="L393" s="1" t="inlineStr"/>
       <c r="M393" s="1" t="inlineStr"/>
       <c r="N393" s="1" t="inlineStr">
@@ -18700,11 +16208,7 @@
       <c r="H394" s="1" t="inlineStr"/>
       <c r="I394" s="1" t="inlineStr"/>
       <c r="J394" s="1" t="inlineStr"/>
-      <c r="K394" s="1" t="inlineStr">
-        <is>
-          <t>L1967: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: la Constitution afin de rendre son Ã©lec-</t>
-        </is>
-      </c>
+      <c r="K394" s="1" t="inlineStr"/>
       <c r="L394" s="1" t="inlineStr"/>
       <c r="M394" s="1" t="inlineStr"/>
       <c r="N394" s="1" t="inlineStr">
@@ -18739,11 +16243,7 @@
       <c r="H395" s="1" t="inlineStr"/>
       <c r="I395" s="1" t="inlineStr"/>
       <c r="J395" s="1" t="inlineStr"/>
-      <c r="K395" s="1" t="inlineStr">
-        <is>
-          <t>L1973: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A2 CENT SIGN :: L'hon. MÃ©nard avait su l'acquÃ©rir grÃ¢ce</t>
-        </is>
-      </c>
+      <c r="K395" s="1" t="inlineStr"/>
       <c r="L395" s="1" t="inlineStr"/>
       <c r="M395" s="1" t="inlineStr"/>
       <c r="N395" s="1" t="inlineStr">
@@ -18778,11 +16278,7 @@
       <c r="H396" s="1" t="inlineStr"/>
       <c r="I396" s="1" t="inlineStr"/>
       <c r="J396" s="1" t="inlineStr"/>
-      <c r="K396" s="1" t="inlineStr">
-        <is>
-          <t>L1978: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: la CitÃ© du SupÃ©rieur n'avait pas encore</t>
-        </is>
-      </c>
+      <c r="K396" s="1" t="inlineStr"/>
       <c r="L396" s="1" t="inlineStr"/>
       <c r="M396" s="1" t="inlineStr"/>
       <c r="N396" s="1" t="inlineStr">
@@ -18817,11 +16313,7 @@
       <c r="H397" s="1" t="inlineStr"/>
       <c r="I397" s="1" t="inlineStr"/>
       <c r="J397" s="1" t="inlineStr"/>
-      <c r="K397" s="1" t="inlineStr">
-        <is>
-          <t>L1979: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: derriÃ¨re elle de campagnes cultivÃ©es, ni</t>
-        </is>
-      </c>
+      <c r="K397" s="1" t="inlineStr"/>
       <c r="L397" s="1" t="inlineStr"/>
       <c r="M397" s="1" t="inlineStr"/>
       <c r="N397" s="1" t="inlineStr">
@@ -18856,11 +16348,7 @@
       <c r="H398" s="1" t="inlineStr"/>
       <c r="I398" s="1" t="inlineStr"/>
       <c r="J398" s="1" t="inlineStr"/>
-      <c r="K398" s="1" t="inlineStr">
-        <is>
-          <t>L1980: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: mÃªme une voie ferrÃ©e. Aussi elle est pas-</t>
-        </is>
-      </c>
+      <c r="K398" s="1" t="inlineStr"/>
       <c r="L398" s="1" t="inlineStr"/>
       <c r="M398" s="1" t="inlineStr"/>
       <c r="N398" s="1" t="inlineStr">
@@ -18895,11 +16383,7 @@
       <c r="H399" s="1" t="inlineStr"/>
       <c r="I399" s="1" t="inlineStr"/>
       <c r="J399" s="1" t="inlineStr"/>
-      <c r="K399" s="1" t="inlineStr">
-        <is>
-          <t>L1981: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: sÃ©e, la pauvre ville, comme passent les</t>
-        </is>
-      </c>
+      <c r="K399" s="1" t="inlineStr"/>
       <c r="L399" s="1" t="inlineStr"/>
       <c r="M399" s="1" t="inlineStr"/>
       <c r="N399" s="1" t="inlineStr">
@@ -18934,11 +16418,7 @@
       <c r="H400" s="1" t="inlineStr"/>
       <c r="I400" s="1" t="inlineStr"/>
       <c r="J400" s="1" t="inlineStr"/>
-      <c r="K400" s="1" t="inlineStr">
-        <is>
-          <t>L1984: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: "Lefebvre Ã©tait l'un des plus intrÃ©pi-1</t>
-        </is>
-      </c>
+      <c r="K400" s="1" t="inlineStr"/>
       <c r="L400" s="1" t="inlineStr"/>
       <c r="M400" s="1" t="inlineStr"/>
       <c r="N400" s="1" t="inlineStr">
@@ -18973,11 +16453,7 @@
       <c r="H401" s="1" t="inlineStr"/>
       <c r="I401" s="1" t="inlineStr"/>
       <c r="J401" s="1" t="inlineStr"/>
-      <c r="K401" s="1" t="inlineStr">
-        <is>
-          <t>L1988: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ses jambes. La diligence Ã©tait inconnue</t>
-        </is>
-      </c>
+      <c r="K401" s="1" t="inlineStr"/>
       <c r="L401" s="1" t="inlineStr"/>
       <c r="M401" s="1" t="inlineStr"/>
       <c r="N401" s="1" t="inlineStr">
@@ -19012,11 +16488,7 @@
       <c r="H402" s="1" t="inlineStr"/>
       <c r="I402" s="1" t="inlineStr"/>
       <c r="J402" s="1" t="inlineStr"/>
-      <c r="K402" s="1" t="inlineStr">
-        <is>
-          <t>L1990: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: vait pas encore fait retentir les Ã©chos du</t>
-        </is>
-      </c>
+      <c r="K402" s="1" t="inlineStr"/>
       <c r="L402" s="1" t="inlineStr"/>
       <c r="M402" s="1" t="inlineStr"/>
       <c r="N402" s="1" t="inlineStr">
@@ -19051,11 +16523,7 @@
       <c r="H403" s="1" t="inlineStr"/>
       <c r="I403" s="1" t="inlineStr"/>
       <c r="J403" s="1" t="inlineStr"/>
-      <c r="K403" s="1" t="inlineStr">
-        <is>
-          <t>L1992: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Quatre jeunes gens ont passÃ© la moi lac SupÃ©rieur." Les voyageurs ne pou-</t>
-        </is>
-      </c>
+      <c r="K403" s="1" t="inlineStr"/>
       <c r="L403" s="1" t="inlineStr"/>
       <c r="M403" s="1" t="inlineStr"/>
       <c r="N403" s="1" t="inlineStr">
@@ -19090,11 +16558,7 @@
       <c r="H404" s="1" t="inlineStr"/>
       <c r="I404" s="1" t="inlineStr"/>
       <c r="J404" s="1" t="inlineStr"/>
-      <c r="K404" s="1" t="inlineStr">
-        <is>
-          <t>L1993: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: tiÃ© de la nuit Ã jouer. En se sÃ©parant, ! vaient trouver de meilleur guide que Le-</t>
-        </is>
-      </c>
+      <c r="K404" s="1" t="inlineStr"/>
       <c r="L404" s="1" t="inlineStr"/>
       <c r="M404" s="1" t="inlineStr"/>
       <c r="N404" s="1" t="inlineStr">
@@ -19129,11 +16593,7 @@
       <c r="H405" s="1" t="inlineStr"/>
       <c r="I405" s="1" t="inlineStr"/>
       <c r="J405" s="1" t="inlineStr"/>
-      <c r="K405" s="1" t="inlineStr">
-        <is>
-          <t>L1995: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: chacun a gagnÃ© 40 francs, et que per-!piaines et les forÃªts environnantes. Il</t>
-        </is>
-      </c>
+      <c r="K405" s="1" t="inlineStr"/>
       <c r="L405" s="1" t="inlineStr"/>
       <c r="M405" s="1" t="inlineStr"/>
       <c r="N405" s="1" t="inlineStr">
@@ -19168,11 +16628,7 @@
       <c r="H406" s="1" t="inlineStr"/>
       <c r="I406" s="1" t="inlineStr"/>
       <c r="J406" s="1" t="inlineStr"/>
-      <c r="K406" s="1" t="inlineStr">
-        <is>
-          <t>L1998: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Comment cela peut-il se faire? ses histoires dramatiques, faire oublier</t>
-        </is>
-      </c>
+      <c r="K406" s="1" t="inlineStr"/>
       <c r="L406" s="1" t="inlineStr"/>
       <c r="M406" s="1" t="inlineStr"/>
       <c r="N406" s="1" t="inlineStr">
@@ -19207,11 +16663,7 @@
       <c r="H407" s="1" t="inlineStr"/>
       <c r="I407" s="1" t="inlineStr"/>
       <c r="J407" s="1" t="inlineStr"/>
-      <c r="K407" s="1" t="inlineStr">
-        <is>
-          <t>L1999: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A9 COPYRIGHT SIGN :: â€”C'est que tous les quatre sont des les fatigues de la journÃ©e. Parmi ceux</t>
-        </is>
-      </c>
+      <c r="K407" s="1" t="inlineStr"/>
       <c r="L407" s="1" t="inlineStr"/>
       <c r="M407" s="1" t="inlineStr"/>
       <c r="N407" s="1" t="inlineStr">
@@ -19246,11 +16698,7 @@
       <c r="H408" s="1" t="inlineStr"/>
       <c r="I408" s="1" t="inlineStr"/>
       <c r="J408" s="1" t="inlineStr"/>
-      <c r="K408" s="1" t="inlineStr">
-        <is>
-          <t>L2000: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: joueurs de violon. qui bÃ©nÃ©ficiÃ¨rent de ses connaissances,</t>
-        </is>
-      </c>
+      <c r="K408" s="1" t="inlineStr"/>
       <c r="L408" s="1" t="inlineStr"/>
       <c r="M408" s="1" t="inlineStr"/>
       <c r="N408" s="1" t="inlineStr">
@@ -19285,11 +16733,7 @@
       <c r="H409" s="1" t="inlineStr"/>
       <c r="I409" s="1" t="inlineStr"/>
       <c r="J409" s="1" t="inlineStr"/>
-      <c r="K409" s="1" t="inlineStr">
-        <is>
-          <t>L2002: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: vie de grandes entreprises, dâ€™as-</t>
-        </is>
-      </c>
+      <c r="K409" s="1" t="inlineStr"/>
       <c r="L409" s="1" t="inlineStr"/>
       <c r="M409" s="1" t="inlineStr"/>
       <c r="N409" s="1" t="inlineStr">
@@ -19324,11 +16768,7 @@
       <c r="H410" s="1" t="inlineStr"/>
       <c r="I410" s="1" t="inlineStr"/>
       <c r="J410" s="1" t="inlineStr"/>
-      <c r="K410" s="1" t="inlineStr">
-        <is>
-          <t>L2005: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: quoi satisfaire les amateurs dâ€™a-</t>
-        </is>
-      </c>
+      <c r="K410" s="1" t="inlineStr"/>
       <c r="L410" s="1" t="inlineStr"/>
       <c r="M410" s="1" t="inlineStr"/>
       <c r="N410" s="1" t="inlineStr">
@@ -19363,11 +16803,7 @@
       <c r="H411" s="1" t="inlineStr"/>
       <c r="I411" s="1" t="inlineStr"/>
       <c r="J411" s="1" t="inlineStr"/>
-      <c r="K411" s="1" t="inlineStr">
-        <is>
-          <t>L2013: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: aussi les menaces de la ruine dÃ©finitive.</t>
-        </is>
-      </c>
+      <c r="K411" s="1" t="inlineStr"/>
       <c r="L411" s="1" t="inlineStr"/>
       <c r="M411" s="1" t="inlineStr"/>
       <c r="N411" s="1" t="inlineStr">
@@ -19402,11 +16838,7 @@
       <c r="H412" s="1" t="inlineStr"/>
       <c r="I412" s="1" t="inlineStr"/>
       <c r="J412" s="1" t="inlineStr"/>
-      <c r="K412" s="1" t="inlineStr">
-        <is>
-          <t>L2014: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: MalgrÃ© toutes les pertes que Beaudry</t>
-        </is>
-      </c>
+      <c r="K412" s="1" t="inlineStr"/>
       <c r="L412" s="1" t="inlineStr"/>
       <c r="M412" s="1" t="inlineStr"/>
       <c r="N412" s="1" t="inlineStr">
@@ -19441,11 +16873,7 @@
       <c r="H413" s="1" t="inlineStr"/>
       <c r="I413" s="1" t="inlineStr"/>
       <c r="J413" s="1" t="inlineStr"/>
-      <c r="K413" s="1" t="inlineStr">
-        <is>
-          <t>L2015: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: eut Ã subir, il rÃ©ussit Ã se constituer une</t>
-        </is>
-      </c>
+      <c r="K413" s="1" t="inlineStr"/>
       <c r="L413" s="1" t="inlineStr"/>
       <c r="M413" s="1" t="inlineStr"/>
       <c r="N413" s="1" t="inlineStr">
@@ -19480,11 +16908,7 @@
       <c r="H414" s="1" t="inlineStr"/>
       <c r="I414" s="1" t="inlineStr"/>
       <c r="J414" s="1" t="inlineStr"/>
-      <c r="K414" s="1" t="inlineStr">
-        <is>
-          <t>L2019: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dire autant que "tÃ©moin", et pour avoir</t>
-        </is>
-      </c>
+      <c r="K414" s="1" t="inlineStr"/>
       <c r="L414" s="1" t="inlineStr"/>
       <c r="M414" s="1" t="inlineStr"/>
       <c r="N414" s="1" t="inlineStr">
@@ -19519,11 +16943,7 @@
       <c r="H415" s="1" t="inlineStr"/>
       <c r="I415" s="1" t="inlineStr"/>
       <c r="J415" s="1" t="inlineStr"/>
-      <c r="K415" s="1" t="inlineStr">
-        <is>
-          <t>L2020: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ã©tÃ© tout trempÃ© du sang des chrÃ©tiens,</t>
-        </is>
-      </c>
+      <c r="K415" s="1" t="inlineStr"/>
       <c r="L415" s="1" t="inlineStr"/>
       <c r="M415" s="1" t="inlineStr"/>
       <c r="N415" s="1" t="inlineStr">
@@ -19558,11 +16978,7 @@
       <c r="H416" s="1" t="inlineStr"/>
       <c r="I416" s="1" t="inlineStr"/>
       <c r="J416" s="1" t="inlineStr"/>
-      <c r="K416" s="1" t="inlineStr">
-        <is>
-          <t>L2023: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: "victimes", quelquefois mÃªme trÃ¨s di-</t>
-        </is>
-      </c>
+      <c r="K416" s="1" t="inlineStr"/>
       <c r="L416" s="1" t="inlineStr"/>
       <c r="M416" s="1" t="inlineStr"/>
       <c r="N416" s="1" t="inlineStr">
@@ -19597,11 +17013,7 @@
       <c r="H417" s="1" t="inlineStr"/>
       <c r="I417" s="1" t="inlineStr"/>
       <c r="J417" s="1" t="inlineStr"/>
-      <c r="K417" s="1" t="inlineStr">
-        <is>
-          <t>L2024: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: gnes de pitiÃ©; mais la vÃ©ritÃ© seule a des</t>
-        </is>
-      </c>
+      <c r="K417" s="1" t="inlineStr"/>
       <c r="L417" s="1" t="inlineStr"/>
       <c r="M417" s="1" t="inlineStr"/>
       <c r="N417" s="1" t="inlineStr">
@@ -19636,11 +17048,7 @@
       <c r="H418" s="1" t="inlineStr"/>
       <c r="I418" s="1" t="inlineStr"/>
       <c r="J418" s="1" t="inlineStr"/>
-      <c r="K418" s="1" t="inlineStr">
-        <is>
-          <t>L2025: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: "martyrs". Ainsi l'ont entendu les PÃ¨-</t>
-        </is>
-      </c>
+      <c r="K418" s="1" t="inlineStr"/>
       <c r="L418" s="1" t="inlineStr"/>
       <c r="M418" s="1" t="inlineStr"/>
       <c r="N418" s="1" t="inlineStr">
@@ -19675,11 +17083,7 @@
       <c r="H419" s="1" t="inlineStr"/>
       <c r="I419" s="1" t="inlineStr"/>
       <c r="J419" s="1" t="inlineStr"/>
-      <c r="K419" s="1" t="inlineStr">
-        <is>
-          <t>L2031: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: diens franÃ§ais attirÃ©s par les dÃ©couver-</t>
-        </is>
-      </c>
+      <c r="K419" s="1" t="inlineStr"/>
       <c r="L419" s="1" t="inlineStr"/>
       <c r="M419" s="1" t="inlineStr"/>
       <c r="N419" s="1" t="inlineStr">
@@ -19714,11 +17118,7 @@
       <c r="H420" s="1" t="inlineStr"/>
       <c r="I420" s="1" t="inlineStr"/>
       <c r="J420" s="1" t="inlineStr"/>
-      <c r="K420" s="1" t="inlineStr">
-        <is>
-          <t>L2033: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: gnala en fondant une agence de goÃ©let-</t>
-        </is>
-      </c>
+      <c r="K420" s="1" t="inlineStr"/>
       <c r="L420" s="1" t="inlineStr"/>
       <c r="M420" s="1" t="inlineStr"/>
       <c r="N420" s="1" t="inlineStr">
@@ -19753,11 +17153,7 @@
       <c r="H421" s="1" t="inlineStr"/>
       <c r="I421" s="1" t="inlineStr"/>
       <c r="J421" s="1" t="inlineStr"/>
-      <c r="K421" s="1" t="inlineStr">
-        <is>
-          <t>L2036: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: compagnie de son frÃ¨re, Prudent, il or-</t>
-        </is>
-      </c>
+      <c r="K421" s="1" t="inlineStr"/>
       <c r="L421" s="1" t="inlineStr"/>
       <c r="M421" s="1" t="inlineStr"/>
       <c r="N421" s="1" t="inlineStr">
@@ -19792,11 +17188,7 @@
       <c r="H422" s="1" t="inlineStr"/>
       <c r="I422" s="1" t="inlineStr"/>
       <c r="J422" s="1" t="inlineStr"/>
-      <c r="K422" s="1" t="inlineStr">
-        <is>
-          <t>L2038: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: tion le tenta de nouveau et il Ã©tablit</t>
-        </is>
-      </c>
+      <c r="K422" s="1" t="inlineStr"/>
       <c r="L422" s="1" t="inlineStr"/>
       <c r="M422" s="1" t="inlineStr"/>
       <c r="N422" s="1" t="inlineStr">
@@ -19831,11 +17223,7 @@
       <c r="H423" s="1" t="inlineStr"/>
       <c r="I423" s="1" t="inlineStr"/>
       <c r="J423" s="1" t="inlineStr"/>
-      <c r="K423" s="1" t="inlineStr">
-        <is>
-          <t>L2041: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Los Angeles deux annÃ©es plus tard. La</t>
-        </is>
-      </c>
+      <c r="K423" s="1" t="inlineStr"/>
       <c r="L423" s="1" t="inlineStr"/>
       <c r="M423" s="1" t="inlineStr"/>
       <c r="N423" s="1" t="inlineStr">
@@ -19870,11 +17258,7 @@
       <c r="H424" s="1" t="inlineStr"/>
       <c r="I424" s="1" t="inlineStr"/>
       <c r="J424" s="1" t="inlineStr"/>
-      <c r="K424" s="1" t="inlineStr">
-        <is>
-          <t>L2042: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: terrible guerre de sÃ©cession lui permit</t>
-        </is>
-      </c>
+      <c r="K424" s="1" t="inlineStr"/>
       <c r="L424" s="1" t="inlineStr"/>
       <c r="M424" s="1" t="inlineStr"/>
       <c r="N424" s="1" t="inlineStr">
@@ -19909,11 +17293,7 @@
       <c r="H425" s="1" t="inlineStr"/>
       <c r="I425" s="1" t="inlineStr"/>
       <c r="J425" s="1" t="inlineStr"/>
-      <c r="K425" s="1" t="inlineStr">
-        <is>
-          <t>L2043: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT :: de jouer un rÃ´le important. Il devint</t>
-        </is>
-      </c>
+      <c r="K425" s="1" t="inlineStr"/>
       <c r="L425" s="1" t="inlineStr"/>
       <c r="M425" s="1" t="inlineStr"/>
       <c r="N425" s="1" t="inlineStr">
@@ -19948,11 +17328,7 @@
       <c r="H426" s="1" t="inlineStr"/>
       <c r="I426" s="1" t="inlineStr"/>
       <c r="J426" s="1" t="inlineStr"/>
-      <c r="K426" s="1" t="inlineStr">
-        <is>
-          <t>L2048: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN | suspicious token(s): sa1 (letter/digit mix) :: Ã l'Ã¢ge de 77 ans. Cinq ans avant sa1</t>
-        </is>
-      </c>
+      <c r="K426" s="1" t="inlineStr"/>
       <c r="L426" s="1" t="inlineStr"/>
       <c r="M426" s="1" t="inlineStr"/>
       <c r="N426" s="1" t="inlineStr">
@@ -19987,11 +17363,7 @@
       <c r="H427" s="1" t="inlineStr"/>
       <c r="I427" s="1" t="inlineStr"/>
       <c r="J427" s="1" t="inlineStr"/>
-      <c r="K427" s="1" t="inlineStr">
-        <is>
-          <t>L2049: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: mort les autoritÃ©s avaient donnÃ© le nom :</t>
-        </is>
-      </c>
+      <c r="K427" s="1" t="inlineStr"/>
       <c r="L427" s="1" t="inlineStr"/>
       <c r="M427" s="1" t="inlineStr"/>
       <c r="N427" s="1" t="inlineStr">
@@ -20026,11 +17398,7 @@
       <c r="H428" s="1" t="inlineStr"/>
       <c r="I428" s="1" t="inlineStr"/>
       <c r="J428" s="1" t="inlineStr"/>
-      <c r="K428" s="1" t="inlineStr">
-        <is>
-          <t>L2050: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de MÃ©nard Ã l'un des comtÃ©s les plus</t>
-        </is>
-      </c>
+      <c r="K428" s="1" t="inlineStr"/>
       <c r="L428" s="1" t="inlineStr"/>
       <c r="M428" s="1" t="inlineStr"/>
       <c r="N428" s="1" t="inlineStr">
@@ -20042,7 +17410,7 @@
       <c r="P428" s="1" t="inlineStr"/>
       <c r="Q428" s="1" t="inlineStr">
         <is>
-          <t>L1272: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Fernande TieuliÃ©, Legal .................</t>
+          <t>L1272: punctuation artifact: repeated periods :: Fernande Tieulié, Legal .................</t>
         </is>
       </c>
       <c r="R428" s="1" t="inlineStr"/>
@@ -20065,11 +17433,7 @@
       <c r="H429" s="1" t="inlineStr"/>
       <c r="I429" s="1" t="inlineStr"/>
       <c r="J429" s="1" t="inlineStr"/>
-      <c r="K429" s="1" t="inlineStr">
-        <is>
-          <t>L2054: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: rÃ©e presque lÃ©gendaire jusqu'Ã nos jours.</t>
-        </is>
-      </c>
+      <c r="K429" s="1" t="inlineStr"/>
       <c r="L429" s="1" t="inlineStr"/>
       <c r="M429" s="1" t="inlineStr"/>
       <c r="N429" s="1" t="inlineStr">
@@ -20081,7 +17445,7 @@
       <c r="P429" s="1" t="inlineStr"/>
       <c r="Q429" s="1" t="inlineStr">
         <is>
-          <t>L1274: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Guy Tessier, Ã©cole Grandin ..............</t>
+          <t>L1274: punctuation artifact: repeated periods :: Guy Tessier, école Grandin ..............</t>
         </is>
       </c>
       <c r="R429" s="1" t="inlineStr"/>
@@ -20104,11 +17468,7 @@
       <c r="H430" s="1" t="inlineStr"/>
       <c r="I430" s="1" t="inlineStr"/>
       <c r="J430" s="1" t="inlineStr"/>
-      <c r="K430" s="1" t="inlineStr">
-        <is>
-          <t>L2056: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Parkman a dÃ©signÃ© Pierre MÃ©nard</t>
-        </is>
-      </c>
+      <c r="K430" s="1" t="inlineStr"/>
       <c r="L430" s="1" t="inlineStr"/>
       <c r="M430" s="1" t="inlineStr"/>
       <c r="N430" s="1" t="inlineStr">
@@ -20120,7 +17480,7 @@
       <c r="P430" s="1" t="inlineStr"/>
       <c r="Q430" s="1" t="inlineStr">
         <is>
-          <t>L1276: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jacques Voyer, Ã©cole Thibeault .........</t>
+          <t>L1276: punctuation artifact: repeated periods :: Jacques Voyer, école Thibeault .........</t>
         </is>
       </c>
       <c r="R430" s="1" t="inlineStr"/>
@@ -20143,11 +17503,7 @@
       <c r="H431" s="1" t="inlineStr"/>
       <c r="I431" s="1" t="inlineStr"/>
       <c r="J431" s="1" t="inlineStr"/>
-      <c r="K431" s="1" t="inlineStr">
-        <is>
-          <t>L2057: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: comme "le vÃ©nÃ©rable patriarche de lâ€™Il-</t>
-        </is>
-      </c>
+      <c r="K431" s="1" t="inlineStr"/>
       <c r="L431" s="1" t="inlineStr"/>
       <c r="M431" s="1" t="inlineStr"/>
       <c r="N431" s="1" t="inlineStr">
@@ -20194,7 +17550,7 @@
       <c r="P432" s="1" t="inlineStr"/>
       <c r="Q432" s="1" t="inlineStr">
         <is>
-          <t>L1280: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: BÃ©atrice Hurtubise, Saint-Paul .......</t>
+          <t>L1280: punctuation artifact: repeated periods :: Béatrice Hurtubise, Saint-Paul .......</t>
         </is>
       </c>
       <c r="R432" s="1" t="inlineStr"/>
@@ -20229,7 +17585,7 @@
       <c r="P433" s="1" t="inlineStr"/>
       <c r="Q433" s="1" t="inlineStr">
         <is>
-          <t>L1292: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ...86 RÃ©al Demers, Beaumont..........................</t>
+          <t>L1292: punctuation artifact: repeated periods :: ...86 Réal Demers, Beaumont..........................</t>
         </is>
       </c>
       <c r="R433" s="1" t="inlineStr"/>
@@ -20264,7 +17620,7 @@
       <c r="P434" s="1" t="inlineStr"/>
       <c r="Q434" s="1" t="inlineStr">
         <is>
-          <t>L1302: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ...861 Constant Maisonneuve, Ã©cole consolidÃ©e, Donnelly</t>
+          <t>L1302: punctuation artifact: repeated periods :: ...861 Constant Maisonneuve, école consolidée, Donnelly</t>
         </is>
       </c>
       <c r="R434" s="1" t="inlineStr"/>
@@ -20299,7 +17655,7 @@
       <c r="P435" s="1" t="inlineStr"/>
       <c r="Q435" s="1" t="inlineStr">
         <is>
-          <t>L1304: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ...86, Roland SÃ©guin, Ã©cole Dunrobin .................</t>
+          <t>L1304: punctuation artifact: repeated periods :: ...86, Roland Séguin, école Dunrobin .................</t>
         </is>
       </c>
       <c r="R435" s="1" t="inlineStr"/>
@@ -20369,7 +17725,7 @@
       <c r="P437" s="1" t="inlineStr"/>
       <c r="Q437" s="1" t="inlineStr">
         <is>
-          <t>L1312: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 86Edouard (letter/digit mix) | localized OCR phrase divergence vs other OCR: "65 Edouard" vs "86Edouard" :: 86Edouard Garneau, Ã©cole Grandin ..........</t>
+          <t>L1312: punctuation artifact: repeated periods | suspicious token(s): 86Edouard (letter/digit mix) | localized OCR phrase divergence vs other OCR: "65 Edouard" vs "86Edouard" :: 86Edouard Garneau, école Grandin ..........</t>
         </is>
       </c>
       <c r="R437" s="1" t="inlineStr"/>
@@ -21069,7 +18425,7 @@
       <c r="P457" s="1" t="inlineStr"/>
       <c r="Q457" s="1" t="inlineStr">
         <is>
-          <t>L1382: punctuation artifact: repeated periods :: Georgette NoÃ«l, Saint-Paul ...........</t>
+          <t>L1382: punctuation artifact: repeated periods :: Georgette Noël, Saint-Paul ...........</t>
         </is>
       </c>
       <c r="R457" s="1" t="inlineStr"/>
@@ -21174,7 +18530,7 @@
       <c r="P460" s="1" t="inlineStr"/>
       <c r="Q460" s="1" t="inlineStr">
         <is>
-          <t>L1394: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: : HÃ©lÃ¨ne Normand, ThÃ©rien Village ...............</t>
+          <t>L1394: punctuation artifact: repeated periods :: : Hélène Normand, Thérien Village ...............</t>
         </is>
       </c>
       <c r="R460" s="1" t="inlineStr"/>
@@ -21279,7 +18635,7 @@
       <c r="P463" s="1" t="inlineStr"/>
       <c r="Q463" s="1" t="inlineStr">
         <is>
-          <t>L1410: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Maurier, Legal ...........................</t>
+          <t>L1410: punctuation artifact: repeated periods :: René Maurier, Legal ...........................</t>
         </is>
       </c>
       <c r="R463" s="1" t="inlineStr"/>
@@ -21314,7 +18670,7 @@
       <c r="P464" s="1" t="inlineStr"/>
       <c r="Q464" s="1" t="inlineStr">
         <is>
-          <t>L1416: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© La Brie, Fort Kent .................</t>
+          <t>L1416: punctuation artifact: repeated periods :: André La Brie, Fort Kent .................</t>
         </is>
       </c>
       <c r="R464" s="1" t="inlineStr"/>
@@ -21559,7 +18915,7 @@
       <c r="P471" s="1" t="inlineStr"/>
       <c r="Q471" s="1" t="inlineStr">
         <is>
-          <t>L1442: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Claire Petersen, Ã©cole Grandin ................</t>
+          <t>L1442: punctuation artifact: repeated periods :: Claire Petersen, école Grandin ................</t>
         </is>
       </c>
       <c r="R471" s="1" t="inlineStr"/>
@@ -21594,7 +18950,7 @@
       <c r="P472" s="1" t="inlineStr"/>
       <c r="Q472" s="1" t="inlineStr">
         <is>
-          <t>L1450: punctuation artifact: repeated periods :: NoÃ«l Gour, Bonnyville ......................</t>
+          <t>L1450: punctuation artifact: repeated periods :: Noël Gour, Bonnyville ......................</t>
         </is>
       </c>
       <c r="R472" s="1" t="inlineStr"/>
@@ -21629,7 +18985,7 @@
       <c r="P473" s="1" t="inlineStr"/>
       <c r="Q473" s="1" t="inlineStr">
         <is>
-          <t>L1452: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Billy Dubois, Ã©cole Dunrobin ..............</t>
+          <t>L1452: punctuation artifact: repeated periods :: Billy Dubois, école Dunrobin ..............</t>
         </is>
       </c>
       <c r="R473" s="1" t="inlineStr"/>
@@ -21734,7 +19090,7 @@
       <c r="P476" s="1" t="inlineStr"/>
       <c r="Q476" s="1" t="inlineStr">
         <is>
-          <t>L1482: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©onard Rousseau, Ã©cole Thibeault ...........</t>
+          <t>L1482: punctuation artifact: repeated periods :: Léonard Rousseau, école Thibeault ...........</t>
         </is>
       </c>
       <c r="R476" s="1" t="inlineStr"/>
@@ -21769,7 +19125,7 @@
       <c r="P477" s="1" t="inlineStr"/>
       <c r="Q477" s="1" t="inlineStr">
         <is>
-          <t>L1484: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Charles Ouellette, ThÃ©rien Village ..........</t>
+          <t>L1484: punctuation artifact: repeated periods :: Charles Ouellette, Thérien Village ..........</t>
         </is>
       </c>
       <c r="R477" s="1" t="inlineStr"/>
@@ -21804,7 +19160,7 @@
       <c r="P478" s="1" t="inlineStr"/>
       <c r="Q478" s="1" t="inlineStr">
         <is>
-          <t>L1488: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lucien Gagnon, Ã©cole consolidÃ©e, Falher .....</t>
+          <t>L1488: punctuation artifact: repeated periods :: Lucien Gagnon, école consolidée, Falher .....</t>
         </is>
       </c>
       <c r="R478" s="1" t="inlineStr"/>
@@ -21839,7 +19195,7 @@
       <c r="P479" s="1" t="inlineStr"/>
       <c r="Q479" s="1" t="inlineStr">
         <is>
-          <t>L1490: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Annette Lessard, Ã©cole consolidÃ©e, Falher ...</t>
+          <t>L1490: punctuation artifact: repeated periods :: Annette Lessard, école consolidée, Falher ...</t>
         </is>
       </c>
       <c r="R479" s="1" t="inlineStr"/>
@@ -21944,7 +19300,7 @@
       <c r="P482" s="1" t="inlineStr"/>
       <c r="Q482" s="1" t="inlineStr">
         <is>
-          <t>L1496: punctuation artifact: repeated periods :: FranÃ§oise Lissenden, Saint-Paul .............</t>
+          <t>L1496: punctuation artifact: repeated periods :: Françoise Lissenden, Saint-Paul .............</t>
         </is>
       </c>
       <c r="R482" s="1" t="inlineStr"/>
@@ -21979,7 +19335,7 @@
       <c r="P483" s="1" t="inlineStr"/>
       <c r="Q483" s="1" t="inlineStr">
         <is>
-          <t>L1498: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lilianne Doran, Ã©cole consolidÃ©e, Falher ....</t>
+          <t>L1498: punctuation artifact: repeated periods :: Lilianne Doran, école consolidée, Falher ....</t>
         </is>
       </c>
       <c r="R483" s="1" t="inlineStr"/>
@@ -22049,7 +19405,7 @@
       <c r="P485" s="1" t="inlineStr"/>
       <c r="Q485" s="1" t="inlineStr">
         <is>
-          <t>L1502: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se ChÃ©nard. Tangente ...................</t>
+          <t>L1502: punctuation artifact: repeated periods :: Thérèse Chénard. Tangente ...................</t>
         </is>
       </c>
       <c r="R485" s="1" t="inlineStr"/>
@@ -22084,7 +19440,7 @@
       <c r="P486" s="1" t="inlineStr"/>
       <c r="Q486" s="1" t="inlineStr">
         <is>
-          <t>L1505: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Fortin, Tangente..................</t>
+          <t>L1505: punctuation artifact: repeated periods :: René Fortin, Tangente..................</t>
         </is>
       </c>
       <c r="R486" s="1" t="inlineStr"/>
@@ -22154,7 +19510,7 @@
       <c r="P488" s="1" t="inlineStr"/>
       <c r="Q488" s="1" t="inlineStr">
         <is>
-          <t>L1513: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Michel Voyer, Ã©cole Grandin ................</t>
+          <t>L1513: punctuation artifact: repeated periods :: Michel Voyer, école Grandin ................</t>
         </is>
       </c>
       <c r="R488" s="1" t="inlineStr"/>
@@ -22189,7 +19545,7 @@
       <c r="P489" s="1" t="inlineStr"/>
       <c r="Q489" s="1" t="inlineStr">
         <is>
-          <t>L1515: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RomÃ©o BÃ©dard, Tangente .....................</t>
+          <t>L1515: punctuation artifact: repeated periods :: Roméo Bédard, Tangente .....................</t>
         </is>
       </c>
       <c r="R489" s="1" t="inlineStr"/>
@@ -22994,7 +20350,7 @@
       <c r="P512" s="1" t="inlineStr"/>
       <c r="Q512" s="1" t="inlineStr">
         <is>
-          <t>L1569: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lorraine BÃ©rubÃ©. Beaumont .......................</t>
+          <t>L1569: punctuation artifact: repeated periods :: Lorraine Bérubé. Beaumont .......................</t>
         </is>
       </c>
       <c r="R512" s="1" t="inlineStr"/>
@@ -23029,7 +20385,7 @@
       <c r="P513" s="1" t="inlineStr"/>
       <c r="Q513" s="1" t="inlineStr">
         <is>
-          <t>L1571: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Alberta LabontÃ©, Ã©cole Thibeault ................</t>
+          <t>L1571: punctuation artifact: repeated periods :: Alberta Labonté, école Thibeault ................</t>
         </is>
       </c>
       <c r="R513" s="1" t="inlineStr"/>
@@ -23064,7 +20420,7 @@
       <c r="P514" s="1" t="inlineStr"/>
       <c r="Q514" s="1" t="inlineStr">
         <is>
-          <t>L1573: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Fleurette Rousseau, Ã©cole Thibeault .............</t>
+          <t>L1573: punctuation artifact: repeated periods :: Fleurette Rousseau, école Thibeault .............</t>
         </is>
       </c>
       <c r="R514" s="1" t="inlineStr"/>
@@ -23134,7 +20490,7 @@
       <c r="P516" s="1" t="inlineStr"/>
       <c r="Q516" s="1" t="inlineStr">
         <is>
-          <t>L1577: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©ontine Aubin, Ã©cole consolidÃ©e, Falher ........</t>
+          <t>L1577: punctuation artifact: repeated periods :: Léontine Aubin, école consolidée, Falher ........</t>
         </is>
       </c>
       <c r="R516" s="1" t="inlineStr"/>
@@ -23274,7 +20630,7 @@
       <c r="P520" s="1" t="inlineStr"/>
       <c r="Q520" s="1" t="inlineStr">
         <is>
-          <t>L1585: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: OrigÃ¨ne Caouette, Bonnyville ....................</t>
+          <t>L1585: punctuation artifact: repeated periods :: Origène Caouette, Bonnyville ....................</t>
         </is>
       </c>
       <c r="R520" s="1" t="inlineStr"/>
@@ -23309,7 +20665,7 @@
       <c r="P521" s="1" t="inlineStr"/>
       <c r="Q521" s="1" t="inlineStr">
         <is>
-          <t>L1587: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Etiennette SÃ©guin, Bonnyville ...................</t>
+          <t>L1587: punctuation artifact: repeated periods :: Etiennette Séguin, Bonnyville ...................</t>
         </is>
       </c>
       <c r="R521" s="1" t="inlineStr"/>
@@ -23379,7 +20735,7 @@
       <c r="P523" s="1" t="inlineStr"/>
       <c r="Q523" s="1" t="inlineStr">
         <is>
-          <t>L1591: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ©e Meunier Ã©cole Thibeault ...................</t>
+          <t>L1591: punctuation artifact: repeated periods :: Renée Meunier école Thibeault ...................</t>
         </is>
       </c>
       <c r="R523" s="1" t="inlineStr"/>
@@ -23414,7 +20770,7 @@
       <c r="P524" s="1" t="inlineStr"/>
       <c r="Q524" s="1" t="inlineStr">
         <is>
-          <t>L1593: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©vis Chiasson, Sainte-Lina .....................</t>
+          <t>L1593: punctuation artifact: repeated periods :: Lévis Chiasson, Sainte-Lina .....................</t>
         </is>
       </c>
       <c r="R524" s="1" t="inlineStr"/>
@@ -23449,7 +20805,7 @@
       <c r="P525" s="1" t="inlineStr"/>
       <c r="Q525" s="1" t="inlineStr">
         <is>
-          <t>L1595: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marcel Legris, Ã©cole Grandin ....................</t>
+          <t>L1595: punctuation artifact: repeated periods :: Marcel Legris, école Grandin ....................</t>
         </is>
       </c>
       <c r="R525" s="1" t="inlineStr"/>
@@ -23554,7 +20910,7 @@
       <c r="P528" s="1" t="inlineStr"/>
       <c r="Q528" s="1" t="inlineStr">
         <is>
-          <t>L1601: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 64 Rose-Marie Aubert, ThÃ©rien ...................</t>
+          <t>L1601: punctuation artifact: repeated periods :: 64 Rose-Marie Aubert, Thérien ...................</t>
         </is>
       </c>
       <c r="R528" s="1" t="inlineStr"/>
@@ -23589,7 +20945,7 @@
       <c r="P529" s="1" t="inlineStr"/>
       <c r="Q529" s="1" t="inlineStr">
         <is>
-          <t>L1603: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ,ThÃ©rÃ¨se Rochette. Tangente.................</t>
+          <t>L1603: punctuation artifact: repeated periods :: ,Thérèse Rochette. Tangente.................</t>
         </is>
       </c>
       <c r="R529" s="1" t="inlineStr"/>
@@ -23624,7 +20980,7 @@
       <c r="P530" s="1" t="inlineStr"/>
       <c r="Q530" s="1" t="inlineStr">
         <is>
-          <t>L1605: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Lussier, Tangente......................</t>
+          <t>L1605: punctuation artifact: repeated periods :: René Lussier, Tangente......................</t>
         </is>
       </c>
       <c r="R530" s="1" t="inlineStr"/>
@@ -23694,7 +21050,7 @@
       <c r="P532" s="1" t="inlineStr"/>
       <c r="Q532" s="1" t="inlineStr">
         <is>
-          <t>L1609: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ;ThÃ©rÃ¨se Gauthier, Plamondon................</t>
+          <t>L1609: punctuation artifact: repeated periods :: ;Thérèse Gauthier, Plamondon................</t>
         </is>
       </c>
       <c r="R532" s="1" t="inlineStr"/>
@@ -23764,7 +21120,7 @@
       <c r="P534" s="1" t="inlineStr"/>
       <c r="Q534" s="1" t="inlineStr">
         <is>
-          <t>L1613: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Elise Chartrand, Ã©cole Grandin .............</t>
+          <t>L1613: punctuation artifact: repeated periods :: Elise Chartrand, école Grandin .............</t>
         </is>
       </c>
       <c r="R534" s="1" t="inlineStr"/>
@@ -23799,7 +21155,7 @@
       <c r="P535" s="1" t="inlineStr"/>
       <c r="Q535" s="1" t="inlineStr">
         <is>
-          <t>L1615: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RomÃ©o Dechaine, Sainte-Lina ................</t>
+          <t>L1615: punctuation artifact: repeated periods :: Roméo Dechaine, Sainte-Lina ................</t>
         </is>
       </c>
       <c r="R535" s="1" t="inlineStr"/>
@@ -23834,7 +21190,7 @@
       <c r="P536" s="1" t="inlineStr"/>
       <c r="Q536" s="1" t="inlineStr">
         <is>
-          <t>L1617: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Bouchard, Tangente .................</t>
+          <t>L1617: punctuation artifact: repeated periods :: Thérèse Bouchard, Tangente .................</t>
         </is>
       </c>
       <c r="R536" s="1" t="inlineStr"/>
@@ -23939,7 +21295,7 @@
       <c r="P539" s="1" t="inlineStr"/>
       <c r="Q539" s="1" t="inlineStr">
         <is>
-          <t>L1623: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: Laurier CarriÃ¨re, Legal ....................</t>
+          <t>L1623: punctuation artifact: repeated periods :: Laurier Carrière, Legal ....................</t>
         </is>
       </c>
       <c r="R539" s="1" t="inlineStr"/>
@@ -24044,7 +21400,7 @@
       <c r="P542" s="1" t="inlineStr"/>
       <c r="Q542" s="1" t="inlineStr">
         <is>
-          <t>L1629: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Laurette Lafond, Ã©cole Thibeault ...........</t>
+          <t>L1629: punctuation artifact: repeated periods :: Laurette Lafond, école Thibeault ...........</t>
         </is>
       </c>
       <c r="R542" s="1" t="inlineStr"/>
@@ -24079,7 +21435,7 @@
       <c r="P543" s="1" t="inlineStr"/>
       <c r="Q543" s="1" t="inlineStr">
         <is>
-          <t>L1631: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Doreen Stelte, Ã©cole Thibeault .............</t>
+          <t>L1631: punctuation artifact: repeated periods :: Doreen Stelte, école Thibeault .............</t>
         </is>
       </c>
       <c r="R543" s="1" t="inlineStr"/>
@@ -24149,7 +21505,7 @@
       <c r="P545" s="1" t="inlineStr"/>
       <c r="Q545" s="1" t="inlineStr">
         <is>
-          <t>L1635: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Magant, Sainte-Lina ......-</t>
+          <t>L1635: punctuation artifact: repeated periods :: René Magant, Sainte-Lina ......-</t>
         </is>
       </c>
       <c r="R545" s="1" t="inlineStr"/>
@@ -24289,7 +21645,7 @@
       <c r="P549" s="1" t="inlineStr"/>
       <c r="Q549" s="1" t="inlineStr">
         <is>
-          <t>L1643: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RÃ©jeanne Rochette, Tangente ................</t>
+          <t>L1643: punctuation artifact: repeated periods :: Réjeanne Rochette, Tangente ................</t>
         </is>
       </c>
       <c r="R549" s="1" t="inlineStr"/>
@@ -24324,7 +21680,7 @@
       <c r="P550" s="1" t="inlineStr"/>
       <c r="Q550" s="1" t="inlineStr">
         <is>
-          <t>L1645: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: Rachel Ouellette, Tangente .............â€”...</t>
+          <t>L1645: punctuation artifact: repeated periods :: Rachel Ouellette, Tangente .............—...</t>
         </is>
       </c>
       <c r="R550" s="1" t="inlineStr"/>
@@ -24359,7 +21715,7 @@
       <c r="P551" s="1" t="inlineStr"/>
       <c r="Q551" s="1" t="inlineStr">
         <is>
-          <t>L1651: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marc Voyer, Ã©cole Grandin ..................</t>
+          <t>L1651: punctuation artifact: repeated periods :: Marc Voyer, école Grandin ..................</t>
         </is>
       </c>
       <c r="R551" s="1" t="inlineStr"/>
@@ -24429,7 +21785,7 @@
       <c r="P553" s="1" t="inlineStr"/>
       <c r="Q553" s="1" t="inlineStr">
         <is>
-          <t>L1661: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Denise Despins, Ã©cole Dunrobin ..........................</t>
+          <t>L1661: punctuation artifact: repeated periods :: Denise Despins, école Dunrobin ..........................</t>
         </is>
       </c>
       <c r="R553" s="1" t="inlineStr"/>
@@ -24464,7 +21820,7 @@
       <c r="P554" s="1" t="inlineStr"/>
       <c r="Q554" s="1" t="inlineStr">
         <is>
-          <t>L1663: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 82 Antonia Villeneuve, Ã©cole consolidÃ©e, Falher ........</t>
+          <t>L1663: punctuation artifact: repeated periods :: 82 Antonia Villeneuve, école consolidée, Falher ........</t>
         </is>
       </c>
       <c r="R554" s="1" t="inlineStr"/>
@@ -24569,7 +21925,7 @@
       <c r="P557" s="1" t="inlineStr"/>
       <c r="Q557" s="1" t="inlineStr">
         <is>
-          <t>L1671: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Diane Ouellette, Ã©cole consolidÃ©e, Donnelly .............</t>
+          <t>L1671: punctuation artifact: repeated periods :: Diane Ouellette, école consolidée, Donnelly .............</t>
         </is>
       </c>
       <c r="R557" s="1" t="inlineStr"/>
@@ -24674,7 +22030,7 @@
       <c r="P560" s="1" t="inlineStr"/>
       <c r="Q560" s="1" t="inlineStr">
         <is>
-          <t>L1678: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ....85 Denise Plaquin, ThÃ©rien:</t>
+          <t>L1678: punctuation artifact: repeated periods :: ....85 Denise Plaquin, Thérien:</t>
         </is>
       </c>
       <c r="R560" s="1" t="inlineStr"/>
@@ -24744,7 +22100,7 @@
       <c r="P562" s="1" t="inlineStr"/>
       <c r="Q562" s="1" t="inlineStr">
         <is>
-          <t>L1694: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ©a Trudel, Saint-Paul ................</t>
+          <t>L1694: punctuation artifact: repeated periods :: Andréa Trudel, Saint-Paul ................</t>
         </is>
       </c>
       <c r="R562" s="1" t="inlineStr"/>
@@ -24814,7 +22170,7 @@
       <c r="P564" s="1" t="inlineStr"/>
       <c r="Q564" s="1" t="inlineStr">
         <is>
-          <t>L1698: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Emile Isabel, Ã©cole consolidÃ©e, Falher ..</t>
+          <t>L1698: punctuation artifact: repeated periods :: Emile Isabel, école consolidée, Falher ..</t>
         </is>
       </c>
       <c r="R564" s="1" t="inlineStr"/>
@@ -24884,7 +22240,7 @@
       <c r="P566" s="1" t="inlineStr"/>
       <c r="Q566" s="1" t="inlineStr">
         <is>
-          <t>L1702: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lucien Gratton, ThÃ©rien Village .........</t>
+          <t>L1702: punctuation artifact: repeated periods :: Lucien Gratton, Thérien Village .........</t>
         </is>
       </c>
       <c r="R566" s="1" t="inlineStr"/>
@@ -24989,7 +22345,7 @@
       <c r="P569" s="1" t="inlineStr"/>
       <c r="Q569" s="1" t="inlineStr">
         <is>
-          <t>L1712: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lucien Roy, Ã©cole consolidÃ©e, Falher .....</t>
+          <t>L1712: punctuation artifact: repeated periods :: Lucien Roy, école consolidée, Falher .....</t>
         </is>
       </c>
       <c r="R569" s="1" t="inlineStr"/>
@@ -25199,7 +22555,7 @@
       <c r="P575" s="1" t="inlineStr"/>
       <c r="Q575" s="1" t="inlineStr">
         <is>
-          <t>L1803: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: double/multiple hyphen :: tableau qui comportait un homme dÃ©ca--</t>
+          <t>L1803: punctuation artifact: double/multiple hyphen :: tableau qui comportait un homme déca--</t>
         </is>
       </c>
       <c r="R575" s="1" t="inlineStr"/>
@@ -25234,7 +22590,7 @@
       <c r="P576" s="1" t="inlineStr"/>
       <c r="Q576" s="1" t="inlineStr">
         <is>
-          <t>L1929: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00B4 ACUTE ACCENT, U+20AC EURO SIGN | punctuation artifact: repeated periods :: la fonte des mine- lÃ©e Ã devenir l'entrepÃ´t des produits du ..........__â€ž</t>
+          <t>L1929: punctuation artifact: repeated periods :: la fonte des mine- lée à devenir l'entrepôt des produits du ..........__„</t>
         </is>
       </c>
       <c r="R576" s="1" t="inlineStr"/>
@@ -26750,7 +24106,7 @@
       <c r="M625" s="1" t="inlineStr"/>
       <c r="N625" s="1" t="inlineStr">
         <is>
-          <t>L1284: isolated marker/symbol line :: 65</t>
+          <t>L1282: stray/suspicious non-ASCII glyph(s): U+4E0A CJK UNIFIED IDEOGRAPH-4E0A | isolated marker/symbol line :: 上</t>
         </is>
       </c>
       <c r="O625" s="1" t="inlineStr"/>
@@ -26781,7 +24137,7 @@
       <c r="M626" s="1" t="inlineStr"/>
       <c r="N626" s="1" t="inlineStr">
         <is>
-          <t>L1286: isolated marker/symbol line :: 65</t>
+          <t>L1284: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O626" s="1" t="inlineStr"/>
@@ -26812,7 +24168,7 @@
       <c r="M627" s="1" t="inlineStr"/>
       <c r="N627" s="1" t="inlineStr">
         <is>
-          <t>L1288: isolated marker/symbol line :: 656</t>
+          <t>L1286: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O627" s="1" t="inlineStr"/>
@@ -26843,7 +24199,7 @@
       <c r="M628" s="1" t="inlineStr"/>
       <c r="N628" s="1" t="inlineStr">
         <is>
-          <t>L1290: symbol-only separator/garbage line :: 365464</t>
+          <t>L1288: isolated marker/symbol line :: 656</t>
         </is>
       </c>
       <c r="O628" s="1" t="inlineStr"/>
@@ -26874,7 +24230,7 @@
       <c r="M629" s="1" t="inlineStr"/>
       <c r="N629" s="1" t="inlineStr">
         <is>
-          <t>L1291: isolated marker/symbol line :: 64</t>
+          <t>L1290: symbol-only separator/garbage line :: 365464</t>
         </is>
       </c>
       <c r="O629" s="1" t="inlineStr"/>
@@ -26905,7 +24261,7 @@
       <c r="M630" s="1" t="inlineStr"/>
       <c r="N630" s="1" t="inlineStr">
         <is>
-          <t>L1292: isolated marker/symbol line :: 64</t>
+          <t>L1291: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O630" s="1" t="inlineStr"/>
@@ -26936,7 +24292,7 @@
       <c r="M631" s="1" t="inlineStr"/>
       <c r="N631" s="1" t="inlineStr">
         <is>
-          <t>L1298: isolated marker/symbol line :: -</t>
+          <t>L1292: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O631" s="1" t="inlineStr"/>
@@ -26967,7 +24323,7 @@
       <c r="M632" s="1" t="inlineStr"/>
       <c r="N632" s="1" t="inlineStr">
         <is>
-          <t>L1310: isolated marker/symbol line :: ***</t>
+          <t>L1294: stray/suspicious non-ASCII glyph(s): U+548C CJK UNIFIED IDEOGRAPH-548C | isolated marker/symbol line :: 和</t>
         </is>
       </c>
       <c r="O632" s="1" t="inlineStr"/>
@@ -26998,7 +24354,7 @@
       <c r="M633" s="1" t="inlineStr"/>
       <c r="N633" s="1" t="inlineStr">
         <is>
-          <t>L1311: isolated marker/symbol line :: ***</t>
+          <t>L1298: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O633" s="1" t="inlineStr"/>
@@ -27029,7 +24385,7 @@
       <c r="M634" s="1" t="inlineStr"/>
       <c r="N634" s="1" t="inlineStr">
         <is>
-          <t>L1313: symbol-only separator/garbage line :: (1831-?)</t>
+          <t>L1301: stray/suspicious non-ASCII glyph(s): U+771F CJK UNIFIED IDEOGRAPH-771F | isolated marker/symbol line :: 真</t>
         </is>
       </c>
       <c r="O634" s="1" t="inlineStr"/>
@@ -27060,7 +24416,7 @@
       <c r="M635" s="1" t="inlineStr"/>
       <c r="N635" s="1" t="inlineStr">
         <is>
-          <t>L1366: symbol-only separator/garbage line :: (1815-1871)</t>
+          <t>L1310: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O635" s="1" t="inlineStr"/>
@@ -27091,7 +24447,7 @@
       <c r="M636" s="1" t="inlineStr"/>
       <c r="N636" s="1" t="inlineStr">
         <is>
-          <t>L1404: isolated marker/symbol line :: ***</t>
+          <t>L1311: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O636" s="1" t="inlineStr"/>
@@ -27122,7 +24478,7 @@
       <c r="M637" s="1" t="inlineStr"/>
       <c r="N637" s="1" t="inlineStr">
         <is>
-          <t>L1406: isolated marker/symbol line :: V</t>
+          <t>L1313: symbol-only separator/garbage line :: (1831-?)</t>
         </is>
       </c>
       <c r="O637" s="1" t="inlineStr"/>
@@ -27153,7 +24509,7 @@
       <c r="M638" s="1" t="inlineStr"/>
       <c r="N638" s="1" t="inlineStr">
         <is>
-          <t>L1408: symbol-only separator/garbage line :: (1767-1844)</t>
+          <t>L1366: symbol-only separator/garbage line :: (1815-1871)</t>
         </is>
       </c>
       <c r="O638" s="1" t="inlineStr"/>
@@ -27184,7 +24540,7 @@
       <c r="M639" s="1" t="inlineStr"/>
       <c r="N639" s="1" t="inlineStr">
         <is>
-          <t>L1411: isolated marker/symbol line :: 1</t>
+          <t>L1404: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O639" s="1" t="inlineStr"/>
@@ -27215,7 +24571,7 @@
       <c r="M640" s="1" t="inlineStr"/>
       <c r="N640" s="1" t="inlineStr">
         <is>
-          <t>L1434: isolated marker/symbol line :: 81</t>
+          <t>L1405: stray/suspicious non-ASCII glyph(s): U+7C73 CJK UNIFIED IDEOGRAPH-7C73 | isolated marker/symbol line :: 米</t>
         </is>
       </c>
       <c r="O640" s="1" t="inlineStr"/>
@@ -27246,7 +24602,7 @@
       <c r="M641" s="1" t="inlineStr"/>
       <c r="N641" s="1" t="inlineStr">
         <is>
-          <t>L1435: isolated marker/symbol line :: 82</t>
+          <t>L1406: isolated marker/symbol line :: V</t>
         </is>
       </c>
       <c r="O641" s="1" t="inlineStr"/>
@@ -27277,7 +24633,7 @@
       <c r="M642" s="1" t="inlineStr"/>
       <c r="N642" s="1" t="inlineStr">
         <is>
-          <t>L1451: isolated marker/symbol line :: :</t>
+          <t>L1408: symbol-only separator/garbage line :: (1767-1844)</t>
         </is>
       </c>
       <c r="O642" s="1" t="inlineStr"/>
@@ -27308,7 +24664,7 @@
       <c r="M643" s="1" t="inlineStr"/>
       <c r="N643" s="1" t="inlineStr">
         <is>
-          <t>L1452: isolated marker/symbol line :: +</t>
+          <t>L1411: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O643" s="1" t="inlineStr"/>
@@ -27339,7 +24695,7 @@
       <c r="M644" s="1" t="inlineStr"/>
       <c r="N644" s="1" t="inlineStr">
         <is>
-          <t>L1553: isolated marker/symbol line :: +</t>
+          <t>L1434: isolated marker/symbol line :: 81</t>
         </is>
       </c>
       <c r="O644" s="1" t="inlineStr"/>
@@ -27354,6 +24710,130 @@
       <c r="X644" s="1" t="inlineStr"/>
       <c r="Y644" s="1" t="inlineStr"/>
     </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr"/>
+      <c r="B645" s="1" t="inlineStr"/>
+      <c r="C645" s="1" t="inlineStr"/>
+      <c r="D645" s="1" t="inlineStr"/>
+      <c r="E645" s="1" t="inlineStr"/>
+      <c r="F645" s="1" t="inlineStr"/>
+      <c r="G645" s="1" t="inlineStr"/>
+      <c r="H645" s="1" t="inlineStr"/>
+      <c r="I645" s="1" t="inlineStr"/>
+      <c r="J645" s="1" t="inlineStr"/>
+      <c r="K645" s="1" t="inlineStr"/>
+      <c r="L645" s="1" t="inlineStr"/>
+      <c r="M645" s="1" t="inlineStr"/>
+      <c r="N645" s="1" t="inlineStr">
+        <is>
+          <t>L1435: isolated marker/symbol line :: 82</t>
+        </is>
+      </c>
+      <c r="O645" s="1" t="inlineStr"/>
+      <c r="P645" s="1" t="inlineStr"/>
+      <c r="Q645" s="1" t="inlineStr"/>
+      <c r="R645" s="1" t="inlineStr"/>
+      <c r="S645" s="1" t="inlineStr"/>
+      <c r="T645" s="1" t="inlineStr"/>
+      <c r="U645" s="1" t="inlineStr"/>
+      <c r="V645" s="1" t="inlineStr"/>
+      <c r="W645" s="1" t="inlineStr"/>
+      <c r="X645" s="1" t="inlineStr"/>
+      <c r="Y645" s="1" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr"/>
+      <c r="B646" s="1" t="inlineStr"/>
+      <c r="C646" s="1" t="inlineStr"/>
+      <c r="D646" s="1" t="inlineStr"/>
+      <c r="E646" s="1" t="inlineStr"/>
+      <c r="F646" s="1" t="inlineStr"/>
+      <c r="G646" s="1" t="inlineStr"/>
+      <c r="H646" s="1" t="inlineStr"/>
+      <c r="I646" s="1" t="inlineStr"/>
+      <c r="J646" s="1" t="inlineStr"/>
+      <c r="K646" s="1" t="inlineStr"/>
+      <c r="L646" s="1" t="inlineStr"/>
+      <c r="M646" s="1" t="inlineStr"/>
+      <c r="N646" s="1" t="inlineStr">
+        <is>
+          <t>L1451: isolated marker/symbol line :: :</t>
+        </is>
+      </c>
+      <c r="O646" s="1" t="inlineStr"/>
+      <c r="P646" s="1" t="inlineStr"/>
+      <c r="Q646" s="1" t="inlineStr"/>
+      <c r="R646" s="1" t="inlineStr"/>
+      <c r="S646" s="1" t="inlineStr"/>
+      <c r="T646" s="1" t="inlineStr"/>
+      <c r="U646" s="1" t="inlineStr"/>
+      <c r="V646" s="1" t="inlineStr"/>
+      <c r="W646" s="1" t="inlineStr"/>
+      <c r="X646" s="1" t="inlineStr"/>
+      <c r="Y646" s="1" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr"/>
+      <c r="B647" s="1" t="inlineStr"/>
+      <c r="C647" s="1" t="inlineStr"/>
+      <c r="D647" s="1" t="inlineStr"/>
+      <c r="E647" s="1" t="inlineStr"/>
+      <c r="F647" s="1" t="inlineStr"/>
+      <c r="G647" s="1" t="inlineStr"/>
+      <c r="H647" s="1" t="inlineStr"/>
+      <c r="I647" s="1" t="inlineStr"/>
+      <c r="J647" s="1" t="inlineStr"/>
+      <c r="K647" s="1" t="inlineStr"/>
+      <c r="L647" s="1" t="inlineStr"/>
+      <c r="M647" s="1" t="inlineStr"/>
+      <c r="N647" s="1" t="inlineStr">
+        <is>
+          <t>L1452: isolated marker/symbol line :: +</t>
+        </is>
+      </c>
+      <c r="O647" s="1" t="inlineStr"/>
+      <c r="P647" s="1" t="inlineStr"/>
+      <c r="Q647" s="1" t="inlineStr"/>
+      <c r="R647" s="1" t="inlineStr"/>
+      <c r="S647" s="1" t="inlineStr"/>
+      <c r="T647" s="1" t="inlineStr"/>
+      <c r="U647" s="1" t="inlineStr"/>
+      <c r="V647" s="1" t="inlineStr"/>
+      <c r="W647" s="1" t="inlineStr"/>
+      <c r="X647" s="1" t="inlineStr"/>
+      <c r="Y647" s="1" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr"/>
+      <c r="B648" s="1" t="inlineStr"/>
+      <c r="C648" s="1" t="inlineStr"/>
+      <c r="D648" s="1" t="inlineStr"/>
+      <c r="E648" s="1" t="inlineStr"/>
+      <c r="F648" s="1" t="inlineStr"/>
+      <c r="G648" s="1" t="inlineStr"/>
+      <c r="H648" s="1" t="inlineStr"/>
+      <c r="I648" s="1" t="inlineStr"/>
+      <c r="J648" s="1" t="inlineStr"/>
+      <c r="K648" s="1" t="inlineStr"/>
+      <c r="L648" s="1" t="inlineStr"/>
+      <c r="M648" s="1" t="inlineStr"/>
+      <c r="N648" s="1" t="inlineStr">
+        <is>
+          <t>L1553: isolated marker/symbol line :: +</t>
+        </is>
+      </c>
+      <c r="O648" s="1" t="inlineStr"/>
+      <c r="P648" s="1" t="inlineStr"/>
+      <c r="Q648" s="1" t="inlineStr"/>
+      <c r="R648" s="1" t="inlineStr"/>
+      <c r="S648" s="1" t="inlineStr"/>
+      <c r="T648" s="1" t="inlineStr"/>
+      <c r="U648" s="1" t="inlineStr"/>
+      <c r="V648" s="1" t="inlineStr"/>
+      <c r="W648" s="1" t="inlineStr"/>
+      <c r="X648" s="1" t="inlineStr"/>
+      <c r="Y648" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
